--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E24D5C-1F98-4145-8AC6-ED0D1DBB8C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B65A8DE-A701-4393-9907-C7F967DB280E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6720" yWindow="-12360" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
@@ -81,76 +81,77 @@
     <t>Cost</t>
   </si>
   <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>IllustName</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Silver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Legend</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Forest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sword</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rune</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Abyss</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Haven</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Portal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>IllustName</t>
-  </si>
-  <si>
-    <t>Bronze</t>
-  </si>
-  <si>
-    <t>Bronze</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Silver</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Legend</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Forest</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Sword</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Rune</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Abyss</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Haven</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Portal</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1-N-001</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1-N-002</t>
-  </si>
-  <si>
-    <t>1-N-003</t>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1_N_001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1_N_002</t>
+  </si>
+  <si>
+    <t>1_N_003</t>
   </si>
 </sst>
 </file>
@@ -506,9 +507,9 @@
     <col min="1" max="1" width="8.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.125" bestFit="1" customWidth="1"/>
@@ -517,7 +518,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>10</v>
@@ -526,45 +527,45 @@
         <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -577,22 +578,22 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>2</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -605,22 +606,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -924,7 +925,7 @@
           <x14:formula1>
             <xm:f>Select!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>E5:E1048576 F2:F4</xm:sqref>
+          <xm:sqref>F5:F1048576 D2:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6D25B85E-3F98-4AD2-9F6A-938890AC8B6D}">
           <x14:formula1>
@@ -954,37 +955,37 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -994,17 +995,17 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B65A8DE-A701-4393-9907-C7F967DB280E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688D0B54-84CB-42BC-9465-44F3D505A000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6720" yWindow="-12360" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Dragon</t>
     <phoneticPr fontId="1"/>
@@ -142,16 +142,6 @@
   <si>
     <t>Type</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1_N_001</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1_N_002</t>
-  </si>
-  <si>
-    <t>1_N_003</t>
   </si>
 </sst>
 </file>
@@ -549,8 +539,8 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>31</v>
+      <c r="A2" s="1">
+        <v>1000</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -577,8 +567,8 @@
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>32</v>
+      <c r="A3" s="1">
+        <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -605,8 +595,8 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>33</v>
+      <c r="A4" s="1">
+        <v>1002</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,18 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688D0B54-84CB-42BC-9465-44F3D505A000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D8CE84-1A30-4074-B6D4-95E6A307D6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="-12360" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
     <sheet name="Select" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Dragon</t>
     <phoneticPr fontId="1"/>
@@ -69,78 +78,177 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Silver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Legend</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Forest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sword</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rune</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Abyss</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Haven</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Portal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IllustID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SelectClass</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Class</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SelectRarity</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Rarity</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>IllustName</t>
-  </si>
-  <si>
-    <t>Bronze</t>
-  </si>
-  <si>
-    <t>Bronze</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Silver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SelectType</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Legend</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rune</t>
+  </si>
+  <si>
+    <t>Spell</t>
   </si>
   <si>
     <t>Forest</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Sword</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Rune</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェアリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナイト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>知恵の光</t>
+    <rPh sb="0" eb="2">
+      <t>チエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒカリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dragon</t>
   </si>
   <si>
     <t>Abyss</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Portal</t>
   </si>
   <si>
     <t>Haven</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Portal</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Type</t>
+  </si>
+  <si>
+    <t>竜の託宣</t>
+    <rPh sb="0" eb="1">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タクセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴースト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>漆黒の法典</t>
+    <rPh sb="0" eb="2">
+      <t>シッコク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操り人形</t>
+    <rPh sb="0" eb="1">
+      <t>アヤツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニンギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リノセウス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Defence</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -148,6 +256,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -164,7 +275,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,8 +288,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -201,16 +318,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -491,412 +637,729 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" style="14" customWidth="1"/>
+    <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.75" style="14" customWidth="1"/>
+    <col min="8" max="8" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="7">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11">
+        <f>VLOOKUP(B2,Select!A:D,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1">
-        <v>1000</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="11">
+        <f>VLOOKUP(D2,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="11">
+        <f>VLOOKUP(F2,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
         <v>2</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1">
-        <v>1001</v>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="7">
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
+      <c r="C3" s="11">
+        <f>VLOOKUP(CardData!B3,Select!A:D,4,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="11">
+        <f>VLOOKUP(D3,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="11">
+        <f>VLOOKUP(F3,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1">
+      <c r="I3" s="1">
         <v>2</v>
       </c>
-      <c r="G3" s="1">
+      <c r="J3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="1">
+      <c r="K3" s="1">
         <v>2</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1">
-        <v>1002</v>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="7">
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
+      <c r="C4" s="11">
+        <f>VLOOKUP(CardData!B4,Select!A:D,4,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="11">
+        <f>VLOOKUP(D4,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="11">
+        <f>VLOOKUP(F4,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="1">
+      <c r="I4" s="1">
         <v>4</v>
       </c>
-      <c r="G4" s="1">
+      <c r="J4" s="1">
         <v>3</v>
       </c>
-      <c r="H4" s="1">
+      <c r="K4" s="1">
         <v>4</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="8">
+        <v>100</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="12">
+        <f>VLOOKUP(CardData!B5,Select!A:D,4,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="12">
+        <f>VLOOKUP(D5,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="12">
+        <f>VLOOKUP(F5,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="8">
+        <v>200</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="12">
+        <f>VLOOKUP(CardData!B6,Select!A:D,4,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="12">
+        <f>VLOOKUP(D6,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="12">
+        <f>VLOOKUP(F6,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="7">
+        <v>300</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="11">
+        <f>VLOOKUP(CardData!B7,Select!A:D,4,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="11">
+        <f>VLOOKUP(D7,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="11">
+        <f>VLOOKUP(F7,Select!C:D,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="7">
+        <v>400</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="11">
+        <f>VLOOKUP(CardData!B8,Select!A:D,4,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="11">
+        <f>VLOOKUP(D8,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="11">
+        <f>VLOOKUP(F8,Select!C:D,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="7">
+        <v>500</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="11">
+        <f>VLOOKUP(CardData!B9,Select!A:D,4,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="11">
+        <f>VLOOKUP(D9,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="11">
+        <f>VLOOKUP(F9,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="7">
+        <v>600</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="11">
+        <f>VLOOKUP(CardData!B10,Select!A:D,4,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="11">
+        <f>VLOOKUP(D10,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="11">
+        <f>VLOOKUP(F10,Select!C:D,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="7">
+        <v>700</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="11">
+        <f>VLOOKUP(CardData!B11,Select!A:D,4,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="11">
+        <f>VLOOKUP(D11,Select!B:D,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="11">
+        <f>VLOOKUP(F11,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="7">
+        <v>1100</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="11">
+        <f>VLOOKUP(CardData!B12,Select!A:D,4,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="11">
+        <f>VLOOKUP(D12,Select!B:D,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="11">
+        <f>VLOOKUP(F12,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="9"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="9"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="9"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="9"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="9"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="9"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="9"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="9"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="9"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="9"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="9"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="9"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="9"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="9"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="9"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -909,19 +1372,19 @@
           <x14:formula1>
             <xm:f>Select!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B1048576</xm:sqref>
+          <xm:sqref>B2:B1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77E3A9D4-78DD-4D2C-96E8-862DE589AFFD}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6D25B85E-3F98-4AD2-9F6A-938890AC8B6D}">
           <x14:formula1>
             <xm:f>Select!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F1048576 D2:D1048576</xm:sqref>
+          <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6D25B85E-3F98-4AD2-9F6A-938890AC8B6D}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C3DBEF1F-74F9-454C-944E-EB27193EBDB8}">
           <x14:formula1>
             <xm:f>Select!$C:$C</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C1048576</xm:sqref>
+          <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -931,71 +1394,95 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12953D30-CE33-4EF2-BD8B-9EB747A2658E}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>28</v>
+      <c r="D8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D8CE84-1A30-4074-B6D4-95E6A307D6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7464D79-4165-40DF-AB73-3107C98D8163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
   <si>
     <t>Dragon</t>
     <phoneticPr fontId="1"/>
@@ -249,6 +249,16 @@
   </si>
   <si>
     <t>Defence</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>レヴィオンの迅雷・アルベール</t>
+    <rPh sb="6" eb="8">
+      <t>ジンライ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -335,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -357,6 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -647,7 +658,7 @@
     <col min="5" max="5" width="7.375" style="14" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.75" style="14" customWidth="1"/>
-    <col min="8" max="8" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.625" bestFit="1" customWidth="1"/>
@@ -1137,19 +1148,44 @@
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="9"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="A13" s="7">
+        <v>1200</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="11">
+        <f>VLOOKUP(CardData!B13,Select!A:D,4,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="11">
+        <f>VLOOKUP(D13,Select!B:D,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="11">
+        <f>VLOOKUP(F13,Select!C:D,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="15">
+        <v>5</v>
+      </c>
+      <c r="J13" s="15">
+        <v>3</v>
+      </c>
+      <c r="K13" s="15">
+        <v>5</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="9"/>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5894E381-53B9-4598-9D13-274C9EB23A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132DBCB4-5206-4EEA-90E5-BDE3A05BF229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Select" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6033" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5589" uniqueCount="1174">
   <si>
     <t>Dragon</t>
     <phoneticPr fontId="1"/>
@@ -4893,34 +4897,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFEBD8BB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE8D9F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFE6D5F3"/>
         </patternFill>
       </fill>
@@ -4950,6 +4926,34 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEBD8BB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE8D9F3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5124,10 +5128,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7715D875-69E8-4A33-A479-D6F5A01629FF}" name="テーブル1" displayName="テーブル1" ref="A1:P1048574" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22">
-  <autoFilter ref="A1:P1048574" xr:uid="{7715D875-69E8-4A33-A479-D6F5A01629FF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P1209">
-    <sortCondition ref="A1:A1048574"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7715D875-69E8-4A33-A479-D6F5A01629FF}" name="テーブル1" displayName="テーブル1" ref="A1:P1048490" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22">
+  <autoFilter ref="A1:P1048490" xr:uid="{7715D875-69E8-4A33-A479-D6F5A01629FF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P1107">
+    <sortCondition ref="A1:A1048490"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{65C53740-30CA-4A63-90A8-9F5F9123741B}" name="ID" dataDxfId="21"/>
@@ -5416,7 +5420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1218"/>
+  <dimension ref="A1:P1107"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7.875" style="8" bestFit="1" customWidth="1"/>
@@ -55669,14 +55673,14 @@
     </row>
     <row r="1030" spans="1:16">
       <c r="A1030" s="7">
-        <v>103124</v>
+        <v>103200</v>
       </c>
       <c r="B1030" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1030" s="2">
         <f>VLOOKUP(B1030,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1030" s="1" t="s">
         <v>11</v>
@@ -55692,10 +55696,18 @@
         <f>VLOOKUP(F1030,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1030" s="1"/>
-      <c r="I1030" s="1"/>
-      <c r="J1030" s="1"/>
-      <c r="K1030" s="1"/>
+      <c r="H1030" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I1030" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1030" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1030" s="1">
+        <v>2</v>
+      </c>
       <c r="L1030" s="1"/>
       <c r="M1030" s="1"/>
       <c r="N1030" s="4" t="b">
@@ -55711,14 +55723,14 @@
     </row>
     <row r="1031" spans="1:16">
       <c r="A1031" s="7">
-        <v>103125</v>
+        <v>103201</v>
       </c>
       <c r="B1031" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1031" s="2">
         <f>VLOOKUP(B1031,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1031" s="1" t="s">
         <v>11</v>
@@ -55734,10 +55746,18 @@
         <f>VLOOKUP(F1031,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1031" s="1"/>
-      <c r="I1031" s="1"/>
-      <c r="J1031" s="1"/>
-      <c r="K1031" s="1"/>
+      <c r="H1031" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I1031" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1031" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1031" s="1">
+        <v>2</v>
+      </c>
       <c r="L1031" s="1"/>
       <c r="M1031" s="1"/>
       <c r="N1031" s="4" t="b">
@@ -55753,14 +55773,14 @@
     </row>
     <row r="1032" spans="1:16">
       <c r="A1032" s="7">
-        <v>103126</v>
+        <v>103202</v>
       </c>
       <c r="B1032" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1032" s="2">
         <f>VLOOKUP(B1032,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1032" s="1" t="s">
         <v>11</v>
@@ -55776,10 +55796,18 @@
         <f>VLOOKUP(F1032,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1032" s="1"/>
-      <c r="I1032" s="1"/>
-      <c r="J1032" s="1"/>
-      <c r="K1032" s="1"/>
+      <c r="H1032" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I1032" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1032" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1032" s="1">
+        <v>2</v>
+      </c>
       <c r="L1032" s="1"/>
       <c r="M1032" s="1"/>
       <c r="N1032" s="4" t="b">
@@ -55795,14 +55823,14 @@
     </row>
     <row r="1033" spans="1:16">
       <c r="A1033" s="7">
-        <v>103127</v>
+        <v>103203</v>
       </c>
       <c r="B1033" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1033" s="2">
         <f>VLOOKUP(B1033,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1033" s="1" t="s">
         <v>11</v>
@@ -55818,10 +55846,18 @@
         <f>VLOOKUP(F1033,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1033" s="1"/>
-      <c r="I1033" s="1"/>
-      <c r="J1033" s="1"/>
-      <c r="K1033" s="1"/>
+      <c r="H1033" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I1033" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1033" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1033" s="1">
+        <v>6</v>
+      </c>
       <c r="L1033" s="1"/>
       <c r="M1033" s="1"/>
       <c r="N1033" s="4" t="b">
@@ -55837,14 +55873,14 @@
     </row>
     <row r="1034" spans="1:16">
       <c r="A1034" s="7">
-        <v>103128</v>
+        <v>103204</v>
       </c>
       <c r="B1034" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1034" s="2">
         <f>VLOOKUP(B1034,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1034" s="1" t="s">
         <v>11</v>
@@ -55854,14 +55890,18 @@
         <v>0</v>
       </c>
       <c r="F1034" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1034" s="2">
         <f>VLOOKUP(F1034,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1034" s="1"/>
-      <c r="I1034" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1034" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I1034" s="1">
+        <v>3</v>
+      </c>
       <c r="J1034" s="1"/>
       <c r="K1034" s="1"/>
       <c r="L1034" s="1"/>
@@ -55879,21 +55919,21 @@
     </row>
     <row r="1035" spans="1:16">
       <c r="A1035" s="7">
-        <v>103129</v>
+        <v>103205</v>
       </c>
       <c r="B1035" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1035" s="2">
         <f>VLOOKUP(B1035,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1035" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1035" s="2">
         <f>VLOOKUP(D1035,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1035" s="1" t="s">
         <v>3</v>
@@ -55902,10 +55942,18 @@
         <f>VLOOKUP(F1035,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1035" s="1"/>
-      <c r="I1035" s="1"/>
-      <c r="J1035" s="1"/>
-      <c r="K1035" s="1"/>
+      <c r="H1035" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I1035" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1035" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1035" s="1">
+        <v>2</v>
+      </c>
       <c r="L1035" s="1"/>
       <c r="M1035" s="1"/>
       <c r="N1035" s="4" t="b">
@@ -55921,21 +55969,21 @@
     </row>
     <row r="1036" spans="1:16">
       <c r="A1036" s="7">
-        <v>103130</v>
+        <v>103206</v>
       </c>
       <c r="B1036" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1036" s="2">
         <f>VLOOKUP(B1036,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1036" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1036" s="2">
         <f>VLOOKUP(D1036,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1036" s="1" t="s">
         <v>3</v>
@@ -55944,10 +55992,18 @@
         <f>VLOOKUP(F1036,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1036" s="1"/>
-      <c r="I1036" s="1"/>
-      <c r="J1036" s="1"/>
-      <c r="K1036" s="1"/>
+      <c r="H1036" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I1036" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1036" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1036" s="1">
+        <v>3</v>
+      </c>
       <c r="L1036" s="1"/>
       <c r="M1036" s="1"/>
       <c r="N1036" s="4" t="b">
@@ -55963,21 +56019,21 @@
     </row>
     <row r="1037" spans="1:16">
       <c r="A1037" s="7">
-        <v>103131</v>
+        <v>103207</v>
       </c>
       <c r="B1037" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1037" s="2">
         <f>VLOOKUP(B1037,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1037" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1037" s="2">
         <f>VLOOKUP(D1037,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1037" s="1" t="s">
         <v>3</v>
@@ -55986,10 +56042,18 @@
         <f>VLOOKUP(F1037,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1037" s="1"/>
-      <c r="I1037" s="1"/>
-      <c r="J1037" s="1"/>
-      <c r="K1037" s="1"/>
+      <c r="H1037" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I1037" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1037" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1037" s="1">
+        <v>4</v>
+      </c>
       <c r="L1037" s="1"/>
       <c r="M1037" s="1"/>
       <c r="N1037" s="4" t="b">
@@ -56005,31 +56069,35 @@
     </row>
     <row r="1038" spans="1:16">
       <c r="A1038" s="7">
-        <v>103132</v>
+        <v>103208</v>
       </c>
       <c r="B1038" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1038" s="2">
         <f>VLOOKUP(B1038,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1038" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1038" s="2">
         <f>VLOOKUP(D1038,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1038" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1038" s="2">
         <f>VLOOKUP(F1038,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1038" s="1"/>
-      <c r="I1038" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1038" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I1038" s="1">
+        <v>5</v>
+      </c>
       <c r="J1038" s="1"/>
       <c r="K1038" s="1"/>
       <c r="L1038" s="1"/>
@@ -56047,21 +56115,21 @@
     </row>
     <row r="1039" spans="1:16">
       <c r="A1039" s="7">
-        <v>103133</v>
+        <v>103209</v>
       </c>
       <c r="B1039" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1039" s="2">
         <f>VLOOKUP(B1039,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1039" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1039" s="2">
         <f>VLOOKUP(D1039,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1039" s="1" t="s">
         <v>3</v>
@@ -56070,10 +56138,18 @@
         <f>VLOOKUP(F1039,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1039" s="1"/>
-      <c r="I1039" s="1"/>
-      <c r="J1039" s="1"/>
-      <c r="K1039" s="1"/>
+      <c r="H1039" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I1039" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1039" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1039" s="1">
+        <v>4</v>
+      </c>
       <c r="L1039" s="1"/>
       <c r="M1039" s="1"/>
       <c r="N1039" s="4" t="b">
@@ -56089,21 +56165,21 @@
     </row>
     <row r="1040" spans="1:16">
       <c r="A1040" s="7">
-        <v>103134</v>
+        <v>103210</v>
       </c>
       <c r="B1040" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1040" s="2">
         <f>VLOOKUP(B1040,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1040" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1040" s="2">
         <f>VLOOKUP(D1040,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1040" s="1" t="s">
         <v>3</v>
@@ -56112,10 +56188,18 @@
         <f>VLOOKUP(F1040,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1040" s="1"/>
-      <c r="I1040" s="1"/>
-      <c r="J1040" s="1"/>
-      <c r="K1040" s="1"/>
+      <c r="H1040" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I1040" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1040" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1040" s="1">
+        <v>8</v>
+      </c>
       <c r="L1040" s="1"/>
       <c r="M1040" s="1"/>
       <c r="N1040" s="4" t="b">
@@ -56131,31 +56215,35 @@
     </row>
     <row r="1041" spans="1:16">
       <c r="A1041" s="7">
-        <v>103135</v>
+        <v>103211</v>
       </c>
       <c r="B1041" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1041" s="2">
         <f>VLOOKUP(B1041,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1041" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1041" s="2">
         <f>VLOOKUP(D1041,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1041" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G1041" s="2">
         <f>VLOOKUP(F1041,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1041" s="1"/>
-      <c r="I1041" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1041" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I1041" s="1">
+        <v>3</v>
+      </c>
       <c r="J1041" s="1"/>
       <c r="K1041" s="1"/>
       <c r="L1041" s="1"/>
@@ -56173,21 +56261,21 @@
     </row>
     <row r="1042" spans="1:16">
       <c r="A1042" s="7">
-        <v>103136</v>
+        <v>103212</v>
       </c>
       <c r="B1042" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1042" s="2">
         <f>VLOOKUP(B1042,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1042" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E1042" s="2">
         <f>VLOOKUP(D1042,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1042" s="1" t="s">
         <v>3</v>
@@ -56196,10 +56284,18 @@
         <f>VLOOKUP(F1042,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1042" s="1"/>
-      <c r="I1042" s="1"/>
-      <c r="J1042" s="1"/>
-      <c r="K1042" s="1"/>
+      <c r="H1042" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I1042" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1042" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1042" s="1">
+        <v>5</v>
+      </c>
       <c r="L1042" s="1"/>
       <c r="M1042" s="1"/>
       <c r="N1042" s="4" t="b">
@@ -56215,14 +56311,14 @@
     </row>
     <row r="1043" spans="1:16">
       <c r="A1043" s="7">
-        <v>103137</v>
+        <v>103300</v>
       </c>
       <c r="B1043" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1043" s="2">
         <f>VLOOKUP(B1043,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1043" s="1" t="s">
         <v>11</v>
@@ -56238,10 +56334,18 @@
         <f>VLOOKUP(F1043,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1043" s="1"/>
-      <c r="I1043" s="1"/>
-      <c r="J1043" s="1"/>
-      <c r="K1043" s="1"/>
+      <c r="H1043" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I1043" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1043" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1043" s="1">
+        <v>2</v>
+      </c>
       <c r="L1043" s="1"/>
       <c r="M1043" s="1"/>
       <c r="N1043" s="4" t="b">
@@ -56257,14 +56361,14 @@
     </row>
     <row r="1044" spans="1:16">
       <c r="A1044" s="7">
-        <v>103138</v>
+        <v>103301</v>
       </c>
       <c r="B1044" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1044" s="2">
         <f>VLOOKUP(B1044,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1044" s="1" t="s">
         <v>11</v>
@@ -56280,10 +56384,18 @@
         <f>VLOOKUP(F1044,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1044" s="1"/>
-      <c r="I1044" s="1"/>
-      <c r="J1044" s="1"/>
-      <c r="K1044" s="1"/>
+      <c r="H1044" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1044" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1044" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1044" s="1">
+        <v>4</v>
+      </c>
       <c r="L1044" s="1"/>
       <c r="M1044" s="1"/>
       <c r="N1044" s="4" t="b">
@@ -56299,14 +56411,14 @@
     </row>
     <row r="1045" spans="1:16">
       <c r="A1045" s="7">
-        <v>103139</v>
+        <v>103302</v>
       </c>
       <c r="B1045" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1045" s="2">
         <f>VLOOKUP(B1045,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1045" s="1" t="s">
         <v>11</v>
@@ -56322,10 +56434,18 @@
         <f>VLOOKUP(F1045,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1045" s="1"/>
-      <c r="I1045" s="1"/>
-      <c r="J1045" s="1"/>
-      <c r="K1045" s="1"/>
+      <c r="H1045" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I1045" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1045" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1045" s="1">
+        <v>4</v>
+      </c>
       <c r="L1045" s="1"/>
       <c r="M1045" s="1"/>
       <c r="N1045" s="4" t="b">
@@ -56341,14 +56461,14 @@
     </row>
     <row r="1046" spans="1:16">
       <c r="A1046" s="7">
-        <v>103140</v>
+        <v>103303</v>
       </c>
       <c r="B1046" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1046" s="2">
         <f>VLOOKUP(B1046,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1046" s="1" t="s">
         <v>11</v>
@@ -56364,10 +56484,18 @@
         <f>VLOOKUP(F1046,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1046" s="1"/>
-      <c r="I1046" s="1"/>
-      <c r="J1046" s="1"/>
-      <c r="K1046" s="1"/>
+      <c r="H1046" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I1046" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1046" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1046" s="1">
+        <v>2</v>
+      </c>
       <c r="L1046" s="1"/>
       <c r="M1046" s="1"/>
       <c r="N1046" s="4" t="b">
@@ -56383,14 +56511,14 @@
     </row>
     <row r="1047" spans="1:16">
       <c r="A1047" s="7">
-        <v>103141</v>
+        <v>103304</v>
       </c>
       <c r="B1047" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1047" s="2">
         <f>VLOOKUP(B1047,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1047" s="1" t="s">
         <v>11</v>
@@ -56400,14 +56528,18 @@
         <v>0</v>
       </c>
       <c r="F1047" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1047" s="2">
         <f>VLOOKUP(F1047,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1047" s="1"/>
-      <c r="I1047" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1047" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="I1047" s="1">
+        <v>3</v>
+      </c>
       <c r="J1047" s="1"/>
       <c r="K1047" s="1"/>
       <c r="L1047" s="1"/>
@@ -56425,21 +56557,21 @@
     </row>
     <row r="1048" spans="1:16">
       <c r="A1048" s="7">
-        <v>103142</v>
+        <v>103305</v>
       </c>
       <c r="B1048" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1048" s="2">
         <f>VLOOKUP(B1048,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1048" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1048" s="2">
         <f>VLOOKUP(D1048,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1048" s="1" t="s">
         <v>3</v>
@@ -56448,10 +56580,18 @@
         <f>VLOOKUP(F1048,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1048" s="1"/>
-      <c r="I1048" s="1"/>
-      <c r="J1048" s="1"/>
-      <c r="K1048" s="1"/>
+      <c r="H1048" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I1048" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1048" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1048" s="1">
+        <v>2</v>
+      </c>
       <c r="L1048" s="1"/>
       <c r="M1048" s="1"/>
       <c r="N1048" s="4" t="b">
@@ -56467,21 +56607,21 @@
     </row>
     <row r="1049" spans="1:16">
       <c r="A1049" s="7">
-        <v>103143</v>
+        <v>103306</v>
       </c>
       <c r="B1049" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1049" s="2">
         <f>VLOOKUP(B1049,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1049" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1049" s="2">
         <f>VLOOKUP(D1049,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1049" s="1" t="s">
         <v>3</v>
@@ -56490,10 +56630,18 @@
         <f>VLOOKUP(F1049,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1049" s="1"/>
-      <c r="I1049" s="1"/>
-      <c r="J1049" s="1"/>
-      <c r="K1049" s="1"/>
+      <c r="H1049" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I1049" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1049" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1049" s="1">
+        <v>3</v>
+      </c>
       <c r="L1049" s="1"/>
       <c r="M1049" s="1"/>
       <c r="N1049" s="4" t="b">
@@ -56509,21 +56657,21 @@
     </row>
     <row r="1050" spans="1:16">
       <c r="A1050" s="7">
-        <v>103144</v>
+        <v>103307</v>
       </c>
       <c r="B1050" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1050" s="2">
         <f>VLOOKUP(B1050,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1050" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1050" s="2">
         <f>VLOOKUP(D1050,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1050" s="1" t="s">
         <v>3</v>
@@ -56532,10 +56680,18 @@
         <f>VLOOKUP(F1050,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1050" s="1"/>
-      <c r="I1050" s="1"/>
-      <c r="J1050" s="1"/>
-      <c r="K1050" s="1"/>
+      <c r="H1050" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I1050" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1050" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1050" s="1">
+        <v>4</v>
+      </c>
       <c r="L1050" s="1"/>
       <c r="M1050" s="1"/>
       <c r="N1050" s="4" t="b">
@@ -56551,31 +56707,35 @@
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="7">
-        <v>103145</v>
+        <v>103308</v>
       </c>
       <c r="B1051" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1051" s="2">
         <f>VLOOKUP(B1051,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1051" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1051" s="2">
         <f>VLOOKUP(D1051,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1051" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1051" s="2">
         <f>VLOOKUP(F1051,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1051" s="1"/>
-      <c r="I1051" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1051" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I1051" s="1">
+        <v>4</v>
+      </c>
       <c r="J1051" s="1"/>
       <c r="K1051" s="1"/>
       <c r="L1051" s="1"/>
@@ -56593,21 +56753,21 @@
     </row>
     <row r="1052" spans="1:16">
       <c r="A1052" s="7">
-        <v>103146</v>
+        <v>103309</v>
       </c>
       <c r="B1052" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1052" s="2">
         <f>VLOOKUP(B1052,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1052" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1052" s="2">
         <f>VLOOKUP(D1052,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1052" s="1" t="s">
         <v>3</v>
@@ -56616,10 +56776,18 @@
         <f>VLOOKUP(F1052,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1052" s="1"/>
-      <c r="I1052" s="1"/>
-      <c r="J1052" s="1"/>
-      <c r="K1052" s="1"/>
+      <c r="H1052" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I1052" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1052" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1052" s="1">
+        <v>5</v>
+      </c>
       <c r="L1052" s="1"/>
       <c r="M1052" s="1"/>
       <c r="N1052" s="4" t="b">
@@ -56635,21 +56803,21 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="7">
-        <v>103147</v>
+        <v>103310</v>
       </c>
       <c r="B1053" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1053" s="2">
         <f>VLOOKUP(B1053,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1053" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1053" s="2">
         <f>VLOOKUP(D1053,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1053" s="1" t="s">
         <v>3</v>
@@ -56658,10 +56826,18 @@
         <f>VLOOKUP(F1053,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1053" s="1"/>
-      <c r="I1053" s="1"/>
-      <c r="J1053" s="1"/>
-      <c r="K1053" s="1"/>
+      <c r="H1053" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I1053" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1053" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1053" s="1">
+        <v>3</v>
+      </c>
       <c r="L1053" s="1"/>
       <c r="M1053" s="1"/>
       <c r="N1053" s="4" t="b">
@@ -56677,31 +56853,35 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="7">
-        <v>103148</v>
+        <v>103311</v>
       </c>
       <c r="B1054" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1054" s="2">
         <f>VLOOKUP(B1054,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1054" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1054" s="2">
         <f>VLOOKUP(D1054,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1054" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1054" s="2">
         <f>VLOOKUP(F1054,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1054" s="1"/>
-      <c r="I1054" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1054" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I1054" s="1">
+        <v>3</v>
+      </c>
       <c r="J1054" s="1"/>
       <c r="K1054" s="1"/>
       <c r="L1054" s="1"/>
@@ -56719,21 +56899,21 @@
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="7">
-        <v>103149</v>
+        <v>103312</v>
       </c>
       <c r="B1055" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1055" s="2">
         <f>VLOOKUP(B1055,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1055" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E1055" s="2">
         <f>VLOOKUP(D1055,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1055" s="1" t="s">
         <v>3</v>
@@ -56742,10 +56922,18 @@
         <f>VLOOKUP(F1055,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1055" s="1"/>
-      <c r="I1055" s="1"/>
-      <c r="J1055" s="1"/>
-      <c r="K1055" s="1"/>
+      <c r="H1055" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I1055" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1055" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1055" s="1">
+        <v>5</v>
+      </c>
       <c r="L1055" s="1"/>
       <c r="M1055" s="1"/>
       <c r="N1055" s="4" t="b">
@@ -56761,17 +56949,17 @@
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="7">
-        <v>103150</v>
+        <v>103400</v>
       </c>
       <c r="B1056" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1056" s="2">
         <f>VLOOKUP(B1056,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1056" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1056" s="2">
         <f>VLOOKUP(D1056,Select!B:H,7,FALSE)</f>
@@ -56784,10 +56972,18 @@
         <f>VLOOKUP(F1056,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1056" s="1"/>
-      <c r="I1056" s="1"/>
-      <c r="J1056" s="1"/>
-      <c r="K1056" s="1"/>
+      <c r="H1056" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I1056" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1056" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1056" s="1">
+        <v>2</v>
+      </c>
       <c r="L1056" s="1"/>
       <c r="M1056" s="1"/>
       <c r="N1056" s="4" t="b">
@@ -56803,14 +56999,14 @@
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="7">
-        <v>103151</v>
+        <v>103401</v>
       </c>
       <c r="B1057" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1057" s="2">
         <f>VLOOKUP(B1057,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1057" s="1" t="s">
         <v>11</v>
@@ -56826,10 +57022,18 @@
         <f>VLOOKUP(F1057,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1057" s="1"/>
-      <c r="I1057" s="1"/>
-      <c r="J1057" s="1"/>
-      <c r="K1057" s="1"/>
+      <c r="H1057" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="I1057" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1057" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1057" s="1">
+        <v>1</v>
+      </c>
       <c r="L1057" s="1"/>
       <c r="M1057" s="1"/>
       <c r="N1057" s="4" t="b">
@@ -56845,14 +57049,14 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="7">
-        <v>103152</v>
+        <v>103402</v>
       </c>
       <c r="B1058" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1058" s="2">
         <f>VLOOKUP(B1058,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1058" s="1" t="s">
         <v>11</v>
@@ -56868,10 +57072,18 @@
         <f>VLOOKUP(F1058,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1058" s="1"/>
-      <c r="I1058" s="1"/>
-      <c r="J1058" s="1"/>
-      <c r="K1058" s="1"/>
+      <c r="H1058" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I1058" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1058" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1058" s="1">
+        <v>3</v>
+      </c>
       <c r="L1058" s="1"/>
       <c r="M1058" s="1"/>
       <c r="N1058" s="4" t="b">
@@ -56887,14 +57099,14 @@
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="7">
-        <v>103153</v>
+        <v>103403</v>
       </c>
       <c r="B1059" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1059" s="2">
         <f>VLOOKUP(B1059,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1059" s="1" t="s">
         <v>11</v>
@@ -56910,10 +57122,18 @@
         <f>VLOOKUP(F1059,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1059" s="1"/>
-      <c r="I1059" s="1"/>
-      <c r="J1059" s="1"/>
-      <c r="K1059" s="1"/>
+      <c r="H1059" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I1059" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1059" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1059" s="1">
+        <v>5</v>
+      </c>
       <c r="L1059" s="1"/>
       <c r="M1059" s="1"/>
       <c r="N1059" s="4" t="b">
@@ -56929,14 +57149,14 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="7">
-        <v>103154</v>
+        <v>103404</v>
       </c>
       <c r="B1060" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1060" s="2">
         <f>VLOOKUP(B1060,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1060" s="1" t="s">
         <v>11</v>
@@ -56946,14 +57166,18 @@
         <v>0</v>
       </c>
       <c r="F1060" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G1060" s="2">
         <f>VLOOKUP(F1060,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1060" s="1"/>
-      <c r="I1060" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1060" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I1060" s="1">
+        <v>5</v>
+      </c>
       <c r="J1060" s="1"/>
       <c r="K1060" s="1"/>
       <c r="L1060" s="1"/>
@@ -56971,21 +57195,21 @@
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="7">
-        <v>103155</v>
+        <v>103405</v>
       </c>
       <c r="B1061" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1061" s="2">
         <f>VLOOKUP(B1061,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1061" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1061" s="2">
         <f>VLOOKUP(D1061,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1061" s="1" t="s">
         <v>3</v>
@@ -56994,10 +57218,18 @@
         <f>VLOOKUP(F1061,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1061" s="1"/>
-      <c r="I1061" s="1"/>
-      <c r="J1061" s="1"/>
-      <c r="K1061" s="1"/>
+      <c r="H1061" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I1061" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1061" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1061" s="1">
+        <v>1</v>
+      </c>
       <c r="L1061" s="1"/>
       <c r="M1061" s="1"/>
       <c r="N1061" s="4" t="b">
@@ -57013,21 +57245,21 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="7">
-        <v>103156</v>
+        <v>103406</v>
       </c>
       <c r="B1062" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1062" s="2">
         <f>VLOOKUP(B1062,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1062" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1062" s="2">
         <f>VLOOKUP(D1062,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1062" s="1" t="s">
         <v>3</v>
@@ -57036,10 +57268,18 @@
         <f>VLOOKUP(F1062,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1062" s="1"/>
-      <c r="I1062" s="1"/>
-      <c r="J1062" s="1"/>
-      <c r="K1062" s="1"/>
+      <c r="H1062" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I1062" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1062" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1062" s="1">
+        <v>4</v>
+      </c>
       <c r="L1062" s="1"/>
       <c r="M1062" s="1"/>
       <c r="N1062" s="4" t="b">
@@ -57055,21 +57295,21 @@
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="7">
-        <v>103157</v>
+        <v>103407</v>
       </c>
       <c r="B1063" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1063" s="2">
         <f>VLOOKUP(B1063,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1063" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1063" s="2">
         <f>VLOOKUP(D1063,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1063" s="1" t="s">
         <v>3</v>
@@ -57078,10 +57318,18 @@
         <f>VLOOKUP(F1063,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1063" s="1"/>
-      <c r="I1063" s="1"/>
-      <c r="J1063" s="1"/>
-      <c r="K1063" s="1"/>
+      <c r="H1063" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I1063" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1063" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1063" s="1">
+        <v>6</v>
+      </c>
       <c r="L1063" s="1"/>
       <c r="M1063" s="1"/>
       <c r="N1063" s="4" t="b">
@@ -57097,31 +57345,35 @@
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="7">
-        <v>103158</v>
+        <v>103408</v>
       </c>
       <c r="B1064" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1064" s="2">
         <f>VLOOKUP(B1064,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1064" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1064" s="2">
         <f>VLOOKUP(D1064,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1064" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1064" s="2">
         <f>VLOOKUP(F1064,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1064" s="1"/>
-      <c r="I1064" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1064" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I1064" s="1">
+        <v>5</v>
+      </c>
       <c r="J1064" s="1"/>
       <c r="K1064" s="1"/>
       <c r="L1064" s="1"/>
@@ -57139,21 +57391,21 @@
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="7">
-        <v>103159</v>
+        <v>103409</v>
       </c>
       <c r="B1065" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1065" s="2">
         <f>VLOOKUP(B1065,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1065" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1065" s="2">
         <f>VLOOKUP(D1065,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1065" s="1" t="s">
         <v>3</v>
@@ -57162,10 +57414,18 @@
         <f>VLOOKUP(F1065,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1065" s="1"/>
-      <c r="I1065" s="1"/>
-      <c r="J1065" s="1"/>
-      <c r="K1065" s="1"/>
+      <c r="H1065" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I1065" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1065" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1065" s="1">
+        <v>2</v>
+      </c>
       <c r="L1065" s="1"/>
       <c r="M1065" s="1"/>
       <c r="N1065" s="4" t="b">
@@ -57181,21 +57441,21 @@
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="7">
-        <v>103160</v>
+        <v>103410</v>
       </c>
       <c r="B1066" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1066" s="2">
         <f>VLOOKUP(B1066,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1066" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1066" s="2">
         <f>VLOOKUP(D1066,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1066" s="1" t="s">
         <v>3</v>
@@ -57204,10 +57464,18 @@
         <f>VLOOKUP(F1066,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1066" s="1"/>
-      <c r="I1066" s="1"/>
-      <c r="J1066" s="1"/>
-      <c r="K1066" s="1"/>
+      <c r="H1066" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I1066" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1066" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1066" s="1">
+        <v>3</v>
+      </c>
       <c r="L1066" s="1"/>
       <c r="M1066" s="1"/>
       <c r="N1066" s="4" t="b">
@@ -57223,31 +57491,35 @@
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="7">
-        <v>103161</v>
+        <v>103411</v>
       </c>
       <c r="B1067" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1067" s="2">
         <f>VLOOKUP(B1067,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1067" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1067" s="2">
         <f>VLOOKUP(D1067,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1067" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1067" s="2">
         <f>VLOOKUP(F1067,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1067" s="1"/>
-      <c r="I1067" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1067" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I1067" s="1">
+        <v>2</v>
+      </c>
       <c r="J1067" s="1"/>
       <c r="K1067" s="1"/>
       <c r="L1067" s="1"/>
@@ -57265,21 +57537,21 @@
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="7">
-        <v>103162</v>
+        <v>103412</v>
       </c>
       <c r="B1068" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1068" s="2">
         <f>VLOOKUP(B1068,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1068" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E1068" s="2">
         <f>VLOOKUP(D1068,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1068" s="1" t="s">
         <v>3</v>
@@ -57288,10 +57560,18 @@
         <f>VLOOKUP(F1068,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1068" s="1"/>
-      <c r="I1068" s="1"/>
-      <c r="J1068" s="1"/>
-      <c r="K1068" s="1"/>
+      <c r="H1068" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I1068" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1068" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1068" s="1">
+        <v>5</v>
+      </c>
       <c r="L1068" s="1"/>
       <c r="M1068" s="1"/>
       <c r="N1068" s="4" t="b">
@@ -57307,17 +57587,17 @@
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="7">
-        <v>103163</v>
+        <v>103500</v>
       </c>
       <c r="B1069" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1069" s="2">
         <f>VLOOKUP(B1069,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1069" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1069" s="2">
         <f>VLOOKUP(D1069,Select!B:H,7,FALSE)</f>
@@ -57330,10 +57610,18 @@
         <f>VLOOKUP(F1069,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1069" s="1"/>
-      <c r="I1069" s="1"/>
-      <c r="J1069" s="1"/>
-      <c r="K1069" s="1"/>
+      <c r="H1069" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I1069" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1069" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1069" s="1">
+        <v>2</v>
+      </c>
       <c r="L1069" s="1"/>
       <c r="M1069" s="1"/>
       <c r="N1069" s="4" t="b">
@@ -57349,14 +57637,14 @@
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="7">
-        <v>103164</v>
+        <v>103501</v>
       </c>
       <c r="B1070" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1070" s="2">
         <f>VLOOKUP(B1070,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1070" s="1" t="s">
         <v>11</v>
@@ -57372,10 +57660,18 @@
         <f>VLOOKUP(F1070,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1070" s="1"/>
-      <c r="I1070" s="1"/>
-      <c r="J1070" s="1"/>
-      <c r="K1070" s="1"/>
+      <c r="H1070" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I1070" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1070" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1070" s="1">
+        <v>2</v>
+      </c>
       <c r="L1070" s="1"/>
       <c r="M1070" s="1"/>
       <c r="N1070" s="4" t="b">
@@ -57391,14 +57687,14 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="7">
-        <v>103165</v>
+        <v>103502</v>
       </c>
       <c r="B1071" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1071" s="2">
         <f>VLOOKUP(B1071,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1071" s="1" t="s">
         <v>11</v>
@@ -57414,10 +57710,18 @@
         <f>VLOOKUP(F1071,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1071" s="1"/>
-      <c r="I1071" s="1"/>
-      <c r="J1071" s="1"/>
-      <c r="K1071" s="1"/>
+      <c r="H1071" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I1071" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1071" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1071" s="1">
+        <v>1</v>
+      </c>
       <c r="L1071" s="1"/>
       <c r="M1071" s="1"/>
       <c r="N1071" s="4" t="b">
@@ -57433,14 +57737,14 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="7">
-        <v>103166</v>
+        <v>103503</v>
       </c>
       <c r="B1072" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1072" s="2">
         <f>VLOOKUP(B1072,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1072" s="1" t="s">
         <v>11</v>
@@ -57456,10 +57760,18 @@
         <f>VLOOKUP(F1072,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1072" s="1"/>
-      <c r="I1072" s="1"/>
-      <c r="J1072" s="1"/>
-      <c r="K1072" s="1"/>
+      <c r="H1072" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I1072" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1072" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1072" s="1">
+        <v>2</v>
+      </c>
       <c r="L1072" s="1"/>
       <c r="M1072" s="1"/>
       <c r="N1072" s="4" t="b">
@@ -57475,14 +57787,14 @@
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="7">
-        <v>103167</v>
+        <v>103504</v>
       </c>
       <c r="B1073" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1073" s="2">
         <f>VLOOKUP(B1073,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1073" s="1" t="s">
         <v>11</v>
@@ -57492,14 +57804,18 @@
         <v>0</v>
       </c>
       <c r="F1073" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1073" s="2">
         <f>VLOOKUP(F1073,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1073" s="1"/>
-      <c r="I1073" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1073" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I1073" s="1">
+        <v>3</v>
+      </c>
       <c r="J1073" s="1"/>
       <c r="K1073" s="1"/>
       <c r="L1073" s="1"/>
@@ -57517,21 +57833,21 @@
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="7">
-        <v>103168</v>
+        <v>103505</v>
       </c>
       <c r="B1074" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1074" s="2">
         <f>VLOOKUP(B1074,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1074" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1074" s="2">
         <f>VLOOKUP(D1074,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1074" s="1" t="s">
         <v>3</v>
@@ -57540,10 +57856,18 @@
         <f>VLOOKUP(F1074,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1074" s="1"/>
-      <c r="I1074" s="1"/>
-      <c r="J1074" s="1"/>
-      <c r="K1074" s="1"/>
+      <c r="H1074" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="I1074" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1074" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1074" s="1">
+        <v>2</v>
+      </c>
       <c r="L1074" s="1"/>
       <c r="M1074" s="1"/>
       <c r="N1074" s="4" t="b">
@@ -57559,21 +57883,21 @@
     </row>
     <row r="1075" spans="1:16">
       <c r="A1075" s="7">
-        <v>103169</v>
+        <v>103506</v>
       </c>
       <c r="B1075" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1075" s="2">
         <f>VLOOKUP(B1075,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1075" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1075" s="2">
         <f>VLOOKUP(D1075,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1075" s="1" t="s">
         <v>3</v>
@@ -57582,10 +57906,18 @@
         <f>VLOOKUP(F1075,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1075" s="1"/>
-      <c r="I1075" s="1"/>
-      <c r="J1075" s="1"/>
-      <c r="K1075" s="1"/>
+      <c r="H1075" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I1075" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1075" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1075" s="1">
+        <v>3</v>
+      </c>
       <c r="L1075" s="1"/>
       <c r="M1075" s="1"/>
       <c r="N1075" s="4" t="b">
@@ -57601,21 +57933,21 @@
     </row>
     <row r="1076" spans="1:16">
       <c r="A1076" s="7">
-        <v>103170</v>
+        <v>103507</v>
       </c>
       <c r="B1076" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1076" s="2">
         <f>VLOOKUP(B1076,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1076" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1076" s="2">
         <f>VLOOKUP(D1076,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1076" s="1" t="s">
         <v>3</v>
@@ -57624,10 +57956,18 @@
         <f>VLOOKUP(F1076,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1076" s="1"/>
-      <c r="I1076" s="1"/>
-      <c r="J1076" s="1"/>
-      <c r="K1076" s="1"/>
+      <c r="H1076" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I1076" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1076" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1076" s="1">
+        <v>5</v>
+      </c>
       <c r="L1076" s="1"/>
       <c r="M1076" s="1"/>
       <c r="N1076" s="4" t="b">
@@ -57643,31 +57983,35 @@
     </row>
     <row r="1077" spans="1:16">
       <c r="A1077" s="7">
-        <v>103171</v>
+        <v>103508</v>
       </c>
       <c r="B1077" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1077" s="2">
         <f>VLOOKUP(B1077,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1077" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1077" s="2">
         <f>VLOOKUP(D1077,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1077" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1077" s="2">
         <f>VLOOKUP(F1077,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1077" s="1"/>
-      <c r="I1077" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1077" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I1077" s="1">
+        <v>1</v>
+      </c>
       <c r="J1077" s="1"/>
       <c r="K1077" s="1"/>
       <c r="L1077" s="1"/>
@@ -57685,21 +58029,21 @@
     </row>
     <row r="1078" spans="1:16">
       <c r="A1078" s="7">
-        <v>103172</v>
+        <v>103509</v>
       </c>
       <c r="B1078" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1078" s="2">
         <f>VLOOKUP(B1078,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1078" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1078" s="2">
         <f>VLOOKUP(D1078,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1078" s="1" t="s">
         <v>3</v>
@@ -57708,10 +58052,18 @@
         <f>VLOOKUP(F1078,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1078" s="1"/>
-      <c r="I1078" s="1"/>
-      <c r="J1078" s="1"/>
-      <c r="K1078" s="1"/>
+      <c r="H1078" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I1078" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1078" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1078" s="1">
+        <v>1</v>
+      </c>
       <c r="L1078" s="1"/>
       <c r="M1078" s="1"/>
       <c r="N1078" s="4" t="b">
@@ -57727,21 +58079,21 @@
     </row>
     <row r="1079" spans="1:16">
       <c r="A1079" s="7">
-        <v>103173</v>
+        <v>103510</v>
       </c>
       <c r="B1079" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1079" s="2">
         <f>VLOOKUP(B1079,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1079" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1079" s="2">
         <f>VLOOKUP(D1079,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1079" s="1" t="s">
         <v>3</v>
@@ -57750,10 +58102,18 @@
         <f>VLOOKUP(F1079,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1079" s="1"/>
-      <c r="I1079" s="1"/>
-      <c r="J1079" s="1"/>
-      <c r="K1079" s="1"/>
+      <c r="H1079" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I1079" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1079" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1079" s="1">
+        <v>6</v>
+      </c>
       <c r="L1079" s="1"/>
       <c r="M1079" s="1"/>
       <c r="N1079" s="4" t="b">
@@ -57769,31 +58129,35 @@
     </row>
     <row r="1080" spans="1:16">
       <c r="A1080" s="7">
-        <v>103174</v>
+        <v>103511</v>
       </c>
       <c r="B1080" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1080" s="2">
         <f>VLOOKUP(B1080,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1080" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1080" s="2">
         <f>VLOOKUP(D1080,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1080" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1080" s="2">
         <f>VLOOKUP(F1080,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1080" s="1"/>
-      <c r="I1080" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1080" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I1080" s="1">
+        <v>3</v>
+      </c>
       <c r="J1080" s="1"/>
       <c r="K1080" s="1"/>
       <c r="L1080" s="1"/>
@@ -57811,21 +58175,21 @@
     </row>
     <row r="1081" spans="1:16">
       <c r="A1081" s="7">
-        <v>103175</v>
+        <v>103512</v>
       </c>
       <c r="B1081" s="1" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="C1081" s="2">
         <f>VLOOKUP(B1081,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D1081" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E1081" s="2">
         <f>VLOOKUP(D1081,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1081" s="1" t="s">
         <v>3</v>
@@ -57834,10 +58198,18 @@
         <f>VLOOKUP(F1081,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1081" s="1"/>
-      <c r="I1081" s="1"/>
-      <c r="J1081" s="1"/>
-      <c r="K1081" s="1"/>
+      <c r="H1081" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I1081" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1081" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1081" s="1">
+        <v>5</v>
+      </c>
       <c r="L1081" s="1"/>
       <c r="M1081" s="1"/>
       <c r="N1081" s="4" t="b">
@@ -57853,17 +58225,17 @@
     </row>
     <row r="1082" spans="1:16">
       <c r="A1082" s="7">
-        <v>103176</v>
+        <v>103600</v>
       </c>
       <c r="B1082" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1082" s="2">
         <f>VLOOKUP(B1082,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1082" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1082" s="2">
         <f>VLOOKUP(D1082,Select!B:H,7,FALSE)</f>
@@ -57876,10 +58248,18 @@
         <f>VLOOKUP(F1082,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1082" s="1"/>
-      <c r="I1082" s="1"/>
-      <c r="J1082" s="1"/>
-      <c r="K1082" s="1"/>
+      <c r="H1082" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I1082" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1082" s="1">
+        <v>3</v>
+      </c>
       <c r="L1082" s="1"/>
       <c r="M1082" s="1"/>
       <c r="N1082" s="4" t="b">
@@ -57895,14 +58275,14 @@
     </row>
     <row r="1083" spans="1:16">
       <c r="A1083" s="7">
-        <v>103177</v>
+        <v>103601</v>
       </c>
       <c r="B1083" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1083" s="2">
         <f>VLOOKUP(B1083,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1083" s="1" t="s">
         <v>11</v>
@@ -57918,10 +58298,18 @@
         <f>VLOOKUP(F1083,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1083" s="1"/>
-      <c r="I1083" s="1"/>
-      <c r="J1083" s="1"/>
-      <c r="K1083" s="1"/>
+      <c r="H1083" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I1083" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1083" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1083" s="1">
+        <v>2</v>
+      </c>
       <c r="L1083" s="1"/>
       <c r="M1083" s="1"/>
       <c r="N1083" s="4" t="b">
@@ -57937,14 +58325,14 @@
     </row>
     <row r="1084" spans="1:16">
       <c r="A1084" s="7">
-        <v>103178</v>
+        <v>103602</v>
       </c>
       <c r="B1084" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1084" s="2">
         <f>VLOOKUP(B1084,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1084" s="1" t="s">
         <v>11</v>
@@ -57960,10 +58348,18 @@
         <f>VLOOKUP(F1084,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1084" s="1"/>
-      <c r="I1084" s="1"/>
-      <c r="J1084" s="1"/>
-      <c r="K1084" s="1"/>
+      <c r="H1084" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I1084" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1084" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1084" s="1">
+        <v>3</v>
+      </c>
       <c r="L1084" s="1"/>
       <c r="M1084" s="1"/>
       <c r="N1084" s="4" t="b">
@@ -57979,14 +58375,14 @@
     </row>
     <row r="1085" spans="1:16">
       <c r="A1085" s="7">
-        <v>103179</v>
+        <v>103603</v>
       </c>
       <c r="B1085" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1085" s="2">
         <f>VLOOKUP(B1085,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1085" s="1" t="s">
         <v>11</v>
@@ -58002,10 +58398,18 @@
         <f>VLOOKUP(F1085,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1085" s="1"/>
-      <c r="I1085" s="1"/>
-      <c r="J1085" s="1"/>
-      <c r="K1085" s="1"/>
+      <c r="H1085" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I1085" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1085" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1085" s="1">
+        <v>7</v>
+      </c>
       <c r="L1085" s="1"/>
       <c r="M1085" s="1"/>
       <c r="N1085" s="4" t="b">
@@ -58021,14 +58425,14 @@
     </row>
     <row r="1086" spans="1:16">
       <c r="A1086" s="7">
-        <v>103180</v>
+        <v>103604</v>
       </c>
       <c r="B1086" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1086" s="2">
         <f>VLOOKUP(B1086,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1086" s="1" t="s">
         <v>11</v>
@@ -58038,14 +58442,18 @@
         <v>0</v>
       </c>
       <c r="F1086" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1086" s="2">
         <f>VLOOKUP(F1086,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1086" s="1"/>
-      <c r="I1086" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1086" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="I1086" s="1">
+        <v>1</v>
+      </c>
       <c r="J1086" s="1"/>
       <c r="K1086" s="1"/>
       <c r="L1086" s="1"/>
@@ -58063,21 +58471,21 @@
     </row>
     <row r="1087" spans="1:16">
       <c r="A1087" s="7">
-        <v>103181</v>
+        <v>103605</v>
       </c>
       <c r="B1087" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1087" s="2">
         <f>VLOOKUP(B1087,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1087" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1087" s="2">
         <f>VLOOKUP(D1087,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1087" s="1" t="s">
         <v>3</v>
@@ -58086,10 +58494,18 @@
         <f>VLOOKUP(F1087,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1087" s="1"/>
-      <c r="I1087" s="1"/>
-      <c r="J1087" s="1"/>
-      <c r="K1087" s="1"/>
+      <c r="H1087" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I1087" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1087" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1087" s="1">
+        <v>2</v>
+      </c>
       <c r="L1087" s="1"/>
       <c r="M1087" s="1"/>
       <c r="N1087" s="4" t="b">
@@ -58105,21 +58521,21 @@
     </row>
     <row r="1088" spans="1:16">
       <c r="A1088" s="7">
-        <v>103182</v>
+        <v>103606</v>
       </c>
       <c r="B1088" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1088" s="2">
         <f>VLOOKUP(B1088,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1088" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1088" s="2">
         <f>VLOOKUP(D1088,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1088" s="1" t="s">
         <v>3</v>
@@ -58128,10 +58544,18 @@
         <f>VLOOKUP(F1088,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1088" s="1"/>
-      <c r="I1088" s="1"/>
-      <c r="J1088" s="1"/>
-      <c r="K1088" s="1"/>
+      <c r="H1088" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I1088" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1088" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1088" s="1">
+        <v>5</v>
+      </c>
       <c r="L1088" s="1"/>
       <c r="M1088" s="1"/>
       <c r="N1088" s="4" t="b">
@@ -58147,21 +58571,21 @@
     </row>
     <row r="1089" spans="1:16">
       <c r="A1089" s="7">
-        <v>103183</v>
+        <v>103607</v>
       </c>
       <c r="B1089" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1089" s="2">
         <f>VLOOKUP(B1089,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1089" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1089" s="2">
         <f>VLOOKUP(D1089,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1089" s="1" t="s">
         <v>3</v>
@@ -58170,10 +58594,18 @@
         <f>VLOOKUP(F1089,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1089" s="1"/>
-      <c r="I1089" s="1"/>
-      <c r="J1089" s="1"/>
-      <c r="K1089" s="1"/>
+      <c r="H1089" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="I1089" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1089" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1089" s="1">
+        <v>6</v>
+      </c>
       <c r="L1089" s="1"/>
       <c r="M1089" s="1"/>
       <c r="N1089" s="4" t="b">
@@ -58189,31 +58621,35 @@
     </row>
     <row r="1090" spans="1:16">
       <c r="A1090" s="7">
-        <v>103184</v>
+        <v>103608</v>
       </c>
       <c r="B1090" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1090" s="2">
         <f>VLOOKUP(B1090,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1090" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1090" s="2">
         <f>VLOOKUP(D1090,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1090" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1090" s="2">
         <f>VLOOKUP(F1090,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1090" s="1"/>
-      <c r="I1090" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1090" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I1090" s="1">
+        <v>2</v>
+      </c>
       <c r="J1090" s="1"/>
       <c r="K1090" s="1"/>
       <c r="L1090" s="1"/>
@@ -58231,21 +58667,21 @@
     </row>
     <row r="1091" spans="1:16">
       <c r="A1091" s="7">
-        <v>103185</v>
+        <v>103609</v>
       </c>
       <c r="B1091" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1091" s="2">
         <f>VLOOKUP(B1091,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1091" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1091" s="2">
         <f>VLOOKUP(D1091,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1091" s="1" t="s">
         <v>3</v>
@@ -58254,10 +58690,18 @@
         <f>VLOOKUP(F1091,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1091" s="1"/>
-      <c r="I1091" s="1"/>
-      <c r="J1091" s="1"/>
-      <c r="K1091" s="1"/>
+      <c r="H1091" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I1091" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1091" s="1">
+        <v>6</v>
+      </c>
+      <c r="K1091" s="1">
+        <v>6</v>
+      </c>
       <c r="L1091" s="1"/>
       <c r="M1091" s="1"/>
       <c r="N1091" s="4" t="b">
@@ -58273,21 +58717,21 @@
     </row>
     <row r="1092" spans="1:16">
       <c r="A1092" s="7">
-        <v>103186</v>
+        <v>103610</v>
       </c>
       <c r="B1092" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1092" s="2">
         <f>VLOOKUP(B1092,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1092" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1092" s="2">
         <f>VLOOKUP(D1092,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1092" s="1" t="s">
         <v>3</v>
@@ -58296,10 +58740,18 @@
         <f>VLOOKUP(F1092,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1092" s="1"/>
-      <c r="I1092" s="1"/>
-      <c r="J1092" s="1"/>
-      <c r="K1092" s="1"/>
+      <c r="H1092" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="I1092" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1092" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1092" s="1">
+        <v>7</v>
+      </c>
       <c r="L1092" s="1"/>
       <c r="M1092" s="1"/>
       <c r="N1092" s="4" t="b">
@@ -58315,31 +58767,35 @@
     </row>
     <row r="1093" spans="1:16">
       <c r="A1093" s="7">
-        <v>103187</v>
+        <v>103611</v>
       </c>
       <c r="B1093" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1093" s="2">
         <f>VLOOKUP(B1093,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1093" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1093" s="2">
         <f>VLOOKUP(D1093,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1093" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1093" s="2">
         <f>VLOOKUP(F1093,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1093" s="1"/>
-      <c r="I1093" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1093" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I1093" s="1">
+        <v>3</v>
+      </c>
       <c r="J1093" s="1"/>
       <c r="K1093" s="1"/>
       <c r="L1093" s="1"/>
@@ -58357,21 +58813,21 @@
     </row>
     <row r="1094" spans="1:16">
       <c r="A1094" s="7">
-        <v>103188</v>
+        <v>103612</v>
       </c>
       <c r="B1094" s="1" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C1094" s="2">
         <f>VLOOKUP(B1094,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D1094" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E1094" s="2">
         <f>VLOOKUP(D1094,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1094" s="1" t="s">
         <v>3</v>
@@ -58380,10 +58836,18 @@
         <f>VLOOKUP(F1094,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1094" s="1"/>
-      <c r="I1094" s="1"/>
-      <c r="J1094" s="1"/>
-      <c r="K1094" s="1"/>
+      <c r="H1094" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I1094" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1094" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1094" s="1">
+        <v>5</v>
+      </c>
       <c r="L1094" s="1"/>
       <c r="M1094" s="1"/>
       <c r="N1094" s="4" t="b">
@@ -58399,17 +58863,17 @@
     </row>
     <row r="1095" spans="1:16">
       <c r="A1095" s="7">
-        <v>103189</v>
+        <v>103700</v>
       </c>
       <c r="B1095" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1095" s="2">
         <f>VLOOKUP(B1095,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1095" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1095" s="2">
         <f>VLOOKUP(D1095,Select!B:H,7,FALSE)</f>
@@ -58422,10 +58886,18 @@
         <f>VLOOKUP(F1095,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1095" s="1"/>
-      <c r="I1095" s="1"/>
-      <c r="J1095" s="1"/>
-      <c r="K1095" s="1"/>
+      <c r="H1095" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I1095" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1095" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1095" s="1">
+        <v>2</v>
+      </c>
       <c r="L1095" s="1"/>
       <c r="M1095" s="1"/>
       <c r="N1095" s="4" t="b">
@@ -58441,14 +58913,14 @@
     </row>
     <row r="1096" spans="1:16">
       <c r="A1096" s="7">
-        <v>103190</v>
+        <v>103701</v>
       </c>
       <c r="B1096" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1096" s="2">
         <f>VLOOKUP(B1096,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1096" s="1" t="s">
         <v>11</v>
@@ -58464,10 +58936,18 @@
         <f>VLOOKUP(F1096,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1096" s="1"/>
-      <c r="I1096" s="1"/>
-      <c r="J1096" s="1"/>
-      <c r="K1096" s="1"/>
+      <c r="H1096" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I1096" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1096" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1096" s="1">
+        <v>2</v>
+      </c>
       <c r="L1096" s="1"/>
       <c r="M1096" s="1"/>
       <c r="N1096" s="4" t="b">
@@ -58483,14 +58963,14 @@
     </row>
     <row r="1097" spans="1:16">
       <c r="A1097" s="7">
-        <v>103191</v>
+        <v>103702</v>
       </c>
       <c r="B1097" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1097" s="2">
         <f>VLOOKUP(B1097,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1097" s="1" t="s">
         <v>11</v>
@@ -58506,10 +58986,18 @@
         <f>VLOOKUP(F1097,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1097" s="1"/>
-      <c r="I1097" s="1"/>
-      <c r="J1097" s="1"/>
-      <c r="K1097" s="1"/>
+      <c r="H1097" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="I1097" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1097" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1097" s="1">
+        <v>3</v>
+      </c>
       <c r="L1097" s="1"/>
       <c r="M1097" s="1"/>
       <c r="N1097" s="4" t="b">
@@ -58525,14 +59013,14 @@
     </row>
     <row r="1098" spans="1:16">
       <c r="A1098" s="7">
-        <v>103192</v>
+        <v>103703</v>
       </c>
       <c r="B1098" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1098" s="2">
         <f>VLOOKUP(B1098,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1098" s="1" t="s">
         <v>11</v>
@@ -58548,10 +59036,18 @@
         <f>VLOOKUP(F1098,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1098" s="1"/>
-      <c r="I1098" s="1"/>
-      <c r="J1098" s="1"/>
-      <c r="K1098" s="1"/>
+      <c r="H1098" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I1098" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1098" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1098" s="1">
+        <v>3</v>
+      </c>
       <c r="L1098" s="1"/>
       <c r="M1098" s="1"/>
       <c r="N1098" s="4" t="b">
@@ -58567,14 +59063,14 @@
     </row>
     <row r="1099" spans="1:16">
       <c r="A1099" s="7">
-        <v>103193</v>
+        <v>103704</v>
       </c>
       <c r="B1099" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1099" s="2">
         <f>VLOOKUP(B1099,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1099" s="1" t="s">
         <v>11</v>
@@ -58584,14 +59080,18 @@
         <v>0</v>
       </c>
       <c r="F1099" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1099" s="2">
         <f>VLOOKUP(F1099,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1099" s="1"/>
-      <c r="I1099" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="H1099" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I1099" s="1">
+        <v>7</v>
+      </c>
       <c r="J1099" s="1"/>
       <c r="K1099" s="1"/>
       <c r="L1099" s="1"/>
@@ -58609,21 +59109,21 @@
     </row>
     <row r="1100" spans="1:16">
       <c r="A1100" s="7">
-        <v>103194</v>
+        <v>103705</v>
       </c>
       <c r="B1100" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1100" s="2">
         <f>VLOOKUP(B1100,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1100" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1100" s="2">
         <f>VLOOKUP(D1100,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1100" s="1" t="s">
         <v>3</v>
@@ -58632,10 +59132,18 @@
         <f>VLOOKUP(F1100,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1100" s="1"/>
-      <c r="I1100" s="1"/>
-      <c r="J1100" s="1"/>
-      <c r="K1100" s="1"/>
+      <c r="H1100" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="I1100" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1100" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1100" s="1">
+        <v>2</v>
+      </c>
       <c r="L1100" s="1"/>
       <c r="M1100" s="1"/>
       <c r="N1100" s="4" t="b">
@@ -58651,21 +59159,21 @@
     </row>
     <row r="1101" spans="1:16">
       <c r="A1101" s="7">
-        <v>103195</v>
+        <v>103706</v>
       </c>
       <c r="B1101" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1101" s="2">
         <f>VLOOKUP(B1101,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1101" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1101" s="2">
         <f>VLOOKUP(D1101,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1101" s="1" t="s">
         <v>3</v>
@@ -58674,10 +59182,18 @@
         <f>VLOOKUP(F1101,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1101" s="1"/>
-      <c r="I1101" s="1"/>
-      <c r="J1101" s="1"/>
-      <c r="K1101" s="1"/>
+      <c r="H1101" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I1101" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1101" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1101" s="1">
+        <v>2</v>
+      </c>
       <c r="L1101" s="1"/>
       <c r="M1101" s="1"/>
       <c r="N1101" s="4" t="b">
@@ -58693,21 +59209,21 @@
     </row>
     <row r="1102" spans="1:16">
       <c r="A1102" s="7">
-        <v>103196</v>
+        <v>103707</v>
       </c>
       <c r="B1102" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1102" s="2">
         <f>VLOOKUP(B1102,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1102" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1102" s="2">
         <f>VLOOKUP(D1102,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1102" s="1" t="s">
         <v>3</v>
@@ -58716,10 +59232,18 @@
         <f>VLOOKUP(F1102,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1102" s="1"/>
-      <c r="I1102" s="1"/>
-      <c r="J1102" s="1"/>
-      <c r="K1102" s="1"/>
+      <c r="H1102" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I1102" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1102" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1102" s="1">
+        <v>5</v>
+      </c>
       <c r="L1102" s="1"/>
       <c r="M1102" s="1"/>
       <c r="N1102" s="4" t="b">
@@ -58735,31 +59259,35 @@
     </row>
     <row r="1103" spans="1:16">
       <c r="A1103" s="7">
-        <v>103197</v>
+        <v>103708</v>
       </c>
       <c r="B1103" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1103" s="2">
         <f>VLOOKUP(B1103,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1103" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E1103" s="2">
         <f>VLOOKUP(D1103,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1103" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G1103" s="2">
         <f>VLOOKUP(F1103,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1103" s="1"/>
-      <c r="I1103" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="H1103" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I1103" s="1">
+        <v>3</v>
+      </c>
       <c r="J1103" s="1"/>
       <c r="K1103" s="1"/>
       <c r="L1103" s="1"/>
@@ -58777,21 +59305,21 @@
     </row>
     <row r="1104" spans="1:16">
       <c r="A1104" s="7">
-        <v>103198</v>
+        <v>103709</v>
       </c>
       <c r="B1104" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1104" s="2">
         <f>VLOOKUP(B1104,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1104" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1104" s="2">
         <f>VLOOKUP(D1104,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1104" s="1" t="s">
         <v>3</v>
@@ -58800,10 +59328,18 @@
         <f>VLOOKUP(F1104,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1104" s="1"/>
-      <c r="I1104" s="1"/>
-      <c r="J1104" s="1"/>
-      <c r="K1104" s="1"/>
+      <c r="H1104" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I1104" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1104" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1104" s="1">
+        <v>3</v>
+      </c>
       <c r="L1104" s="1"/>
       <c r="M1104" s="1"/>
       <c r="N1104" s="4" t="b">
@@ -58819,21 +59355,21 @@
     </row>
     <row r="1105" spans="1:16">
       <c r="A1105" s="7">
-        <v>103199</v>
+        <v>103710</v>
       </c>
       <c r="B1105" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1105" s="2">
         <f>VLOOKUP(B1105,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1105" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1105" s="2">
         <f>VLOOKUP(D1105,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1105" s="1" t="s">
         <v>3</v>
@@ -58842,10 +59378,18 @@
         <f>VLOOKUP(F1105,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1105" s="1"/>
-      <c r="I1105" s="1"/>
-      <c r="J1105" s="1"/>
-      <c r="K1105" s="1"/>
+      <c r="H1105" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I1105" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1105" s="1">
+        <v>5</v>
+      </c>
       <c r="L1105" s="1"/>
       <c r="M1105" s="1"/>
       <c r="N1105" s="4" t="b">
@@ -58861,41 +59405,37 @@
     </row>
     <row r="1106" spans="1:16">
       <c r="A1106" s="7">
-        <v>103200</v>
+        <v>103711</v>
       </c>
       <c r="B1106" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1106" s="2">
         <f>VLOOKUP(B1106,Select!A:H,8,FALSE)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1106" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E1106" s="2">
         <f>VLOOKUP(D1106,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1106" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G1106" s="2">
         <f>VLOOKUP(F1106,Select!C:H,6,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1106" s="1" t="s">
-        <v>1096</v>
+        <v>1172</v>
       </c>
       <c r="I1106" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1106" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1106" s="1">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J1106" s="1"/>
+      <c r="K1106" s="1"/>
       <c r="L1106" s="1"/>
       <c r="M1106" s="1"/>
       <c r="N1106" s="4" t="b">
@@ -58911,21 +59451,21 @@
     </row>
     <row r="1107" spans="1:16">
       <c r="A1107" s="7">
-        <v>103200</v>
+        <v>103712</v>
       </c>
       <c r="B1107" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1107" s="2">
         <f>VLOOKUP(B1107,Select!A:H,8,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1107" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E1107" s="2">
         <f>VLOOKUP(D1107,Select!B:H,7,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1107" s="1" t="s">
         <v>3</v>
@@ -58934,10 +59474,18 @@
         <f>VLOOKUP(F1107,Select!C:H,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="H1107" s="1"/>
-      <c r="I1107" s="1"/>
-      <c r="J1107" s="1"/>
-      <c r="K1107" s="1"/>
+      <c r="H1107" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I1107" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1107" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1107" s="1">
+        <v>5</v>
+      </c>
       <c r="L1107" s="1"/>
       <c r="M1107" s="1"/>
       <c r="N1107" s="4" t="b">
@@ -58948,5212 +59496,6 @@
       </c>
       <c r="P1107" s="2">
         <f>VLOOKUP(O1107,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:16">
-      <c r="A1108" s="7">
-        <v>103201</v>
-      </c>
-      <c r="B1108" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1108" s="2">
-        <f>VLOOKUP(B1108,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1108" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1108" s="2">
-        <f>VLOOKUP(D1108,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1108" s="2">
-        <f>VLOOKUP(F1108,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1108" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="I1108" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1108" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1108" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1108" s="1"/>
-      <c r="M1108" s="1"/>
-      <c r="N1108" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1108" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1108" s="2">
-        <f>VLOOKUP(O1108,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1109" spans="1:16">
-      <c r="A1109" s="7">
-        <v>103201</v>
-      </c>
-      <c r="B1109" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1109" s="2">
-        <f>VLOOKUP(B1109,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1109" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1109" s="2">
-        <f>VLOOKUP(D1109,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1109" s="2">
-        <f>VLOOKUP(F1109,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1109" s="1"/>
-      <c r="I1109" s="1"/>
-      <c r="J1109" s="1"/>
-      <c r="K1109" s="1"/>
-      <c r="L1109" s="1"/>
-      <c r="M1109" s="1"/>
-      <c r="N1109" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1109" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1109" s="2">
-        <f>VLOOKUP(O1109,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1110" spans="1:16">
-      <c r="A1110" s="7">
-        <v>103202</v>
-      </c>
-      <c r="B1110" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1110" s="2">
-        <f>VLOOKUP(B1110,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1110" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1110" s="2">
-        <f>VLOOKUP(D1110,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1110" s="2">
-        <f>VLOOKUP(F1110,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1110" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="I1110" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1110" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1110" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1110" s="1"/>
-      <c r="M1110" s="1"/>
-      <c r="N1110" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1110" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1110" s="2">
-        <f>VLOOKUP(O1110,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1111" spans="1:16">
-      <c r="A1111" s="7">
-        <v>103202</v>
-      </c>
-      <c r="B1111" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1111" s="2">
-        <f>VLOOKUP(B1111,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1111" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1111" s="2">
-        <f>VLOOKUP(D1111,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1111" s="2">
-        <f>VLOOKUP(F1111,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1111" s="1"/>
-      <c r="I1111" s="1"/>
-      <c r="J1111" s="1"/>
-      <c r="K1111" s="1"/>
-      <c r="L1111" s="1"/>
-      <c r="M1111" s="1"/>
-      <c r="N1111" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1111" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1111" s="2">
-        <f>VLOOKUP(O1111,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:16">
-      <c r="A1112" s="7">
-        <v>103203</v>
-      </c>
-      <c r="B1112" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1112" s="2">
-        <f>VLOOKUP(B1112,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1112" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1112" s="2">
-        <f>VLOOKUP(D1112,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1112" s="2">
-        <f>VLOOKUP(F1112,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1112" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I1112" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1112" s="1">
-        <v>5</v>
-      </c>
-      <c r="K1112" s="1">
-        <v>6</v>
-      </c>
-      <c r="L1112" s="1"/>
-      <c r="M1112" s="1"/>
-      <c r="N1112" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1112" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1112" s="2">
-        <f>VLOOKUP(O1112,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:16">
-      <c r="A1113" s="7">
-        <v>103203</v>
-      </c>
-      <c r="B1113" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1113" s="2">
-        <f>VLOOKUP(B1113,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1113" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1113" s="2">
-        <f>VLOOKUP(D1113,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1113" s="2">
-        <f>VLOOKUP(F1113,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1113" s="1"/>
-      <c r="I1113" s="1"/>
-      <c r="J1113" s="1"/>
-      <c r="K1113" s="1"/>
-      <c r="L1113" s="1"/>
-      <c r="M1113" s="1"/>
-      <c r="N1113" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1113" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1113" s="2">
-        <f>VLOOKUP(O1113,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1114" spans="1:16">
-      <c r="A1114" s="7">
-        <v>103204</v>
-      </c>
-      <c r="B1114" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1114" s="2">
-        <f>VLOOKUP(B1114,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1114" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1114" s="2">
-        <f>VLOOKUP(D1114,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1114" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1114" s="2">
-        <f>VLOOKUP(F1114,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1114" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I1114" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1114" s="1"/>
-      <c r="K1114" s="1"/>
-      <c r="L1114" s="1"/>
-      <c r="M1114" s="1"/>
-      <c r="N1114" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1114" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1114" s="2">
-        <f>VLOOKUP(O1114,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1115" spans="1:16">
-      <c r="A1115" s="7">
-        <v>103204</v>
-      </c>
-      <c r="B1115" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1115" s="2">
-        <f>VLOOKUP(B1115,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1115" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1115" s="2">
-        <f>VLOOKUP(D1115,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1115" s="2">
-        <f>VLOOKUP(F1115,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1115" s="1"/>
-      <c r="I1115" s="1"/>
-      <c r="J1115" s="1"/>
-      <c r="K1115" s="1"/>
-      <c r="L1115" s="1"/>
-      <c r="M1115" s="1"/>
-      <c r="N1115" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1115" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1115" s="2">
-        <f>VLOOKUP(O1115,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1116" spans="1:16">
-      <c r="A1116" s="7">
-        <v>103205</v>
-      </c>
-      <c r="B1116" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1116" s="2">
-        <f>VLOOKUP(B1116,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1116" s="2">
-        <f>VLOOKUP(D1116,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1116" s="2">
-        <f>VLOOKUP(F1116,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1116" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="I1116" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1116" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1116" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1116" s="1"/>
-      <c r="M1116" s="1"/>
-      <c r="N1116" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1116" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1116" s="2">
-        <f>VLOOKUP(O1116,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1117" spans="1:16">
-      <c r="A1117" s="7">
-        <v>103205</v>
-      </c>
-      <c r="B1117" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1117" s="2">
-        <f>VLOOKUP(B1117,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1117" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1117" s="2">
-        <f>VLOOKUP(D1117,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1117" s="2">
-        <f>VLOOKUP(F1117,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1117" s="1"/>
-      <c r="I1117" s="1"/>
-      <c r="J1117" s="1"/>
-      <c r="K1117" s="1"/>
-      <c r="L1117" s="1"/>
-      <c r="M1117" s="1"/>
-      <c r="N1117" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1117" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1117" s="2">
-        <f>VLOOKUP(O1117,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1118" spans="1:16">
-      <c r="A1118" s="7">
-        <v>103206</v>
-      </c>
-      <c r="B1118" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1118" s="2">
-        <f>VLOOKUP(B1118,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1118" s="2">
-        <f>VLOOKUP(D1118,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1118" s="2">
-        <f>VLOOKUP(F1118,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1118" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="I1118" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1118" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1118" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1118" s="1"/>
-      <c r="M1118" s="1"/>
-      <c r="N1118" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1118" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1118" s="2">
-        <f>VLOOKUP(O1118,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1119" spans="1:16">
-      <c r="A1119" s="7">
-        <v>103206</v>
-      </c>
-      <c r="B1119" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1119" s="2">
-        <f>VLOOKUP(B1119,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1119" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1119" s="2">
-        <f>VLOOKUP(D1119,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1119" s="2">
-        <f>VLOOKUP(F1119,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1119" s="1"/>
-      <c r="I1119" s="1"/>
-      <c r="J1119" s="1"/>
-      <c r="K1119" s="1"/>
-      <c r="L1119" s="1"/>
-      <c r="M1119" s="1"/>
-      <c r="N1119" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1119" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1119" s="2">
-        <f>VLOOKUP(O1119,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1120" spans="1:16">
-      <c r="A1120" s="7">
-        <v>103207</v>
-      </c>
-      <c r="B1120" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1120" s="2">
-        <f>VLOOKUP(B1120,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1120" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1120" s="2">
-        <f>VLOOKUP(D1120,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1120" s="2">
-        <f>VLOOKUP(F1120,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1120" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="I1120" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1120" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1120" s="1">
-        <v>4</v>
-      </c>
-      <c r="L1120" s="1"/>
-      <c r="M1120" s="1"/>
-      <c r="N1120" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1120" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1120" s="2">
-        <f>VLOOKUP(O1120,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1121" spans="1:16">
-      <c r="A1121" s="7">
-        <v>103207</v>
-      </c>
-      <c r="B1121" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1121" s="2">
-        <f>VLOOKUP(B1121,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1121" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1121" s="2">
-        <f>VLOOKUP(D1121,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1121" s="2">
-        <f>VLOOKUP(F1121,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1121" s="1"/>
-      <c r="I1121" s="1"/>
-      <c r="J1121" s="1"/>
-      <c r="K1121" s="1"/>
-      <c r="L1121" s="1"/>
-      <c r="M1121" s="1"/>
-      <c r="N1121" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1121" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1121" s="2">
-        <f>VLOOKUP(O1121,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1122" spans="1:16">
-      <c r="A1122" s="7">
-        <v>103208</v>
-      </c>
-      <c r="B1122" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1122" s="2">
-        <f>VLOOKUP(B1122,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1122" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1122" s="2">
-        <f>VLOOKUP(D1122,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1122" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1122" s="2">
-        <f>VLOOKUP(F1122,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1122" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I1122" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1122" s="1"/>
-      <c r="K1122" s="1"/>
-      <c r="L1122" s="1"/>
-      <c r="M1122" s="1"/>
-      <c r="N1122" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1122" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1122" s="2">
-        <f>VLOOKUP(O1122,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1123" spans="1:16">
-      <c r="A1123" s="7">
-        <v>103209</v>
-      </c>
-      <c r="B1123" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1123" s="2">
-        <f>VLOOKUP(B1123,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1123" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1123" s="2">
-        <f>VLOOKUP(D1123,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1123" s="2">
-        <f>VLOOKUP(F1123,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1123" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="I1123" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1123" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1123" s="1">
-        <v>4</v>
-      </c>
-      <c r="L1123" s="1"/>
-      <c r="M1123" s="1"/>
-      <c r="N1123" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1123" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1123" s="2">
-        <f>VLOOKUP(O1123,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1124" spans="1:16">
-      <c r="A1124" s="7">
-        <v>103210</v>
-      </c>
-      <c r="B1124" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1124" s="2">
-        <f>VLOOKUP(B1124,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1124" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1124" s="2">
-        <f>VLOOKUP(D1124,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1124" s="2">
-        <f>VLOOKUP(F1124,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1124" s="1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="I1124" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1124" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1124" s="1">
-        <v>8</v>
-      </c>
-      <c r="L1124" s="1"/>
-      <c r="M1124" s="1"/>
-      <c r="N1124" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1124" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1124" s="2">
-        <f>VLOOKUP(O1124,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1125" spans="1:16">
-      <c r="A1125" s="7">
-        <v>103211</v>
-      </c>
-      <c r="B1125" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1125" s="2">
-        <f>VLOOKUP(B1125,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1125" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1125" s="2">
-        <f>VLOOKUP(D1125,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1125" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1125" s="2">
-        <f>VLOOKUP(F1125,Select!C:H,6,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="H1125" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="I1125" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1125" s="1"/>
-      <c r="K1125" s="1"/>
-      <c r="L1125" s="1"/>
-      <c r="M1125" s="1"/>
-      <c r="N1125" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1125" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1125" s="2">
-        <f>VLOOKUP(O1125,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1126" spans="1:16">
-      <c r="A1126" s="7">
-        <v>103212</v>
-      </c>
-      <c r="B1126" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1126" s="2">
-        <f>VLOOKUP(B1126,Select!A:H,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D1126" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1126" s="2">
-        <f>VLOOKUP(D1126,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1126" s="2">
-        <f>VLOOKUP(F1126,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1126" s="1" t="s">
-        <v>1108</v>
-      </c>
-      <c r="I1126" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1126" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1126" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1126" s="1"/>
-      <c r="M1126" s="1"/>
-      <c r="N1126" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1126" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1126" s="2">
-        <f>VLOOKUP(O1126,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1127" spans="1:16">
-      <c r="A1127" s="7">
-        <v>103300</v>
-      </c>
-      <c r="B1127" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1127" s="2">
-        <f>VLOOKUP(B1127,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1127" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1127" s="2">
-        <f>VLOOKUP(D1127,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1127" s="2">
-        <f>VLOOKUP(F1127,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1127" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="I1127" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1127" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1127" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1127" s="1"/>
-      <c r="M1127" s="1"/>
-      <c r="N1127" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1127" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1127" s="2">
-        <f>VLOOKUP(O1127,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1128" spans="1:16">
-      <c r="A1128" s="7">
-        <v>103301</v>
-      </c>
-      <c r="B1128" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1128" s="2">
-        <f>VLOOKUP(B1128,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1128" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1128" s="2">
-        <f>VLOOKUP(D1128,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1128" s="2">
-        <f>VLOOKUP(F1128,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1128" s="1" t="s">
-        <v>1110</v>
-      </c>
-      <c r="I1128" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1128" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1128" s="1">
-        <v>4</v>
-      </c>
-      <c r="L1128" s="1"/>
-      <c r="M1128" s="1"/>
-      <c r="N1128" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1128" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1128" s="2">
-        <f>VLOOKUP(O1128,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1129" spans="1:16">
-      <c r="A1129" s="7">
-        <v>103302</v>
-      </c>
-      <c r="B1129" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1129" s="2">
-        <f>VLOOKUP(B1129,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1129" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1129" s="2">
-        <f>VLOOKUP(D1129,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1129" s="2">
-        <f>VLOOKUP(F1129,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1129" s="1" t="s">
-        <v>1111</v>
-      </c>
-      <c r="I1129" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1129" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1129" s="1">
-        <v>4</v>
-      </c>
-      <c r="L1129" s="1"/>
-      <c r="M1129" s="1"/>
-      <c r="N1129" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1129" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1129" s="2">
-        <f>VLOOKUP(O1129,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1130" spans="1:16">
-      <c r="A1130" s="7">
-        <v>103303</v>
-      </c>
-      <c r="B1130" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1130" s="2">
-        <f>VLOOKUP(B1130,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1130" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1130" s="2">
-        <f>VLOOKUP(D1130,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1130" s="2">
-        <f>VLOOKUP(F1130,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1130" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="I1130" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1130" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1130" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1130" s="1"/>
-      <c r="M1130" s="1"/>
-      <c r="N1130" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1130" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1130" s="2">
-        <f>VLOOKUP(O1130,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1131" spans="1:16">
-      <c r="A1131" s="7">
-        <v>103304</v>
-      </c>
-      <c r="B1131" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1131" s="2">
-        <f>VLOOKUP(B1131,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1131" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1131" s="2">
-        <f>VLOOKUP(D1131,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1131" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1131" s="2">
-        <f>VLOOKUP(F1131,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1131" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I1131" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1131" s="1"/>
-      <c r="K1131" s="1"/>
-      <c r="L1131" s="1"/>
-      <c r="M1131" s="1"/>
-      <c r="N1131" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1131" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1131" s="2">
-        <f>VLOOKUP(O1131,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1132" spans="1:16">
-      <c r="A1132" s="7">
-        <v>103305</v>
-      </c>
-      <c r="B1132" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1132" s="2">
-        <f>VLOOKUP(B1132,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1132" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1132" s="2">
-        <f>VLOOKUP(D1132,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1132" s="2">
-        <f>VLOOKUP(F1132,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1132" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="I1132" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1132" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1132" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1132" s="1"/>
-      <c r="M1132" s="1"/>
-      <c r="N1132" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1132" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1132" s="2">
-        <f>VLOOKUP(O1132,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1133" spans="1:16">
-      <c r="A1133" s="7">
-        <v>103306</v>
-      </c>
-      <c r="B1133" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1133" s="2">
-        <f>VLOOKUP(B1133,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1133" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1133" s="2">
-        <f>VLOOKUP(D1133,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1133" s="2">
-        <f>VLOOKUP(F1133,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1133" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="I1133" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1133" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1133" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1133" s="1"/>
-      <c r="M1133" s="1"/>
-      <c r="N1133" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1133" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1133" s="2">
-        <f>VLOOKUP(O1133,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1134" spans="1:16">
-      <c r="A1134" s="7">
-        <v>103307</v>
-      </c>
-      <c r="B1134" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1134" s="2">
-        <f>VLOOKUP(B1134,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1134" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1134" s="2">
-        <f>VLOOKUP(D1134,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1134" s="2">
-        <f>VLOOKUP(F1134,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1134" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I1134" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1134" s="1">
-        <v>5</v>
-      </c>
-      <c r="K1134" s="1">
-        <v>4</v>
-      </c>
-      <c r="L1134" s="1"/>
-      <c r="M1134" s="1"/>
-      <c r="N1134" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1134" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1134" s="2">
-        <f>VLOOKUP(O1134,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1135" spans="1:16">
-      <c r="A1135" s="7">
-        <v>103308</v>
-      </c>
-      <c r="B1135" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1135" s="2">
-        <f>VLOOKUP(B1135,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1135" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1135" s="2">
-        <f>VLOOKUP(D1135,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1135" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1135" s="2">
-        <f>VLOOKUP(F1135,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1135" s="1" t="s">
-        <v>1117</v>
-      </c>
-      <c r="I1135" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1135" s="1"/>
-      <c r="K1135" s="1"/>
-      <c r="L1135" s="1"/>
-      <c r="M1135" s="1"/>
-      <c r="N1135" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1135" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1135" s="2">
-        <f>VLOOKUP(O1135,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1136" spans="1:16">
-      <c r="A1136" s="7">
-        <v>103309</v>
-      </c>
-      <c r="B1136" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1136" s="2">
-        <f>VLOOKUP(B1136,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1136" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1136" s="2">
-        <f>VLOOKUP(D1136,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1136" s="2">
-        <f>VLOOKUP(F1136,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1136" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="I1136" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1136" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1136" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1136" s="1"/>
-      <c r="M1136" s="1"/>
-      <c r="N1136" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1136" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1136" s="2">
-        <f>VLOOKUP(O1136,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1137" spans="1:16">
-      <c r="A1137" s="7">
-        <v>103310</v>
-      </c>
-      <c r="B1137" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1137" s="2">
-        <f>VLOOKUP(B1137,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1137" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1137" s="2">
-        <f>VLOOKUP(D1137,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1137" s="2">
-        <f>VLOOKUP(F1137,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1137" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="I1137" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1137" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1137" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1137" s="1"/>
-      <c r="M1137" s="1"/>
-      <c r="N1137" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1137" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1137" s="2">
-        <f>VLOOKUP(O1137,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1138" spans="1:16">
-      <c r="A1138" s="7">
-        <v>103311</v>
-      </c>
-      <c r="B1138" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1138" s="2">
-        <f>VLOOKUP(B1138,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1138" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1138" s="2">
-        <f>VLOOKUP(D1138,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1138" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1138" s="2">
-        <f>VLOOKUP(F1138,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1138" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="I1138" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1138" s="1"/>
-      <c r="K1138" s="1"/>
-      <c r="L1138" s="1"/>
-      <c r="M1138" s="1"/>
-      <c r="N1138" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1138" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1138" s="2">
-        <f>VLOOKUP(O1138,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1139" spans="1:16">
-      <c r="A1139" s="7">
-        <v>103312</v>
-      </c>
-      <c r="B1139" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1139" s="2">
-        <f>VLOOKUP(B1139,Select!A:H,8,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="D1139" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1139" s="2">
-        <f>VLOOKUP(D1139,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1139" s="2">
-        <f>VLOOKUP(F1139,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1139" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="I1139" s="1">
-        <v>9</v>
-      </c>
-      <c r="J1139" s="1">
-        <v>5</v>
-      </c>
-      <c r="K1139" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1139" s="1"/>
-      <c r="M1139" s="1"/>
-      <c r="N1139" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1139" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1139" s="2">
-        <f>VLOOKUP(O1139,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1140" spans="1:16">
-      <c r="A1140" s="7">
-        <v>103400</v>
-      </c>
-      <c r="B1140" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1140" s="2">
-        <f>VLOOKUP(B1140,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1140" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1140" s="2">
-        <f>VLOOKUP(D1140,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1140" s="2">
-        <f>VLOOKUP(F1140,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1140" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="I1140" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1140" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1140" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1140" s="1"/>
-      <c r="M1140" s="1"/>
-      <c r="N1140" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1140" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1140" s="2">
-        <f>VLOOKUP(O1140,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1141" spans="1:16">
-      <c r="A1141" s="7">
-        <v>103401</v>
-      </c>
-      <c r="B1141" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1141" s="2">
-        <f>VLOOKUP(B1141,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1141" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1141" s="2">
-        <f>VLOOKUP(D1141,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1141" s="2">
-        <f>VLOOKUP(F1141,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1141" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="I1141" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1141" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1141" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1141" s="1"/>
-      <c r="M1141" s="1"/>
-      <c r="N1141" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1141" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1141" s="2">
-        <f>VLOOKUP(O1141,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1142" spans="1:16">
-      <c r="A1142" s="7">
-        <v>103402</v>
-      </c>
-      <c r="B1142" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1142" s="2">
-        <f>VLOOKUP(B1142,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1142" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1142" s="2">
-        <f>VLOOKUP(D1142,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1142" s="2">
-        <f>VLOOKUP(F1142,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1142" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="I1142" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1142" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1142" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1142" s="1"/>
-      <c r="M1142" s="1"/>
-      <c r="N1142" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1142" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1142" s="2">
-        <f>VLOOKUP(O1142,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1143" spans="1:16">
-      <c r="A1143" s="7">
-        <v>103403</v>
-      </c>
-      <c r="B1143" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1143" s="2">
-        <f>VLOOKUP(B1143,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1143" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1143" s="2">
-        <f>VLOOKUP(D1143,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1143" s="2">
-        <f>VLOOKUP(F1143,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1143" s="1" t="s">
-        <v>1125</v>
-      </c>
-      <c r="I1143" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1143" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1143" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1143" s="1"/>
-      <c r="M1143" s="1"/>
-      <c r="N1143" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1143" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1143" s="2">
-        <f>VLOOKUP(O1143,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1144" spans="1:16">
-      <c r="A1144" s="7">
-        <v>103404</v>
-      </c>
-      <c r="B1144" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1144" s="2">
-        <f>VLOOKUP(B1144,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1144" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1144" s="2">
-        <f>VLOOKUP(D1144,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1144" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1144" s="2">
-        <f>VLOOKUP(F1144,Select!C:H,6,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="H1144" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I1144" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1144" s="1"/>
-      <c r="K1144" s="1"/>
-      <c r="L1144" s="1"/>
-      <c r="M1144" s="1"/>
-      <c r="N1144" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1144" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1144" s="2">
-        <f>VLOOKUP(O1144,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1145" spans="1:16">
-      <c r="A1145" s="7">
-        <v>103405</v>
-      </c>
-      <c r="B1145" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1145" s="2">
-        <f>VLOOKUP(B1145,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1145" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1145" s="2">
-        <f>VLOOKUP(D1145,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1145" s="2">
-        <f>VLOOKUP(F1145,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1145" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="I1145" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1145" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1145" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1145" s="1"/>
-      <c r="M1145" s="1"/>
-      <c r="N1145" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1145" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1145" s="2">
-        <f>VLOOKUP(O1145,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1146" spans="1:16">
-      <c r="A1146" s="7">
-        <v>103406</v>
-      </c>
-      <c r="B1146" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1146" s="2">
-        <f>VLOOKUP(B1146,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1146" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1146" s="2">
-        <f>VLOOKUP(D1146,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1146" s="2">
-        <f>VLOOKUP(F1146,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1146" s="1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="I1146" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1146" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1146" s="1">
-        <v>4</v>
-      </c>
-      <c r="L1146" s="1"/>
-      <c r="M1146" s="1"/>
-      <c r="N1146" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1146" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1146" s="2">
-        <f>VLOOKUP(O1146,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1147" spans="1:16">
-      <c r="A1147" s="7">
-        <v>103407</v>
-      </c>
-      <c r="B1147" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1147" s="2">
-        <f>VLOOKUP(B1147,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1147" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1147" s="2">
-        <f>VLOOKUP(D1147,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1147" s="2">
-        <f>VLOOKUP(F1147,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1147" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="I1147" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1147" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1147" s="1">
-        <v>6</v>
-      </c>
-      <c r="L1147" s="1"/>
-      <c r="M1147" s="1"/>
-      <c r="N1147" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1147" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1147" s="2">
-        <f>VLOOKUP(O1147,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1148" spans="1:16">
-      <c r="A1148" s="7">
-        <v>103408</v>
-      </c>
-      <c r="B1148" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1148" s="2">
-        <f>VLOOKUP(B1148,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1148" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1148" s="2">
-        <f>VLOOKUP(D1148,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1148" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1148" s="2">
-        <f>VLOOKUP(F1148,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1148" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="I1148" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1148" s="1"/>
-      <c r="K1148" s="1"/>
-      <c r="L1148" s="1"/>
-      <c r="M1148" s="1"/>
-      <c r="N1148" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1148" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1148" s="2">
-        <f>VLOOKUP(O1148,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1149" spans="1:16">
-      <c r="A1149" s="7">
-        <v>103409</v>
-      </c>
-      <c r="B1149" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1149" s="2">
-        <f>VLOOKUP(B1149,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1149" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1149" s="2">
-        <f>VLOOKUP(D1149,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1149" s="2">
-        <f>VLOOKUP(F1149,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1149" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="I1149" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1149" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1149" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1149" s="1"/>
-      <c r="M1149" s="1"/>
-      <c r="N1149" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1149" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1149" s="2">
-        <f>VLOOKUP(O1149,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1150" spans="1:16">
-      <c r="A1150" s="7">
-        <v>103410</v>
-      </c>
-      <c r="B1150" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1150" s="2">
-        <f>VLOOKUP(B1150,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1150" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1150" s="2">
-        <f>VLOOKUP(D1150,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1150" s="2">
-        <f>VLOOKUP(F1150,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1150" s="1" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I1150" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1150" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1150" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1150" s="1"/>
-      <c r="M1150" s="1"/>
-      <c r="N1150" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1150" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1150" s="2">
-        <f>VLOOKUP(O1150,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1151" spans="1:16">
-      <c r="A1151" s="7">
-        <v>103411</v>
-      </c>
-      <c r="B1151" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1151" s="2">
-        <f>VLOOKUP(B1151,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1151" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1151" s="2">
-        <f>VLOOKUP(D1151,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1151" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1151" s="2">
-        <f>VLOOKUP(F1151,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1151" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="I1151" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1151" s="1"/>
-      <c r="K1151" s="1"/>
-      <c r="L1151" s="1"/>
-      <c r="M1151" s="1"/>
-      <c r="N1151" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1151" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1151" s="2">
-        <f>VLOOKUP(O1151,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1152" spans="1:16">
-      <c r="A1152" s="7">
-        <v>103412</v>
-      </c>
-      <c r="B1152" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1152" s="2">
-        <f>VLOOKUP(B1152,Select!A:H,8,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="D1152" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1152" s="2">
-        <f>VLOOKUP(D1152,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1152" s="2">
-        <f>VLOOKUP(F1152,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1152" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="I1152" s="1">
-        <v>9</v>
-      </c>
-      <c r="J1152" s="1">
-        <v>5</v>
-      </c>
-      <c r="K1152" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1152" s="1"/>
-      <c r="M1152" s="1"/>
-      <c r="N1152" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1152" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1152" s="2">
-        <f>VLOOKUP(O1152,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1153" spans="1:16">
-      <c r="A1153" s="7">
-        <v>103500</v>
-      </c>
-      <c r="B1153" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1153" s="2">
-        <f>VLOOKUP(B1153,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1153" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1153" s="2">
-        <f>VLOOKUP(D1153,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1153" s="2">
-        <f>VLOOKUP(F1153,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1153" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="I1153" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1153" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1153" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1153" s="1"/>
-      <c r="M1153" s="1"/>
-      <c r="N1153" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1153" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1153" s="2">
-        <f>VLOOKUP(O1153,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1154" spans="1:16">
-      <c r="A1154" s="7">
-        <v>103501</v>
-      </c>
-      <c r="B1154" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1154" s="2">
-        <f>VLOOKUP(B1154,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1154" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1154" s="2">
-        <f>VLOOKUP(D1154,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1154" s="2">
-        <f>VLOOKUP(F1154,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1154" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="I1154" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1154" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1154" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1154" s="1"/>
-      <c r="M1154" s="1"/>
-      <c r="N1154" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1154" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1154" s="2">
-        <f>VLOOKUP(O1154,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1155" spans="1:16">
-      <c r="A1155" s="7">
-        <v>103502</v>
-      </c>
-      <c r="B1155" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1155" s="2">
-        <f>VLOOKUP(B1155,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1155" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1155" s="2">
-        <f>VLOOKUP(D1155,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1155" s="2">
-        <f>VLOOKUP(F1155,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1155" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="I1155" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1155" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1155" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1155" s="1"/>
-      <c r="M1155" s="1"/>
-      <c r="N1155" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1155" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1155" s="2">
-        <f>VLOOKUP(O1155,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1156" spans="1:16">
-      <c r="A1156" s="7">
-        <v>103503</v>
-      </c>
-      <c r="B1156" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1156" s="2">
-        <f>VLOOKUP(B1156,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1156" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1156" s="2">
-        <f>VLOOKUP(D1156,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1156" s="2">
-        <f>VLOOKUP(F1156,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1156" s="1" t="s">
-        <v>1138</v>
-      </c>
-      <c r="I1156" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1156" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1156" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1156" s="1"/>
-      <c r="M1156" s="1"/>
-      <c r="N1156" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1156" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1156" s="2">
-        <f>VLOOKUP(O1156,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1157" spans="1:16">
-      <c r="A1157" s="7">
-        <v>103504</v>
-      </c>
-      <c r="B1157" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1157" s="2">
-        <f>VLOOKUP(B1157,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1157" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1157" s="2">
-        <f>VLOOKUP(D1157,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1157" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1157" s="2">
-        <f>VLOOKUP(F1157,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1157" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="I1157" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1157" s="1"/>
-      <c r="K1157" s="1"/>
-      <c r="L1157" s="1"/>
-      <c r="M1157" s="1"/>
-      <c r="N1157" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1157" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1157" s="2">
-        <f>VLOOKUP(O1157,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1158" spans="1:16">
-      <c r="A1158" s="7">
-        <v>103505</v>
-      </c>
-      <c r="B1158" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1158" s="2">
-        <f>VLOOKUP(B1158,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1158" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1158" s="2">
-        <f>VLOOKUP(D1158,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1158" s="2">
-        <f>VLOOKUP(F1158,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1158" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="I1158" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1158" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1158" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1158" s="1"/>
-      <c r="M1158" s="1"/>
-      <c r="N1158" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1158" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1158" s="2">
-        <f>VLOOKUP(O1158,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1159" spans="1:16">
-      <c r="A1159" s="7">
-        <v>103506</v>
-      </c>
-      <c r="B1159" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1159" s="2">
-        <f>VLOOKUP(B1159,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1159" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1159" s="2">
-        <f>VLOOKUP(D1159,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1159" s="2">
-        <f>VLOOKUP(F1159,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1159" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="I1159" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1159" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1159" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1159" s="1"/>
-      <c r="M1159" s="1"/>
-      <c r="N1159" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1159" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1159" s="2">
-        <f>VLOOKUP(O1159,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1160" spans="1:16">
-      <c r="A1160" s="7">
-        <v>103507</v>
-      </c>
-      <c r="B1160" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1160" s="2">
-        <f>VLOOKUP(B1160,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1160" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1160" s="2">
-        <f>VLOOKUP(D1160,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1160" s="2">
-        <f>VLOOKUP(F1160,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1160" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="I1160" s="1">
-        <v>7</v>
-      </c>
-      <c r="J1160" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1160" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1160" s="1"/>
-      <c r="M1160" s="1"/>
-      <c r="N1160" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1160" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1160" s="2">
-        <f>VLOOKUP(O1160,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1161" spans="1:16">
-      <c r="A1161" s="7">
-        <v>103508</v>
-      </c>
-      <c r="B1161" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1161" s="2">
-        <f>VLOOKUP(B1161,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1161" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1161" s="2">
-        <f>VLOOKUP(D1161,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1161" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1161" s="2">
-        <f>VLOOKUP(F1161,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1161" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="I1161" s="1">
-        <v>1</v>
-      </c>
-      <c r="J1161" s="1"/>
-      <c r="K1161" s="1"/>
-      <c r="L1161" s="1"/>
-      <c r="M1161" s="1"/>
-      <c r="N1161" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1161" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1161" s="2">
-        <f>VLOOKUP(O1161,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1162" spans="1:16">
-      <c r="A1162" s="7">
-        <v>103509</v>
-      </c>
-      <c r="B1162" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1162" s="2">
-        <f>VLOOKUP(B1162,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1162" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1162" s="2">
-        <f>VLOOKUP(D1162,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1162" s="2">
-        <f>VLOOKUP(F1162,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1162" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="I1162" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1162" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1162" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1162" s="1"/>
-      <c r="M1162" s="1"/>
-      <c r="N1162" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1162" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1162" s="2">
-        <f>VLOOKUP(O1162,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1163" spans="1:16">
-      <c r="A1163" s="7">
-        <v>103510</v>
-      </c>
-      <c r="B1163" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1163" s="2">
-        <f>VLOOKUP(B1163,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1163" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1163" s="2">
-        <f>VLOOKUP(D1163,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1163" s="2">
-        <f>VLOOKUP(F1163,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1163" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="I1163" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1163" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1163" s="1">
-        <v>6</v>
-      </c>
-      <c r="L1163" s="1"/>
-      <c r="M1163" s="1"/>
-      <c r="N1163" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1163" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1163" s="2">
-        <f>VLOOKUP(O1163,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1164" spans="1:16">
-      <c r="A1164" s="7">
-        <v>103511</v>
-      </c>
-      <c r="B1164" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1164" s="2">
-        <f>VLOOKUP(B1164,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1164" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1164" s="2">
-        <f>VLOOKUP(D1164,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1164" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1164" s="2">
-        <f>VLOOKUP(F1164,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1164" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="I1164" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1164" s="1"/>
-      <c r="K1164" s="1"/>
-      <c r="L1164" s="1"/>
-      <c r="M1164" s="1"/>
-      <c r="N1164" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1164" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1164" s="2">
-        <f>VLOOKUP(O1164,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1165" spans="1:16">
-      <c r="A1165" s="7">
-        <v>103512</v>
-      </c>
-      <c r="B1165" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C1165" s="2">
-        <f>VLOOKUP(B1165,Select!A:H,8,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="D1165" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1165" s="2">
-        <f>VLOOKUP(D1165,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1165" s="2">
-        <f>VLOOKUP(F1165,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1165" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="I1165" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1165" s="1">
-        <v>5</v>
-      </c>
-      <c r="K1165" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1165" s="1"/>
-      <c r="M1165" s="1"/>
-      <c r="N1165" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1165" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1165" s="2">
-        <f>VLOOKUP(O1165,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1166" spans="1:16">
-      <c r="A1166" s="7">
-        <v>103600</v>
-      </c>
-      <c r="B1166" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1166" s="2">
-        <f>VLOOKUP(B1166,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1166" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1166" s="2">
-        <f>VLOOKUP(D1166,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1166" s="2">
-        <f>VLOOKUP(F1166,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1166" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="I1166" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1166" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1166" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1166" s="1"/>
-      <c r="M1166" s="1"/>
-      <c r="N1166" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1166" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1166" s="2">
-        <f>VLOOKUP(O1166,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1167" spans="1:16">
-      <c r="A1167" s="7">
-        <v>103601</v>
-      </c>
-      <c r="B1167" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1167" s="2">
-        <f>VLOOKUP(B1167,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1167" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1167" s="2">
-        <f>VLOOKUP(D1167,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1167" s="2">
-        <f>VLOOKUP(F1167,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1167" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I1167" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1167" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1167" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1167" s="1"/>
-      <c r="M1167" s="1"/>
-      <c r="N1167" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1167" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1167" s="2">
-        <f>VLOOKUP(O1167,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1168" spans="1:16">
-      <c r="A1168" s="7">
-        <v>103602</v>
-      </c>
-      <c r="B1168" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1168" s="2">
-        <f>VLOOKUP(B1168,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1168" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1168" s="2">
-        <f>VLOOKUP(D1168,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1168" s="2">
-        <f>VLOOKUP(F1168,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1168" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="I1168" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1168" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1168" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1168" s="1"/>
-      <c r="M1168" s="1"/>
-      <c r="N1168" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1168" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1168" s="2">
-        <f>VLOOKUP(O1168,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1169" spans="1:16">
-      <c r="A1169" s="7">
-        <v>103603</v>
-      </c>
-      <c r="B1169" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1169" s="2">
-        <f>VLOOKUP(B1169,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1169" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1169" s="2">
-        <f>VLOOKUP(D1169,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1169" s="2">
-        <f>VLOOKUP(F1169,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1169" s="1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="I1169" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1169" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1169" s="1">
-        <v>7</v>
-      </c>
-      <c r="L1169" s="1"/>
-      <c r="M1169" s="1"/>
-      <c r="N1169" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1169" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1169" s="2">
-        <f>VLOOKUP(O1169,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1170" spans="1:16">
-      <c r="A1170" s="7">
-        <v>103604</v>
-      </c>
-      <c r="B1170" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1170" s="2">
-        <f>VLOOKUP(B1170,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1170" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1170" s="2">
-        <f>VLOOKUP(D1170,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1170" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1170" s="2">
-        <f>VLOOKUP(F1170,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1170" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="I1170" s="1">
-        <v>1</v>
-      </c>
-      <c r="J1170" s="1"/>
-      <c r="K1170" s="1"/>
-      <c r="L1170" s="1"/>
-      <c r="M1170" s="1"/>
-      <c r="N1170" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1170" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1170" s="2">
-        <f>VLOOKUP(O1170,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1171" spans="1:16">
-      <c r="A1171" s="7">
-        <v>103605</v>
-      </c>
-      <c r="B1171" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1171" s="2">
-        <f>VLOOKUP(B1171,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1171" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1171" s="2">
-        <f>VLOOKUP(D1171,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1171" s="2">
-        <f>VLOOKUP(F1171,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1171" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="I1171" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1171" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1171" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1171" s="1"/>
-      <c r="M1171" s="1"/>
-      <c r="N1171" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1171" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1171" s="2">
-        <f>VLOOKUP(O1171,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1172" spans="1:16">
-      <c r="A1172" s="7">
-        <v>103606</v>
-      </c>
-      <c r="B1172" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1172" s="2">
-        <f>VLOOKUP(B1172,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1172" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1172" s="2">
-        <f>VLOOKUP(D1172,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1172" s="2">
-        <f>VLOOKUP(F1172,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1172" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="I1172" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1172" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1172" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1172" s="1"/>
-      <c r="M1172" s="1"/>
-      <c r="N1172" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1172" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1172" s="2">
-        <f>VLOOKUP(O1172,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1173" spans="1:16">
-      <c r="A1173" s="7">
-        <v>103607</v>
-      </c>
-      <c r="B1173" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1173" s="2">
-        <f>VLOOKUP(B1173,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1173" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1173" s="2">
-        <f>VLOOKUP(D1173,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1173" s="2">
-        <f>VLOOKUP(F1173,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1173" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="I1173" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1173" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1173" s="1">
-        <v>6</v>
-      </c>
-      <c r="L1173" s="1"/>
-      <c r="M1173" s="1"/>
-      <c r="N1173" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1173" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1173" s="2">
-        <f>VLOOKUP(O1173,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1174" spans="1:16">
-      <c r="A1174" s="7">
-        <v>103608</v>
-      </c>
-      <c r="B1174" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1174" s="2">
-        <f>VLOOKUP(B1174,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1174" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1174" s="2">
-        <f>VLOOKUP(D1174,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1174" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1174" s="2">
-        <f>VLOOKUP(F1174,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1174" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="I1174" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1174" s="1"/>
-      <c r="K1174" s="1"/>
-      <c r="L1174" s="1"/>
-      <c r="M1174" s="1"/>
-      <c r="N1174" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1174" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1174" s="2">
-        <f>VLOOKUP(O1174,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1175" spans="1:16">
-      <c r="A1175" s="7">
-        <v>103609</v>
-      </c>
-      <c r="B1175" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1175" s="2">
-        <f>VLOOKUP(B1175,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1175" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1175" s="2">
-        <f>VLOOKUP(D1175,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1175" s="2">
-        <f>VLOOKUP(F1175,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1175" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="I1175" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1175" s="1">
-        <v>6</v>
-      </c>
-      <c r="K1175" s="1">
-        <v>6</v>
-      </c>
-      <c r="L1175" s="1"/>
-      <c r="M1175" s="1"/>
-      <c r="N1175" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1175" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1175" s="2">
-        <f>VLOOKUP(O1175,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1176" spans="1:16">
-      <c r="A1176" s="7">
-        <v>103610</v>
-      </c>
-      <c r="B1176" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1176" s="2">
-        <f>VLOOKUP(B1176,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1176" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1176" s="2">
-        <f>VLOOKUP(D1176,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1176" s="2">
-        <f>VLOOKUP(F1176,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1176" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="I1176" s="1">
-        <v>7</v>
-      </c>
-      <c r="J1176" s="1">
-        <v>5</v>
-      </c>
-      <c r="K1176" s="1">
-        <v>7</v>
-      </c>
-      <c r="L1176" s="1"/>
-      <c r="M1176" s="1"/>
-      <c r="N1176" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1176" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1176" s="2">
-        <f>VLOOKUP(O1176,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1177" spans="1:16">
-      <c r="A1177" s="7">
-        <v>103611</v>
-      </c>
-      <c r="B1177" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1177" s="2">
-        <f>VLOOKUP(B1177,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1177" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1177" s="2">
-        <f>VLOOKUP(D1177,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1177" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1177" s="2">
-        <f>VLOOKUP(F1177,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1177" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="I1177" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1177" s="1"/>
-      <c r="K1177" s="1"/>
-      <c r="L1177" s="1"/>
-      <c r="M1177" s="1"/>
-      <c r="N1177" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1177" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1177" s="2">
-        <f>VLOOKUP(O1177,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1178" spans="1:16">
-      <c r="A1178" s="7">
-        <v>103612</v>
-      </c>
-      <c r="B1178" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C1178" s="2">
-        <f>VLOOKUP(B1178,Select!A:H,8,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="D1178" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1178" s="2">
-        <f>VLOOKUP(D1178,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1178" s="2">
-        <f>VLOOKUP(F1178,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1178" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="I1178" s="1">
-        <v>7</v>
-      </c>
-      <c r="J1178" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1178" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1178" s="1"/>
-      <c r="M1178" s="1"/>
-      <c r="N1178" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1178" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1178" s="2">
-        <f>VLOOKUP(O1178,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1179" spans="1:16">
-      <c r="A1179" s="7">
-        <v>103700</v>
-      </c>
-      <c r="B1179" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1179" s="2">
-        <f>VLOOKUP(B1179,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1179" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1179" s="2">
-        <f>VLOOKUP(D1179,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1179" s="2">
-        <f>VLOOKUP(F1179,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1179" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="I1179" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1179" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1179" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1179" s="1"/>
-      <c r="M1179" s="1"/>
-      <c r="N1179" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1179" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1179" s="2">
-        <f>VLOOKUP(O1179,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1180" spans="1:16">
-      <c r="A1180" s="7">
-        <v>103701</v>
-      </c>
-      <c r="B1180" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1180" s="2">
-        <f>VLOOKUP(B1180,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1180" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1180" s="2">
-        <f>VLOOKUP(D1180,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1180" s="2">
-        <f>VLOOKUP(F1180,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1180" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="I1180" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1180" s="1">
-        <v>1</v>
-      </c>
-      <c r="K1180" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1180" s="1"/>
-      <c r="M1180" s="1"/>
-      <c r="N1180" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1180" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1180" s="2">
-        <f>VLOOKUP(O1180,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1181" spans="1:16">
-      <c r="A1181" s="7">
-        <v>103702</v>
-      </c>
-      <c r="B1181" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1181" s="2">
-        <f>VLOOKUP(B1181,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1181" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1181" s="2">
-        <f>VLOOKUP(D1181,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1181" s="2">
-        <f>VLOOKUP(F1181,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1181" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="I1181" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1181" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1181" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1181" s="1"/>
-      <c r="M1181" s="1"/>
-      <c r="N1181" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1181" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1181" s="2">
-        <f>VLOOKUP(O1181,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1182" spans="1:16">
-      <c r="A1182" s="7">
-        <v>103703</v>
-      </c>
-      <c r="B1182" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1182" s="2">
-        <f>VLOOKUP(B1182,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1182" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1182" s="2">
-        <f>VLOOKUP(D1182,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1182" s="2">
-        <f>VLOOKUP(F1182,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1182" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="I1182" s="1">
-        <v>7</v>
-      </c>
-      <c r="J1182" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1182" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1182" s="1"/>
-      <c r="M1182" s="1"/>
-      <c r="N1182" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1182" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1182" s="2">
-        <f>VLOOKUP(O1182,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1183" spans="1:16">
-      <c r="A1183" s="7">
-        <v>103704</v>
-      </c>
-      <c r="B1183" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1183" s="2">
-        <f>VLOOKUP(B1183,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1183" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1183" s="2">
-        <f>VLOOKUP(D1183,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1183" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1183" s="2">
-        <f>VLOOKUP(F1183,Select!C:H,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="H1183" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="I1183" s="1">
-        <v>7</v>
-      </c>
-      <c r="J1183" s="1"/>
-      <c r="K1183" s="1"/>
-      <c r="L1183" s="1"/>
-      <c r="M1183" s="1"/>
-      <c r="N1183" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1183" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1183" s="2">
-        <f>VLOOKUP(O1183,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1184" spans="1:16">
-      <c r="A1184" s="7">
-        <v>103705</v>
-      </c>
-      <c r="B1184" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1184" s="2">
-        <f>VLOOKUP(B1184,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1184" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1184" s="2">
-        <f>VLOOKUP(D1184,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1184" s="2">
-        <f>VLOOKUP(F1184,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1184" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="I1184" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1184" s="1">
-        <v>2</v>
-      </c>
-      <c r="K1184" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1184" s="1"/>
-      <c r="M1184" s="1"/>
-      <c r="N1184" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1184" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1184" s="2">
-        <f>VLOOKUP(O1184,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1185" spans="1:16">
-      <c r="A1185" s="7">
-        <v>103706</v>
-      </c>
-      <c r="B1185" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1185" s="2">
-        <f>VLOOKUP(B1185,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1185" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1185" s="2">
-        <f>VLOOKUP(D1185,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1185" s="2">
-        <f>VLOOKUP(F1185,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1185" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="I1185" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1185" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1185" s="1">
-        <v>2</v>
-      </c>
-      <c r="L1185" s="1"/>
-      <c r="M1185" s="1"/>
-      <c r="N1185" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1185" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1185" s="2">
-        <f>VLOOKUP(O1185,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1186" spans="1:16">
-      <c r="A1186" s="7">
-        <v>103707</v>
-      </c>
-      <c r="B1186" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1186" s="2">
-        <f>VLOOKUP(B1186,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1186" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1186" s="2">
-        <f>VLOOKUP(D1186,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1186" s="2">
-        <f>VLOOKUP(F1186,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1186" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="I1186" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1186" s="1">
-        <v>4</v>
-      </c>
-      <c r="K1186" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1186" s="1"/>
-      <c r="M1186" s="1"/>
-      <c r="N1186" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1186" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1186" s="2">
-        <f>VLOOKUP(O1186,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1187" spans="1:16">
-      <c r="A1187" s="7">
-        <v>103708</v>
-      </c>
-      <c r="B1187" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1187" s="2">
-        <f>VLOOKUP(B1187,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1187" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1187" s="2">
-        <f>VLOOKUP(D1187,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1187" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1187" s="2">
-        <f>VLOOKUP(F1187,Select!C:H,6,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="H1187" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="I1187" s="1">
-        <v>3</v>
-      </c>
-      <c r="J1187" s="1"/>
-      <c r="K1187" s="1"/>
-      <c r="L1187" s="1"/>
-      <c r="M1187" s="1"/>
-      <c r="N1187" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1187" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1187" s="2">
-        <f>VLOOKUP(O1187,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1188" spans="1:16">
-      <c r="A1188" s="7">
-        <v>103709</v>
-      </c>
-      <c r="B1188" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1188" s="2">
-        <f>VLOOKUP(B1188,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1188" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1188" s="2">
-        <f>VLOOKUP(D1188,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1188" s="2">
-        <f>VLOOKUP(F1188,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1188" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="I1188" s="1">
-        <v>6</v>
-      </c>
-      <c r="J1188" s="1">
-        <v>3</v>
-      </c>
-      <c r="K1188" s="1">
-        <v>3</v>
-      </c>
-      <c r="L1188" s="1"/>
-      <c r="M1188" s="1"/>
-      <c r="N1188" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1188" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1188" s="2">
-        <f>VLOOKUP(O1188,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1189" spans="1:16">
-      <c r="A1189" s="7">
-        <v>103710</v>
-      </c>
-      <c r="B1189" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1189" s="2">
-        <f>VLOOKUP(B1189,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1189" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1189" s="2">
-        <f>VLOOKUP(D1189,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1189" s="2">
-        <f>VLOOKUP(F1189,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1189" s="1" t="s">
-        <v>1171</v>
-      </c>
-      <c r="I1189" s="1">
-        <v>7</v>
-      </c>
-      <c r="J1189" s="1">
-        <v>5</v>
-      </c>
-      <c r="K1189" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1189" s="1"/>
-      <c r="M1189" s="1"/>
-      <c r="N1189" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1189" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1189" s="2">
-        <f>VLOOKUP(O1189,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1190" spans="1:16">
-      <c r="A1190" s="7">
-        <v>103711</v>
-      </c>
-      <c r="B1190" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1190" s="2">
-        <f>VLOOKUP(B1190,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1190" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1190" s="2">
-        <f>VLOOKUP(D1190,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1190" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1190" s="2">
-        <f>VLOOKUP(F1190,Select!C:H,6,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="H1190" s="1" t="s">
-        <v>1172</v>
-      </c>
-      <c r="I1190" s="1">
-        <v>4</v>
-      </c>
-      <c r="J1190" s="1"/>
-      <c r="K1190" s="1"/>
-      <c r="L1190" s="1"/>
-      <c r="M1190" s="1"/>
-      <c r="N1190" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1190" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1190" s="2">
-        <f>VLOOKUP(O1190,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1191" spans="1:16">
-      <c r="A1191" s="7">
-        <v>103712</v>
-      </c>
-      <c r="B1191" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1191" s="2">
-        <f>VLOOKUP(B1191,Select!A:H,8,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="D1191" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1191" s="2">
-        <f>VLOOKUP(D1191,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1191" s="2">
-        <f>VLOOKUP(F1191,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1191" s="1" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I1191" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1191" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1191" s="1">
-        <v>5</v>
-      </c>
-      <c r="L1191" s="1"/>
-      <c r="M1191" s="1"/>
-      <c r="N1191" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1191" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1191" s="2">
-        <f>VLOOKUP(O1191,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1192" spans="1:16">
-      <c r="A1192" s="7">
-        <v>104000</v>
-      </c>
-      <c r="B1192" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1192" s="2">
-        <f>VLOOKUP(B1192,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1192" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1192" s="2">
-        <f>VLOOKUP(D1192,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1192" s="2">
-        <f>VLOOKUP(F1192,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1192" s="1"/>
-      <c r="I1192" s="1"/>
-      <c r="J1192" s="1"/>
-      <c r="K1192" s="1"/>
-      <c r="L1192" s="1"/>
-      <c r="M1192" s="1"/>
-      <c r="N1192" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1192" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1192" s="2">
-        <f>VLOOKUP(O1192,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1193" spans="1:16">
-      <c r="A1193" s="7">
-        <v>104001</v>
-      </c>
-      <c r="B1193" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1193" s="2">
-        <f>VLOOKUP(B1193,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1193" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1193" s="2">
-        <f>VLOOKUP(D1193,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1193" s="2">
-        <f>VLOOKUP(F1193,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1193" s="1"/>
-      <c r="I1193" s="1"/>
-      <c r="J1193" s="1"/>
-      <c r="K1193" s="1"/>
-      <c r="L1193" s="1"/>
-      <c r="M1193" s="1"/>
-      <c r="N1193" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1193" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1193" s="2">
-        <f>VLOOKUP(O1193,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1194" spans="1:16">
-      <c r="A1194" s="7">
-        <v>104002</v>
-      </c>
-      <c r="B1194" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1194" s="2">
-        <f>VLOOKUP(B1194,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1194" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1194" s="2">
-        <f>VLOOKUP(D1194,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1194" s="2">
-        <f>VLOOKUP(F1194,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1194" s="1"/>
-      <c r="I1194" s="1"/>
-      <c r="J1194" s="1"/>
-      <c r="K1194" s="1"/>
-      <c r="L1194" s="1"/>
-      <c r="M1194" s="1"/>
-      <c r="N1194" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1194" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1194" s="2">
-        <f>VLOOKUP(O1194,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1195" spans="1:16">
-      <c r="A1195" s="7">
-        <v>104003</v>
-      </c>
-      <c r="B1195" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1195" s="2">
-        <f>VLOOKUP(B1195,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1195" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1195" s="2">
-        <f>VLOOKUP(D1195,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1195" s="2">
-        <f>VLOOKUP(F1195,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1195" s="1"/>
-      <c r="I1195" s="1"/>
-      <c r="J1195" s="1"/>
-      <c r="K1195" s="1"/>
-      <c r="L1195" s="1"/>
-      <c r="M1195" s="1"/>
-      <c r="N1195" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1195" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1195" s="2">
-        <f>VLOOKUP(O1195,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1196" spans="1:16">
-      <c r="A1196" s="7">
-        <v>104004</v>
-      </c>
-      <c r="B1196" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1196" s="2">
-        <f>VLOOKUP(B1196,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1196" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1196" s="2">
-        <f>VLOOKUP(D1196,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1196" s="2">
-        <f>VLOOKUP(F1196,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1196" s="1"/>
-      <c r="I1196" s="1"/>
-      <c r="J1196" s="1"/>
-      <c r="K1196" s="1"/>
-      <c r="L1196" s="1"/>
-      <c r="M1196" s="1"/>
-      <c r="N1196" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1196" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1196" s="2">
-        <f>VLOOKUP(O1196,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1197" spans="1:16">
-      <c r="A1197" s="7">
-        <v>104005</v>
-      </c>
-      <c r="B1197" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1197" s="2">
-        <f>VLOOKUP(B1197,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1197" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1197" s="2">
-        <f>VLOOKUP(D1197,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1197" s="2">
-        <f>VLOOKUP(F1197,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1197" s="1"/>
-      <c r="I1197" s="1"/>
-      <c r="J1197" s="1"/>
-      <c r="K1197" s="1"/>
-      <c r="L1197" s="1"/>
-      <c r="M1197" s="1"/>
-      <c r="N1197" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1197" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1197" s="2">
-        <f>VLOOKUP(O1197,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1198" spans="1:16">
-      <c r="A1198" s="7">
-        <v>104006</v>
-      </c>
-      <c r="B1198" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1198" s="2">
-        <f>VLOOKUP(B1198,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1198" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1198" s="2">
-        <f>VLOOKUP(D1198,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1198" s="2">
-        <f>VLOOKUP(F1198,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1198" s="1"/>
-      <c r="I1198" s="1"/>
-      <c r="J1198" s="1"/>
-      <c r="K1198" s="1"/>
-      <c r="L1198" s="1"/>
-      <c r="M1198" s="1"/>
-      <c r="N1198" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1198" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1198" s="2">
-        <f>VLOOKUP(O1198,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1199" spans="1:16">
-      <c r="A1199" s="7">
-        <v>104007</v>
-      </c>
-      <c r="B1199" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1199" s="2">
-        <f>VLOOKUP(B1199,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1199" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1199" s="2">
-        <f>VLOOKUP(D1199,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1199" s="2">
-        <f>VLOOKUP(F1199,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1199" s="1"/>
-      <c r="I1199" s="1"/>
-      <c r="J1199" s="1"/>
-      <c r="K1199" s="1"/>
-      <c r="L1199" s="1"/>
-      <c r="M1199" s="1"/>
-      <c r="N1199" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1199" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1199" s="2">
-        <f>VLOOKUP(O1199,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1200" spans="1:16">
-      <c r="A1200" s="7">
-        <v>104008</v>
-      </c>
-      <c r="B1200" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1200" s="2">
-        <f>VLOOKUP(B1200,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1200" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1200" s="2">
-        <f>VLOOKUP(D1200,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1200" s="2">
-        <f>VLOOKUP(F1200,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1200" s="1"/>
-      <c r="I1200" s="1"/>
-      <c r="J1200" s="1"/>
-      <c r="K1200" s="1"/>
-      <c r="L1200" s="1"/>
-      <c r="M1200" s="1"/>
-      <c r="N1200" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1200" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1200" s="2">
-        <f>VLOOKUP(O1200,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:16">
-      <c r="A1201" s="7">
-        <v>104009</v>
-      </c>
-      <c r="B1201" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1201" s="2">
-        <f>VLOOKUP(B1201,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1201" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1201" s="2">
-        <f>VLOOKUP(D1201,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1201" s="2">
-        <f>VLOOKUP(F1201,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1201" s="1"/>
-      <c r="I1201" s="1"/>
-      <c r="J1201" s="1"/>
-      <c r="K1201" s="1"/>
-      <c r="L1201" s="1"/>
-      <c r="M1201" s="1"/>
-      <c r="N1201" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1201" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1201" s="2">
-        <f>VLOOKUP(O1201,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1202" spans="1:16">
-      <c r="A1202" s="7">
-        <v>104010</v>
-      </c>
-      <c r="B1202" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1202" s="2">
-        <f>VLOOKUP(B1202,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1202" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1202" s="2">
-        <f>VLOOKUP(D1202,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1202" s="2">
-        <f>VLOOKUP(F1202,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1202" s="1"/>
-      <c r="I1202" s="1"/>
-      <c r="J1202" s="1"/>
-      <c r="K1202" s="1"/>
-      <c r="L1202" s="1"/>
-      <c r="M1202" s="1"/>
-      <c r="N1202" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1202" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1202" s="2">
-        <f>VLOOKUP(O1202,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1203" spans="1:16">
-      <c r="A1203" s="7">
-        <v>104011</v>
-      </c>
-      <c r="B1203" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1203" s="2">
-        <f>VLOOKUP(B1203,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1203" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1203" s="2">
-        <f>VLOOKUP(D1203,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1203" s="2">
-        <f>VLOOKUP(F1203,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1203" s="1"/>
-      <c r="I1203" s="1"/>
-      <c r="J1203" s="1"/>
-      <c r="K1203" s="1"/>
-      <c r="L1203" s="1"/>
-      <c r="M1203" s="1"/>
-      <c r="N1203" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1203" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1203" s="2">
-        <f>VLOOKUP(O1203,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1204" spans="1:16">
-      <c r="A1204" s="7">
-        <v>104012</v>
-      </c>
-      <c r="B1204" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1204" s="2">
-        <f>VLOOKUP(B1204,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1204" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1204" s="2">
-        <f>VLOOKUP(D1204,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1204" s="2">
-        <f>VLOOKUP(F1204,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1204" s="1"/>
-      <c r="I1204" s="1"/>
-      <c r="J1204" s="1"/>
-      <c r="K1204" s="1"/>
-      <c r="L1204" s="1"/>
-      <c r="M1204" s="1"/>
-      <c r="N1204" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1204" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1204" s="2">
-        <f>VLOOKUP(O1204,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1205" spans="1:16">
-      <c r="A1205" s="7">
-        <v>104013</v>
-      </c>
-      <c r="B1205" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1205" s="2">
-        <f>VLOOKUP(B1205,Select!A:H,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D1205" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1205" s="2">
-        <f>VLOOKUP(D1205,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1205" s="2">
-        <f>VLOOKUP(F1205,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1205" s="1"/>
-      <c r="I1205" s="1"/>
-      <c r="J1205" s="1"/>
-      <c r="K1205" s="1"/>
-      <c r="L1205" s="1"/>
-      <c r="M1205" s="1"/>
-      <c r="N1205" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1205" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1205" s="2">
-        <f>VLOOKUP(O1205,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1206" spans="1:16">
-      <c r="A1206" s="7">
-        <v>104100</v>
-      </c>
-      <c r="B1206" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1206" s="2">
-        <f>VLOOKUP(B1206,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1206" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1206" s="2">
-        <f>VLOOKUP(D1206,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1206" s="2">
-        <f>VLOOKUP(F1206,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1206" s="1"/>
-      <c r="I1206" s="1"/>
-      <c r="J1206" s="1"/>
-      <c r="K1206" s="1"/>
-      <c r="L1206" s="1"/>
-      <c r="M1206" s="1"/>
-      <c r="N1206" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1206" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1206" s="2">
-        <f>VLOOKUP(O1206,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1207" spans="1:16">
-      <c r="A1207" s="7">
-        <v>104101</v>
-      </c>
-      <c r="B1207" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1207" s="2">
-        <f>VLOOKUP(B1207,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1207" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1207" s="2">
-        <f>VLOOKUP(D1207,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1207" s="2">
-        <f>VLOOKUP(F1207,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1207" s="1"/>
-      <c r="I1207" s="1"/>
-      <c r="J1207" s="1"/>
-      <c r="K1207" s="1"/>
-      <c r="L1207" s="1"/>
-      <c r="M1207" s="1"/>
-      <c r="N1207" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1207" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1207" s="2">
-        <f>VLOOKUP(O1207,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1208" spans="1:16">
-      <c r="A1208" s="7">
-        <v>104102</v>
-      </c>
-      <c r="B1208" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1208" s="2">
-        <f>VLOOKUP(B1208,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1208" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1208" s="2">
-        <f>VLOOKUP(D1208,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1208" s="2">
-        <f>VLOOKUP(F1208,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1208" s="1"/>
-      <c r="I1208" s="1"/>
-      <c r="J1208" s="1"/>
-      <c r="K1208" s="1"/>
-      <c r="L1208" s="1"/>
-      <c r="M1208" s="1"/>
-      <c r="N1208" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1208" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1208" s="2">
-        <f>VLOOKUP(O1208,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1209" spans="1:16">
-      <c r="A1209" s="7">
-        <v>104103</v>
-      </c>
-      <c r="B1209" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1209" s="2">
-        <f>VLOOKUP(B1209,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1209" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1209" s="2">
-        <f>VLOOKUP(D1209,Select!B:H,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F1209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1209" s="2">
-        <f>VLOOKUP(F1209,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1209" s="1"/>
-      <c r="I1209" s="1"/>
-      <c r="J1209" s="1"/>
-      <c r="K1209" s="1"/>
-      <c r="L1209" s="1"/>
-      <c r="M1209" s="1"/>
-      <c r="N1209" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1209" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1209" s="2">
-        <f>VLOOKUP(O1209,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1210" spans="1:16">
-      <c r="A1210" s="7">
-        <v>104104</v>
-      </c>
-      <c r="B1210" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1210" s="2">
-        <f>VLOOKUP(B1210,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1210" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1210" s="2">
-        <f>VLOOKUP(D1210,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1210" s="2">
-        <f>VLOOKUP(F1210,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1210" s="1"/>
-      <c r="I1210" s="1"/>
-      <c r="J1210" s="1"/>
-      <c r="K1210" s="1"/>
-      <c r="L1210" s="1"/>
-      <c r="M1210" s="1"/>
-      <c r="N1210" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1210" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1210" s="2">
-        <f>VLOOKUP(O1210,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1211" spans="1:16">
-      <c r="A1211" s="7">
-        <v>104105</v>
-      </c>
-      <c r="B1211" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1211" s="2">
-        <f>VLOOKUP(B1211,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1211" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1211" s="2">
-        <f>VLOOKUP(D1211,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1211" s="2">
-        <f>VLOOKUP(F1211,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1211" s="1"/>
-      <c r="I1211" s="1"/>
-      <c r="J1211" s="1"/>
-      <c r="K1211" s="1"/>
-      <c r="L1211" s="1"/>
-      <c r="M1211" s="1"/>
-      <c r="N1211" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1211" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1211" s="2">
-        <f>VLOOKUP(O1211,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1212" spans="1:16">
-      <c r="A1212" s="7">
-        <v>104106</v>
-      </c>
-      <c r="B1212" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1212" s="2">
-        <f>VLOOKUP(B1212,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1212" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1212" s="2">
-        <f>VLOOKUP(D1212,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1212" s="2">
-        <f>VLOOKUP(F1212,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1212" s="1"/>
-      <c r="I1212" s="1"/>
-      <c r="J1212" s="1"/>
-      <c r="K1212" s="1"/>
-      <c r="L1212" s="1"/>
-      <c r="M1212" s="1"/>
-      <c r="N1212" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1212" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1212" s="2">
-        <f>VLOOKUP(O1212,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1213" spans="1:16">
-      <c r="A1213" s="7">
-        <v>104107</v>
-      </c>
-      <c r="B1213" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1213" s="2">
-        <f>VLOOKUP(B1213,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1213" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1213" s="2">
-        <f>VLOOKUP(D1213,Select!B:H,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F1213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1213" s="2">
-        <f>VLOOKUP(F1213,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1213" s="1"/>
-      <c r="I1213" s="1"/>
-      <c r="J1213" s="1"/>
-      <c r="K1213" s="1"/>
-      <c r="L1213" s="1"/>
-      <c r="M1213" s="1"/>
-      <c r="N1213" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1213" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1213" s="2">
-        <f>VLOOKUP(O1213,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1214" spans="1:16">
-      <c r="A1214" s="7">
-        <v>104108</v>
-      </c>
-      <c r="B1214" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1214" s="2">
-        <f>VLOOKUP(B1214,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1214" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1214" s="2">
-        <f>VLOOKUP(D1214,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1214" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1214" s="2">
-        <f>VLOOKUP(F1214,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1214" s="1"/>
-      <c r="I1214" s="1"/>
-      <c r="J1214" s="1"/>
-      <c r="K1214" s="1"/>
-      <c r="L1214" s="1"/>
-      <c r="M1214" s="1"/>
-      <c r="N1214" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1214" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1214" s="2">
-        <f>VLOOKUP(O1214,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1215" spans="1:16">
-      <c r="A1215" s="7">
-        <v>104109</v>
-      </c>
-      <c r="B1215" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1215" s="2">
-        <f>VLOOKUP(B1215,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1215" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1215" s="2">
-        <f>VLOOKUP(D1215,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1215" s="2">
-        <f>VLOOKUP(F1215,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1215" s="1"/>
-      <c r="I1215" s="1"/>
-      <c r="J1215" s="1"/>
-      <c r="K1215" s="1"/>
-      <c r="L1215" s="1"/>
-      <c r="M1215" s="1"/>
-      <c r="N1215" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1215" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1215" s="2">
-        <f>VLOOKUP(O1215,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1216" spans="1:16">
-      <c r="A1216" s="7">
-        <v>104110</v>
-      </c>
-      <c r="B1216" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1216" s="2">
-        <f>VLOOKUP(B1216,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1216" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1216" s="2">
-        <f>VLOOKUP(D1216,Select!B:H,7,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F1216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1216" s="2">
-        <f>VLOOKUP(F1216,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1216" s="1"/>
-      <c r="I1216" s="1"/>
-      <c r="J1216" s="1"/>
-      <c r="K1216" s="1"/>
-      <c r="L1216" s="1"/>
-      <c r="M1216" s="1"/>
-      <c r="N1216" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1216" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1216" s="2">
-        <f>VLOOKUP(O1216,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1217" spans="1:16">
-      <c r="A1217" s="7">
-        <v>104111</v>
-      </c>
-      <c r="B1217" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1217" s="2">
-        <f>VLOOKUP(B1217,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1217" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1217" s="2">
-        <f>VLOOKUP(D1217,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1217" s="2">
-        <f>VLOOKUP(F1217,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1217" s="1"/>
-      <c r="I1217" s="1"/>
-      <c r="J1217" s="1"/>
-      <c r="K1217" s="1"/>
-      <c r="L1217" s="1"/>
-      <c r="M1217" s="1"/>
-      <c r="N1217" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1217" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1217" s="2">
-        <f>VLOOKUP(O1217,Select!D:H,5,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1218" spans="1:16">
-      <c r="A1218" s="7">
-        <v>104112</v>
-      </c>
-      <c r="B1218" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1218" s="2">
-        <f>VLOOKUP(B1218,Select!A:H,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D1218" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1218" s="2">
-        <f>VLOOKUP(D1218,Select!B:H,7,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F1218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1218" s="2">
-        <f>VLOOKUP(F1218,Select!C:H,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H1218" s="1"/>
-      <c r="I1218" s="1"/>
-      <c r="J1218" s="1"/>
-      <c r="K1218" s="1"/>
-      <c r="L1218" s="1"/>
-      <c r="M1218" s="1"/>
-      <c r="N1218" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O1218" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="P1218" s="2">
-        <f>VLOOKUP(O1218,Select!D:H,5,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -64256,7 +59598,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B1:B1048574</xm:sqref>
+          <xm:sqref>B1:B1048490</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="6" operator="containsText" id="{4BE5AF07-632D-4617-A7D7-D144151048A8}">
@@ -64303,7 +59645,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>D1:D1048574</xm:sqref>
+          <xm:sqref>D1:D1048490</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="3" operator="containsText" id="{BBAC420F-7571-4A77-83A0-FD132E7103B9}">
@@ -64339,7 +59681,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F1:F1048574</xm:sqref>
+          <xm:sqref>F1:F1048490</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{22FD9130-A289-4A10-9801-E2DC87546FB0}">
@@ -64364,35 +59706,35 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:B1048574</xm:sqref>
+          <xm:sqref>B2:B1048490</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{43F1002D-D54F-4805-98D0-A6FEB4FD1E38}">
+          <x14:formula1>
+            <xm:f>Select!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>Q1048491:Q1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DA0901A2-180C-4E7D-95DA-66E7088258C6}">
           <x14:formula1>
             <xm:f>Select!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B1048574</xm:sqref>
+          <xm:sqref>B2:B1048490</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6D25B85E-3F98-4AD2-9F6A-938890AC8B6D}">
           <x14:formula1>
             <xm:f>Select!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D1048574</xm:sqref>
+          <xm:sqref>D2:D1048490</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C3DBEF1F-74F9-454C-944E-EB27193EBDB8}">
           <x14:formula1>
             <xm:f>Select!$C:$C</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F1048574</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{43F1002D-D54F-4805-98D0-A6FEB4FD1E38}">
-          <x14:formula1>
-            <xm:f>Select!$E:$E</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q1048575:Q1048576</xm:sqref>
+          <xm:sqref>F2:F1048490</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{24463FB5-4836-4AFC-83F3-F0C298FEF06A}">
           <x14:formula1>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Shadow\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C51B87-0260-49C3-B206-52B3E363BDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C9207C-87E0-4179-AC7B-20ADB6624099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
-    <sheet name="Select" sheetId="2" r:id="rId2"/>
+    <sheet name="メモ" sheetId="3" r:id="rId2"/>
+    <sheet name="Select" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6664" uniqueCount="1389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7249" uniqueCount="1492">
   <si>
     <t>Dragon</t>
     <phoneticPr fontId="1"/>
@@ -5629,6 +5633,426 @@
   </si>
   <si>
     <t>黄金郷の獅子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メドリングエンジェル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グラスソルジャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天よりの剣閃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>漆黒の使徒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>旅の調達</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗黒の御使い</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>真相究明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>穢れし天兵</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンパッションドミニオン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デミゴッド・ギルガメッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アフェクションドミニオン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堕天使</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従順な駿馬</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>眺望のエルフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キューティーキャット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイズベア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>森への郷愁</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>森緑のエレメンタラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴールデンインセクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>繁栄の撒き手</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エレガンスシルフィード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アローレイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロストエイジプリンセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天空妖精・アイリス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドゥルガー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>楽園妖精・アイリス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アローストーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェアリーウィスプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツインフェンサー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パレスナイト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日常の記録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>粉砕の勇士</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チーフランサー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>盤上の圧政者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気高き落涙</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷結の騎士</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気鋭の一蹴</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベイジョンマーセナリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誅戮の武者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>極彩の美剣士</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>漆黒の残光・ロサ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>漆黒の曙光・ロサ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気鋭の猛蹴</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>王城の守衛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トキシックウィッチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アーマードスノーマン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バッテリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切除の魔術師</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マーキュリーウィッチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックメイト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支配の魔女</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コールメロディー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天空の掌握</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>永生の大魔女</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エイル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>摂理の隠者・ミデロ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実装済みトークン</t>
+    <rPh sb="0" eb="3">
+      <t>ジッソウズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堕天使</t>
+    <rPh sb="0" eb="3">
+      <t>ダテンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未実装</t>
+    <rPh sb="0" eb="3">
+      <t>ミジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マジカルポーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マジカルリス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウィズダムオウル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マジカルルーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェス</t>
+  </si>
+  <si>
+    <t>スノーナイト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドスノーマン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全天の掌握</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>隠されし賢者・ミデロ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人魚の守護者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リジッドフィッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイレンスドラゴン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竜の模倣</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザードハンター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追憶の白竜</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>挑戦の代価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>流麗なる竜人</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラグジュアリーマーメイド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竜人の魚釣り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竜国の王女・イルマ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苦悶の飢餓竜</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヴァニティードラゴン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>輝竜の皇女・イルマ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白鱗のドラゴン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竜人の大物釣り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屍の討滅者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネメアの獅子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペインフルソウル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魂の具現化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死門の開通</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蘇りし邪悪</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カースドキング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪辣の残滓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンデッドスレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソウルライト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>万死の否定者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビスアベンジャー・ヴィスカリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狂恋のネクロマンサー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全死の裁定者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハートブライト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍵盤の悪鬼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イビルコレクター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開眼の魔人</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本能の乱撃</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5723,7 +6147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -5744,11 +6168,488 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="93">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE3E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2DAF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEBD8BB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE8D9F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6D5F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD1D1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCD6D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFCF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE3E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2DAF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEBD8BB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE8D9F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6D5F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD1D1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCD6D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFCF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE3E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2DAF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEBD8BB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE8D9F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6D5F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD1D1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCD6D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFCF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE3E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2DAF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEBD8BB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE8D9F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6D5F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD1D1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCD6D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCFCF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5907,16 +6808,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color indexed="64"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color indexed="64"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -5983,19 +6884,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7715D875-69E8-4A33-A479-D6F5A01629FF}" name="テーブル1" displayName="テーブル1" ref="A1:P1048485" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7715D875-69E8-4A33-A479-D6F5A01629FF}" name="テーブル1" displayName="テーブル1" ref="A1:P1048485" totalsRowShown="0" headerRowDxfId="92" headerRowBorderDxfId="90" tableBorderDxfId="91">
   <autoFilter ref="A1:P1048485" xr:uid="{7715D875-69E8-4A33-A479-D6F5A01629FF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P1048485">
     <sortCondition ref="A1:A1048485"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{65C53740-30CA-4A63-90A8-9F5F9123741B}" name="ID" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{65C53740-30CA-4A63-90A8-9F5F9123741B}" name="ID" dataDxfId="89"/>
     <tableColumn id="2" xr3:uid="{7C6067E2-AC76-4E3E-A584-F98DBF096A98}" name="SelectClass"/>
-    <tableColumn id="3" xr3:uid="{37DC34B8-0106-4FD0-B6BE-0C76585ABD10}" name="Class" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{37DC34B8-0106-4FD0-B6BE-0C76585ABD10}" name="Class" dataDxfId="88"/>
     <tableColumn id="4" xr3:uid="{CD56D3E6-1C02-4754-8150-823BCD417350}" name="SelectRarity"/>
-    <tableColumn id="5" xr3:uid="{EBD4BE3D-2144-4380-93DB-EC853C41BE35}" name="Rarity" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{EBD4BE3D-2144-4380-93DB-EC853C41BE35}" name="Rarity" dataDxfId="87"/>
     <tableColumn id="6" xr3:uid="{68873549-6BF8-429A-AE0E-E848441C5906}" name="SelectType"/>
-    <tableColumn id="7" xr3:uid="{89AF3C9D-D838-46DF-949B-10B32A793525}" name="Type" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{89AF3C9D-D838-46DF-949B-10B32A793525}" name="Type" dataDxfId="86"/>
     <tableColumn id="8" xr3:uid="{BADA85A6-736B-4460-B08D-F816275132C1}" name="Name"/>
     <tableColumn id="9" xr3:uid="{55E4AF1B-8C48-4367-B33C-754B1371A27B}" name="Cost"/>
     <tableColumn id="10" xr3:uid="{12DEE682-3513-41A5-805B-E3A94B19AC63}" name="Attack"/>
@@ -6004,7 +6905,7 @@
     <tableColumn id="13" xr3:uid="{54E266B1-6339-4384-8E7D-617503E1B8B4}" name="IllustID"/>
     <tableColumn id="14" xr3:uid="{A4351276-2D98-4869-9CCF-9150CDAE0737}" name="Token"/>
     <tableColumn id="17" xr3:uid="{563B5B48-3B7A-4856-8ADA-0E13D340275A}" name="SelectTrait"/>
-    <tableColumn id="16" xr3:uid="{E5ED9831-4A30-4C10-AE69-D47569CED6DA}" name="Trait[]" dataDxfId="17">
+    <tableColumn id="16" xr3:uid="{E5ED9831-4A30-4C10-AE69-D47569CED6DA}" name="Trait[]" dataDxfId="85">
       <calculatedColumnFormula>VLOOKUP(O2,Select!D:H,5,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6275,7 +7176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1322"/>
+  <dimension ref="A1:P1441"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7.875" style="8" bestFit="1" customWidth="1"/>
@@ -70915,6 +71816,5678 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1323" spans="1:16">
+      <c r="A1323" s="7">
+        <v>130000</v>
+      </c>
+      <c r="B1323" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1323" s="2">
+        <f>VLOOKUP(B1323,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1323" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1323" s="2">
+        <f>VLOOKUP(D1323,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1323" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1323" s="2">
+        <f>VLOOKUP(F1323,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1323" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I1323" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1323" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1323" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1323" s="1"/>
+      <c r="M1323" s="1"/>
+      <c r="N1323" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1323" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1323" s="2">
+        <f>VLOOKUP(O1323,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:16">
+      <c r="A1324" s="7">
+        <v>130001</v>
+      </c>
+      <c r="B1324" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1324" s="2">
+        <f>VLOOKUP(B1324,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1324" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1324" s="2">
+        <f>VLOOKUP(D1324,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1324" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1324" s="2">
+        <f>VLOOKUP(F1324,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1324" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I1324" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1324" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1324" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1324" s="1"/>
+      <c r="M1324" s="1"/>
+      <c r="N1324" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1324" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1324" s="2">
+        <f>VLOOKUP(O1324,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:16">
+      <c r="A1325" s="7">
+        <v>130002</v>
+      </c>
+      <c r="B1325" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1325" s="2">
+        <f>VLOOKUP(B1325,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1325" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1325" s="2">
+        <f>VLOOKUP(D1325,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1325" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1325" s="2">
+        <f>VLOOKUP(F1325,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1325" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="I1325" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1325" s="1"/>
+      <c r="K1325" s="1"/>
+      <c r="L1325" s="1"/>
+      <c r="M1325" s="1"/>
+      <c r="N1325" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1325" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1325" s="2">
+        <f>VLOOKUP(O1325,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:16">
+      <c r="A1326" s="7">
+        <v>130003</v>
+      </c>
+      <c r="B1326" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1326" s="2">
+        <f>VLOOKUP(B1326,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1326" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1326" s="2">
+        <f>VLOOKUP(D1326,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1326" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1326" s="2">
+        <f>VLOOKUP(F1326,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1326" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="I1326" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1326" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1326" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1326" s="1"/>
+      <c r="M1326" s="1"/>
+      <c r="N1326" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1326" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1326" s="2">
+        <f>VLOOKUP(O1326,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:16">
+      <c r="A1327" s="7">
+        <v>130004</v>
+      </c>
+      <c r="B1327" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1327" s="2">
+        <f>VLOOKUP(B1327,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1327" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1327" s="2">
+        <f>VLOOKUP(D1327,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1327" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1327" s="2">
+        <f>VLOOKUP(F1327,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1327" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="I1327" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1327" s="1"/>
+      <c r="K1327" s="1"/>
+      <c r="L1327" s="1"/>
+      <c r="M1327" s="1"/>
+      <c r="N1327" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1327" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1327" s="2">
+        <f>VLOOKUP(O1327,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:16">
+      <c r="A1328" s="7">
+        <v>130005</v>
+      </c>
+      <c r="B1328" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1328" s="2">
+        <f>VLOOKUP(B1328,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1328" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1328" s="2">
+        <f>VLOOKUP(D1328,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1328" s="2">
+        <f>VLOOKUP(F1328,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1328" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I1328" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1328" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1328" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1328" s="1"/>
+      <c r="M1328" s="1"/>
+      <c r="N1328" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1328" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1328" s="2">
+        <f>VLOOKUP(O1328,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:16">
+      <c r="A1329" s="7">
+        <v>130006</v>
+      </c>
+      <c r="B1329" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1329" s="2">
+        <f>VLOOKUP(B1329,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1329" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1329" s="2">
+        <f>VLOOKUP(D1329,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1329" s="2">
+        <f>VLOOKUP(F1329,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1329" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I1329" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1329" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1329" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1329" s="1"/>
+      <c r="M1329" s="1"/>
+      <c r="N1329" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1329" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1329" s="2">
+        <f>VLOOKUP(O1329,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:16">
+      <c r="A1330" s="7">
+        <v>130007</v>
+      </c>
+      <c r="B1330" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1330" s="2">
+        <f>VLOOKUP(B1330,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1330" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1330" s="2">
+        <f>VLOOKUP(D1330,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1330" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1330" s="2">
+        <f>VLOOKUP(F1330,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1330" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="I1330" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1330" s="1"/>
+      <c r="K1330" s="1"/>
+      <c r="L1330" s="1"/>
+      <c r="M1330" s="1"/>
+      <c r="N1330" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1330" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1330" s="2">
+        <f>VLOOKUP(O1330,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:16">
+      <c r="A1331" s="7">
+        <v>130008</v>
+      </c>
+      <c r="B1331" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1331" s="2">
+        <f>VLOOKUP(B1331,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1331" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1331" s="2">
+        <f>VLOOKUP(D1331,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1331" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1331" s="2">
+        <f>VLOOKUP(F1331,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1331" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="I1331" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1331" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1331" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1331" s="1"/>
+      <c r="M1331" s="1"/>
+      <c r="N1331" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1331" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1331" s="2">
+        <f>VLOOKUP(O1331,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:16">
+      <c r="A1332" s="7">
+        <v>130009</v>
+      </c>
+      <c r="B1332" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1332" s="2">
+        <f>VLOOKUP(B1332,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1332" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1332" s="2">
+        <f>VLOOKUP(D1332,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1332" s="2">
+        <f>VLOOKUP(F1332,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1332" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="I1332" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1332" s="1">
+        <v>6</v>
+      </c>
+      <c r="K1332" s="1">
+        <v>6</v>
+      </c>
+      <c r="L1332" s="1"/>
+      <c r="M1332" s="1"/>
+      <c r="N1332" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1332" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1332" s="2">
+        <f>VLOOKUP(O1332,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:16">
+      <c r="A1333" s="7">
+        <v>130010</v>
+      </c>
+      <c r="B1333" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1333" s="2">
+        <f>VLOOKUP(B1333,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1333" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1333" s="2">
+        <f>VLOOKUP(D1333,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1333" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1333" s="2">
+        <f>VLOOKUP(F1333,Select!C:H,6,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H1333" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="I1333" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1333" s="1"/>
+      <c r="K1333" s="1"/>
+      <c r="L1333" s="1"/>
+      <c r="M1333" s="1"/>
+      <c r="N1333" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1333" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1333" s="2">
+        <f>VLOOKUP(O1333,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:16">
+      <c r="A1334" s="7">
+        <v>130011</v>
+      </c>
+      <c r="B1334" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1334" s="2">
+        <f>VLOOKUP(B1334,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1334" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1334" s="2">
+        <f>VLOOKUP(D1334,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1334" s="2">
+        <f>VLOOKUP(F1334,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1334" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I1334" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1334" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1334" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1334" s="1"/>
+      <c r="M1334" s="1"/>
+      <c r="N1334" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1334" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1334" s="2">
+        <f>VLOOKUP(O1334,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:16">
+      <c r="A1335" s="7">
+        <v>130012</v>
+      </c>
+      <c r="B1335" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1335" s="2">
+        <f>VLOOKUP(B1335,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1335" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1335" s="2">
+        <f>VLOOKUP(D1335,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1335" s="2">
+        <f>VLOOKUP(F1335,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1335" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="I1335" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1335" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1335" s="1">
+        <v>5</v>
+      </c>
+      <c r="L1335" s="1"/>
+      <c r="M1335" s="1"/>
+      <c r="N1335" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1335" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1335" s="2">
+        <f>VLOOKUP(O1335,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:16">
+      <c r="A1336" s="7">
+        <v>130100</v>
+      </c>
+      <c r="B1336" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1336" s="2">
+        <f>VLOOKUP(B1336,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1336" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1336" s="2">
+        <f>VLOOKUP(D1336,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1336" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1336" s="2">
+        <f>VLOOKUP(F1336,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1336" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="I1336" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1336" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1336" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1336" s="1"/>
+      <c r="M1336" s="1"/>
+      <c r="N1336" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1336" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1336" s="2">
+        <f>VLOOKUP(O1336,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:16">
+      <c r="A1337" s="7">
+        <v>130101</v>
+      </c>
+      <c r="B1337" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1337" s="2">
+        <f>VLOOKUP(B1337,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1337" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1337" s="2">
+        <f>VLOOKUP(D1337,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1337" s="2">
+        <f>VLOOKUP(F1337,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1337" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="I1337" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1337" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1337" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1337" s="1"/>
+      <c r="M1337" s="1"/>
+      <c r="N1337" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1337" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1337" s="2">
+        <f>VLOOKUP(O1337,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:16">
+      <c r="A1338" s="7">
+        <v>130102</v>
+      </c>
+      <c r="B1338" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1338" s="2">
+        <f>VLOOKUP(B1338,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1338" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1338" s="2">
+        <f>VLOOKUP(D1338,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1338" s="2">
+        <f>VLOOKUP(F1338,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1338" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="I1338" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1338" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1338" s="1">
+        <v>4</v>
+      </c>
+      <c r="L1338" s="1"/>
+      <c r="M1338" s="1"/>
+      <c r="N1338" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1338" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1338" s="2">
+        <f>VLOOKUP(O1338,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:16">
+      <c r="A1339" s="7">
+        <v>130103</v>
+      </c>
+      <c r="B1339" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1339" s="2">
+        <f>VLOOKUP(B1339,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1339" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1339" s="2">
+        <f>VLOOKUP(D1339,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1339" s="2">
+        <f>VLOOKUP(F1339,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1339" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="I1339" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1339" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1339" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1339" s="1"/>
+      <c r="M1339" s="1"/>
+      <c r="N1339" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1339" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1339" s="2">
+        <f>VLOOKUP(O1339,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:16">
+      <c r="A1340" s="7">
+        <v>130104</v>
+      </c>
+      <c r="B1340" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1340" s="2">
+        <f>VLOOKUP(B1340,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1340" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1340" s="2">
+        <f>VLOOKUP(D1340,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1340" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1340" s="2">
+        <f>VLOOKUP(F1340,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1340" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="I1340" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1340" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1340" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1340" s="1"/>
+      <c r="M1340" s="1"/>
+      <c r="N1340" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1340" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1340" s="2">
+        <f>VLOOKUP(O1340,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:16">
+      <c r="A1341" s="7">
+        <v>130105</v>
+      </c>
+      <c r="B1341" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1341" s="2">
+        <f>VLOOKUP(B1341,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1341" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1341" s="2">
+        <f>VLOOKUP(D1341,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1341" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1341" s="2">
+        <f>VLOOKUP(F1341,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1341" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I1341" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1341" s="1"/>
+      <c r="K1341" s="1"/>
+      <c r="L1341" s="1"/>
+      <c r="M1341" s="1"/>
+      <c r="N1341" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1341" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1341" s="2">
+        <f>VLOOKUP(O1341,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:16">
+      <c r="A1342" s="7">
+        <v>130106</v>
+      </c>
+      <c r="B1342" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1342" s="2">
+        <f>VLOOKUP(B1342,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1342" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1342" s="2">
+        <f>VLOOKUP(D1342,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1342" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1342" s="2">
+        <f>VLOOKUP(F1342,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1342" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="I1342" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1342" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1342" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1342" s="1"/>
+      <c r="M1342" s="1"/>
+      <c r="N1342" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1342" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1342" s="2">
+        <f>VLOOKUP(O1342,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:16">
+      <c r="A1343" s="7">
+        <v>130107</v>
+      </c>
+      <c r="B1343" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1343" s="2">
+        <f>VLOOKUP(B1343,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1343" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1343" s="2">
+        <f>VLOOKUP(D1343,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1343" s="2">
+        <f>VLOOKUP(F1343,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1343" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="I1343" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1343" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1343" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1343" s="1"/>
+      <c r="M1343" s="1"/>
+      <c r="N1343" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1343" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1343" s="2">
+        <f>VLOOKUP(O1343,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:16">
+      <c r="A1344" s="7">
+        <v>130108</v>
+      </c>
+      <c r="B1344" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1344" s="2">
+        <f>VLOOKUP(B1344,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1344" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1344" s="2">
+        <f>VLOOKUP(D1344,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1344" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1344" s="2">
+        <f>VLOOKUP(F1344,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1344" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="I1344" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1344" s="1"/>
+      <c r="K1344" s="1"/>
+      <c r="L1344" s="1"/>
+      <c r="M1344" s="1"/>
+      <c r="N1344" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1344" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1344" s="2">
+        <f>VLOOKUP(O1344,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:16">
+      <c r="A1345" s="7">
+        <v>130109</v>
+      </c>
+      <c r="B1345" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1345" s="2">
+        <f>VLOOKUP(B1345,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1345" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1345" s="2">
+        <f>VLOOKUP(D1345,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1345" s="2">
+        <f>VLOOKUP(F1345,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1345" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="I1345" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1345" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1345" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1345" s="1"/>
+      <c r="M1345" s="1"/>
+      <c r="N1345" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1345" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1345" s="2">
+        <f>VLOOKUP(O1345,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:16">
+      <c r="A1346" s="7">
+        <v>130110</v>
+      </c>
+      <c r="B1346" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1346" s="2">
+        <f>VLOOKUP(B1346,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1346" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1346" s="2">
+        <f>VLOOKUP(D1346,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1346" s="2">
+        <f>VLOOKUP(F1346,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1346" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="I1346" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1346" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1346" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1346" s="1"/>
+      <c r="M1346" s="1"/>
+      <c r="N1346" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1346" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1346" s="2">
+        <f>VLOOKUP(O1346,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:16">
+      <c r="A1347" s="7">
+        <v>130111</v>
+      </c>
+      <c r="B1347" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1347" s="2">
+        <f>VLOOKUP(B1347,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1347" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1347" s="2">
+        <f>VLOOKUP(D1347,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1347" s="2">
+        <f>VLOOKUP(F1347,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1347" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="I1347" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1347" s="1">
+        <v>6</v>
+      </c>
+      <c r="K1347" s="1">
+        <v>6</v>
+      </c>
+      <c r="L1347" s="1"/>
+      <c r="M1347" s="1"/>
+      <c r="N1347" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1347" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1347" s="2">
+        <f>VLOOKUP(O1347,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:16">
+      <c r="A1348" s="7">
+        <v>130112</v>
+      </c>
+      <c r="B1348" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1348" s="2">
+        <f>VLOOKUP(B1348,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1348" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1348" s="2">
+        <f>VLOOKUP(D1348,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1348" s="2">
+        <f>VLOOKUP(F1348,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1348" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="I1348" s="1">
+        <v>0</v>
+      </c>
+      <c r="J1348" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1348" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1348" s="1"/>
+      <c r="M1348" s="1"/>
+      <c r="N1348" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1348" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1348" s="2">
+        <f>VLOOKUP(O1348,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:16">
+      <c r="A1349" s="7">
+        <v>130113</v>
+      </c>
+      <c r="B1349" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1349" s="2">
+        <f>VLOOKUP(B1349,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1349" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1349" s="2">
+        <f>VLOOKUP(D1349,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1349" s="2">
+        <f>VLOOKUP(F1349,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1349" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="I1349" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1349" s="1"/>
+      <c r="K1349" s="1"/>
+      <c r="L1349" s="1"/>
+      <c r="M1349" s="1"/>
+      <c r="N1349" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1349" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1349" s="2">
+        <f>VLOOKUP(O1349,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:16">
+      <c r="A1350" s="7">
+        <v>130114</v>
+      </c>
+      <c r="B1350" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1350" s="2">
+        <f>VLOOKUP(B1350,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1350" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1350" s="2">
+        <f>VLOOKUP(D1350,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1350" s="2">
+        <f>VLOOKUP(F1350,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1350" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I1350" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1350" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1350" s="1">
+        <v>4</v>
+      </c>
+      <c r="L1350" s="1"/>
+      <c r="M1350" s="1"/>
+      <c r="N1350" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1350" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1350" s="2">
+        <f>VLOOKUP(O1350,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:16">
+      <c r="A1351" s="7">
+        <v>130115</v>
+      </c>
+      <c r="B1351" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1351" s="2">
+        <f>VLOOKUP(B1351,Select!A:H,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D1351" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1351" s="2">
+        <f>VLOOKUP(D1351,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1351" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1351" s="2">
+        <f>VLOOKUP(F1351,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1351" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="I1351" s="1">
+        <v>0</v>
+      </c>
+      <c r="J1351" s="1"/>
+      <c r="K1351" s="1"/>
+      <c r="L1351" s="1"/>
+      <c r="M1351" s="1"/>
+      <c r="N1351" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1351" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1351" s="2">
+        <f>VLOOKUP(O1351,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:16">
+      <c r="A1352" s="7">
+        <v>130200</v>
+      </c>
+      <c r="B1352" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1352" s="2">
+        <f>VLOOKUP(B1352,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1352" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1352" s="2">
+        <f>VLOOKUP(D1352,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1352" s="2">
+        <f>VLOOKUP(F1352,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1352" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="I1352" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1352" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1352" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1352" s="1"/>
+      <c r="M1352" s="1"/>
+      <c r="N1352" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1352" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P1352" s="2">
+        <f>VLOOKUP(O1352,Select!D:H,5,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:16">
+      <c r="A1353" s="7">
+        <v>130201</v>
+      </c>
+      <c r="B1353" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1353" s="2">
+        <f>VLOOKUP(B1353,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1353" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1353" s="2">
+        <f>VLOOKUP(D1353,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1353" s="2">
+        <f>VLOOKUP(F1353,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1353" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="I1353" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1353" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1353" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1353" s="1"/>
+      <c r="M1353" s="1"/>
+      <c r="N1353" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1353" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P1353" s="2">
+        <f>VLOOKUP(O1353,Select!D:H,5,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:16">
+      <c r="A1354" s="7">
+        <v>130202</v>
+      </c>
+      <c r="B1354" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1354" s="2">
+        <f>VLOOKUP(B1354,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1354" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1354" s="2">
+        <f>VLOOKUP(D1354,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1354" s="2">
+        <f>VLOOKUP(F1354,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1354" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I1354" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1354" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1354" s="1">
+        <v>6</v>
+      </c>
+      <c r="L1354" s="1"/>
+      <c r="M1354" s="1"/>
+      <c r="N1354" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1354" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P1354" s="2">
+        <f>VLOOKUP(O1354,Select!D:H,5,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:16">
+      <c r="A1355" s="7">
+        <v>130203</v>
+      </c>
+      <c r="B1355" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1355" s="2">
+        <f>VLOOKUP(B1355,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1355" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1355" s="2">
+        <f>VLOOKUP(D1355,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1355" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1355" s="2">
+        <f>VLOOKUP(F1355,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1355" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I1355" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1355" s="1"/>
+      <c r="K1355" s="1"/>
+      <c r="L1355" s="1"/>
+      <c r="M1355" s="1"/>
+      <c r="N1355" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1355" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1355" s="2">
+        <f>VLOOKUP(O1355,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:16">
+      <c r="A1356" s="7">
+        <v>130204</v>
+      </c>
+      <c r="B1356" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1356" s="2">
+        <f>VLOOKUP(B1356,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1356" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1356" s="2">
+        <f>VLOOKUP(D1356,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1356" s="2">
+        <f>VLOOKUP(F1356,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1356" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="I1356" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1356" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1356" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1356" s="1"/>
+      <c r="M1356" s="1"/>
+      <c r="N1356" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1356" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="P1356" s="2">
+        <f>VLOOKUP(O1356,Select!D:H,5,FALSE)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:16">
+      <c r="A1357" s="7">
+        <v>130205</v>
+      </c>
+      <c r="B1357" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1357" s="2">
+        <f>VLOOKUP(B1357,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1357" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1357" s="2">
+        <f>VLOOKUP(D1357,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1357" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1357" s="2">
+        <f>VLOOKUP(F1357,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1357" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="I1357" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1357" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1357" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1357" s="1"/>
+      <c r="M1357" s="1"/>
+      <c r="N1357" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1357" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="P1357" s="2">
+        <f>VLOOKUP(O1357,Select!D:H,5,FALSE)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:16">
+      <c r="A1358" s="7">
+        <v>130206</v>
+      </c>
+      <c r="B1358" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1358" s="2">
+        <f>VLOOKUP(B1358,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1358" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1358" s="2">
+        <f>VLOOKUP(D1358,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1358" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1358" s="2">
+        <f>VLOOKUP(F1358,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1358" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="I1358" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1358" s="1"/>
+      <c r="K1358" s="1"/>
+      <c r="L1358" s="1"/>
+      <c r="M1358" s="1"/>
+      <c r="N1358" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1358" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1358" s="2">
+        <f>VLOOKUP(O1358,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:16">
+      <c r="A1359" s="7">
+        <v>130207</v>
+      </c>
+      <c r="B1359" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1359" s="2">
+        <f>VLOOKUP(B1359,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1359" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1359" s="2">
+        <f>VLOOKUP(D1359,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1359" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1359" s="2">
+        <f>VLOOKUP(F1359,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1359" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="I1359" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1359" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1359" s="1">
+        <v>4</v>
+      </c>
+      <c r="L1359" s="1"/>
+      <c r="M1359" s="1"/>
+      <c r="N1359" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1359" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P1359" s="2">
+        <f>VLOOKUP(O1359,Select!D:H,5,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:16">
+      <c r="A1360" s="7">
+        <v>130208</v>
+      </c>
+      <c r="B1360" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1360" s="2">
+        <f>VLOOKUP(B1360,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1360" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1360" s="2">
+        <f>VLOOKUP(D1360,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1360" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1360" s="2">
+        <f>VLOOKUP(F1360,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1360" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="I1360" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1360" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1360" s="1">
+        <v>5</v>
+      </c>
+      <c r="L1360" s="1"/>
+      <c r="M1360" s="1"/>
+      <c r="N1360" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1360" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P1360" s="2">
+        <f>VLOOKUP(O1360,Select!D:H,5,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:16">
+      <c r="A1361" s="7">
+        <v>130209</v>
+      </c>
+      <c r="B1361" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1361" s="2">
+        <f>VLOOKUP(B1361,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1361" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1361" s="2">
+        <f>VLOOKUP(D1361,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1361" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1361" s="2">
+        <f>VLOOKUP(F1361,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1361" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="I1361" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1361" s="1"/>
+      <c r="K1361" s="1"/>
+      <c r="L1361" s="1"/>
+      <c r="M1361" s="1"/>
+      <c r="N1361" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1361" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1361" s="2">
+        <f>VLOOKUP(O1361,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:16">
+      <c r="A1362" s="7">
+        <v>130210</v>
+      </c>
+      <c r="B1362" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1362" s="2">
+        <f>VLOOKUP(B1362,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1362" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1362" s="2">
+        <f>VLOOKUP(D1362,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1362" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1362" s="2">
+        <f>VLOOKUP(F1362,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1362" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I1362" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1362" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1362" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1362" s="1"/>
+      <c r="M1362" s="1"/>
+      <c r="N1362" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1362" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P1362" s="2">
+        <f>VLOOKUP(O1362,Select!D:H,5,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:16">
+      <c r="A1363" s="7">
+        <v>130211</v>
+      </c>
+      <c r="B1363" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1363" s="2">
+        <f>VLOOKUP(B1363,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1363" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1363" s="2">
+        <f>VLOOKUP(D1363,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1363" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1363" s="2">
+        <f>VLOOKUP(F1363,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1363" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="I1363" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1363" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1363" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1363" s="1"/>
+      <c r="M1363" s="1"/>
+      <c r="N1363" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1363" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="P1363" s="2">
+        <f>VLOOKUP(O1363,Select!D:H,5,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:16">
+      <c r="A1364" s="7">
+        <v>130212</v>
+      </c>
+      <c r="B1364" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1364" s="2">
+        <f>VLOOKUP(B1364,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1364" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1364" s="2">
+        <f>VLOOKUP(D1364,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1364" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1364" s="2">
+        <f>VLOOKUP(F1364,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1364" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="I1364" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1364" s="1">
+        <v>6</v>
+      </c>
+      <c r="K1364" s="1">
+        <v>6</v>
+      </c>
+      <c r="L1364" s="1"/>
+      <c r="M1364" s="1"/>
+      <c r="N1364" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1364" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="P1364" s="2">
+        <f>VLOOKUP(O1364,Select!D:H,5,FALSE)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:16">
+      <c r="A1365" s="7">
+        <v>130213</v>
+      </c>
+      <c r="B1365" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1365" s="2">
+        <f>VLOOKUP(B1365,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1365" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1365" s="2">
+        <f>VLOOKUP(D1365,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1365" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1365" s="2">
+        <f>VLOOKUP(F1365,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1365" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="I1365" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1365" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1365" s="1">
+        <v>6</v>
+      </c>
+      <c r="L1365" s="1"/>
+      <c r="M1365" s="1"/>
+      <c r="N1365" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1365" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1365" s="2">
+        <f>VLOOKUP(O1365,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:16">
+      <c r="A1366" s="7">
+        <v>130214</v>
+      </c>
+      <c r="B1366" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1366" s="2">
+        <f>VLOOKUP(B1366,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1366" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1366" s="2">
+        <f>VLOOKUP(D1366,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1366" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1366" s="2">
+        <f>VLOOKUP(F1366,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1366" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1366" s="1">
+        <v>0</v>
+      </c>
+      <c r="J1366" s="1"/>
+      <c r="K1366" s="1"/>
+      <c r="L1366" s="1"/>
+      <c r="M1366" s="1"/>
+      <c r="N1366" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1366" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1366" s="2">
+        <f>VLOOKUP(O1366,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:16">
+      <c r="A1367" s="7">
+        <v>130215</v>
+      </c>
+      <c r="B1367" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1367" s="2">
+        <f>VLOOKUP(B1367,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1367" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1367" s="2">
+        <f>VLOOKUP(D1367,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1367" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1367" s="2">
+        <f>VLOOKUP(F1367,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1367" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I1367" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1367" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1367" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1367" s="1"/>
+      <c r="M1367" s="1"/>
+      <c r="N1367" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1367" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="P1367" s="2">
+        <f>VLOOKUP(O1367,Select!D:H,5,FALSE)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:16">
+      <c r="A1368" s="7">
+        <v>130216</v>
+      </c>
+      <c r="B1368" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1368" s="2">
+        <f>VLOOKUP(B1368,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1368" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1368" s="2">
+        <f>VLOOKUP(D1368,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1368" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1368" s="2">
+        <f>VLOOKUP(F1368,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1368" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I1368" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1368" s="1"/>
+      <c r="K1368" s="1"/>
+      <c r="L1368" s="1"/>
+      <c r="M1368" s="1"/>
+      <c r="N1368" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1368" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1368" s="2">
+        <f>VLOOKUP(O1368,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:16">
+      <c r="A1369" s="7">
+        <v>130217</v>
+      </c>
+      <c r="B1369" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1369" s="2">
+        <f>VLOOKUP(B1369,Select!A:H,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D1369" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1369" s="2">
+        <f>VLOOKUP(D1369,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1369" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1369" s="2">
+        <f>VLOOKUP(F1369,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1369" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I1369" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1369" s="1"/>
+      <c r="K1369" s="1"/>
+      <c r="L1369" s="1"/>
+      <c r="M1369" s="1"/>
+      <c r="N1369" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1369" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1369" s="2">
+        <f>VLOOKUP(O1369,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:16">
+      <c r="A1370" s="7">
+        <v>130300</v>
+      </c>
+      <c r="B1370" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1370" s="2">
+        <f>VLOOKUP(B1370,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1370" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1370" s="2">
+        <f>VLOOKUP(D1370,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1370" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1370" s="2">
+        <f>VLOOKUP(F1370,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1370" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="I1370" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1370" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1370" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1370" s="1"/>
+      <c r="M1370" s="1"/>
+      <c r="N1370" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1370" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1370" s="2">
+        <f>VLOOKUP(O1370,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:16">
+      <c r="A1371" s="7">
+        <v>130301</v>
+      </c>
+      <c r="B1371" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1371" s="2">
+        <f>VLOOKUP(B1371,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1371" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1371" s="2">
+        <f>VLOOKUP(D1371,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1371" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1371" s="2">
+        <f>VLOOKUP(F1371,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1371" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I1371" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1371" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1371" s="1">
+        <v>8</v>
+      </c>
+      <c r="L1371" s="1"/>
+      <c r="M1371" s="1"/>
+      <c r="N1371" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1371" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1371" s="2">
+        <f>VLOOKUP(O1371,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:16">
+      <c r="A1372" s="7">
+        <v>130302</v>
+      </c>
+      <c r="B1372" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1372" s="2">
+        <f>VLOOKUP(B1372,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1372" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1372" s="2">
+        <f>VLOOKUP(D1372,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1372" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1372" s="2">
+        <f>VLOOKUP(F1372,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1372" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="I1372" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1372" s="1"/>
+      <c r="K1372" s="1"/>
+      <c r="L1372" s="1"/>
+      <c r="M1372" s="1"/>
+      <c r="N1372" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1372" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1372" s="2">
+        <f>VLOOKUP(O1372,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:16">
+      <c r="A1373" s="7">
+        <v>130303</v>
+      </c>
+      <c r="B1373" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1373" s="2">
+        <f>VLOOKUP(B1373,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1373" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1373" s="2">
+        <f>VLOOKUP(D1373,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1373" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1373" s="2">
+        <f>VLOOKUP(F1373,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1373" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I1373" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1373" s="1"/>
+      <c r="K1373" s="1"/>
+      <c r="L1373" s="1"/>
+      <c r="M1373" s="1"/>
+      <c r="N1373" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1373" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1373" s="2">
+        <f>VLOOKUP(O1373,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:16">
+      <c r="A1374" s="7">
+        <v>130304</v>
+      </c>
+      <c r="B1374" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1374" s="2">
+        <f>VLOOKUP(B1374,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1374" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1374" s="2">
+        <f>VLOOKUP(D1374,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1374" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1374" s="2">
+        <f>VLOOKUP(F1374,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1374" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="I1374" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1374" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1374" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1374" s="1"/>
+      <c r="M1374" s="1"/>
+      <c r="N1374" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1374" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1374" s="2">
+        <f>VLOOKUP(O1374,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:16">
+      <c r="A1375" s="7">
+        <v>130305</v>
+      </c>
+      <c r="B1375" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1375" s="2">
+        <f>VLOOKUP(B1375,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1375" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1375" s="2">
+        <f>VLOOKUP(D1375,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1375" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1375" s="2">
+        <f>VLOOKUP(F1375,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1375" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="I1375" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1375" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1375" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1375" s="1"/>
+      <c r="M1375" s="1"/>
+      <c r="N1375" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1375" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1375" s="2">
+        <f>VLOOKUP(O1375,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:16">
+      <c r="A1376" s="7">
+        <v>130306</v>
+      </c>
+      <c r="B1376" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1376" s="2">
+        <f>VLOOKUP(B1376,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1376" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1376" s="2">
+        <f>VLOOKUP(D1376,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1376" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1376" s="2">
+        <f>VLOOKUP(F1376,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1376" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="I1376" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1376" s="1"/>
+      <c r="K1376" s="1"/>
+      <c r="L1376" s="1"/>
+      <c r="M1376" s="1"/>
+      <c r="N1376" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1376" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1376" s="2">
+        <f>VLOOKUP(O1376,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:16">
+      <c r="A1377" s="7">
+        <v>130307</v>
+      </c>
+      <c r="B1377" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1377" s="2">
+        <f>VLOOKUP(B1377,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1377" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1377" s="2">
+        <f>VLOOKUP(D1377,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1377" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1377" s="2">
+        <f>VLOOKUP(F1377,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1377" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="I1377" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1377" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1377" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1377" s="1"/>
+      <c r="M1377" s="1"/>
+      <c r="N1377" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1377" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1377" s="2">
+        <f>VLOOKUP(O1377,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:16">
+      <c r="A1378" s="7">
+        <v>130308</v>
+      </c>
+      <c r="B1378" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1378" s="2">
+        <f>VLOOKUP(B1378,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1378" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1378" s="2">
+        <f>VLOOKUP(D1378,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1378" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1378" s="2">
+        <f>VLOOKUP(F1378,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1378" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I1378" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1378" s="1"/>
+      <c r="K1378" s="1"/>
+      <c r="L1378" s="1"/>
+      <c r="M1378" s="1"/>
+      <c r="N1378" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1378" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1378" s="2">
+        <f>VLOOKUP(O1378,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:16">
+      <c r="A1379" s="7">
+        <v>130309</v>
+      </c>
+      <c r="B1379" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1379" s="2">
+        <f>VLOOKUP(B1379,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1379" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1379" s="2">
+        <f>VLOOKUP(D1379,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1379" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1379" s="2">
+        <f>VLOOKUP(F1379,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1379" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="I1379" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1379" s="1"/>
+      <c r="K1379" s="1"/>
+      <c r="L1379" s="1"/>
+      <c r="M1379" s="1"/>
+      <c r="N1379" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1379" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1379" s="2">
+        <f>VLOOKUP(O1379,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:16">
+      <c r="A1380" s="7">
+        <v>130310</v>
+      </c>
+      <c r="B1380" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1380" s="2">
+        <f>VLOOKUP(B1380,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1380" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1380" s="2">
+        <f>VLOOKUP(D1380,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1380" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1380" s="2">
+        <f>VLOOKUP(F1380,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1380" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="I1380" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1380" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1380" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1380" s="1"/>
+      <c r="M1380" s="1"/>
+      <c r="N1380" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1380" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1380" s="2">
+        <f>VLOOKUP(O1380,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:16">
+      <c r="A1381" s="7">
+        <v>130311</v>
+      </c>
+      <c r="B1381" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1381" s="2">
+        <f>VLOOKUP(B1381,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1381" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1381" s="2">
+        <f>VLOOKUP(D1381,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1381" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1381" s="2">
+        <f>VLOOKUP(F1381,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1381" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I1381" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1381" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1381" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1381" s="1"/>
+      <c r="M1381" s="1"/>
+      <c r="N1381" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1381" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1381" s="2">
+        <f>VLOOKUP(O1381,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:16">
+      <c r="A1382" s="7">
+        <v>130312</v>
+      </c>
+      <c r="B1382" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1382" s="2">
+        <f>VLOOKUP(B1382,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1382" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1382" s="2">
+        <f>VLOOKUP(D1382,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1382" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1382" s="2">
+        <f>VLOOKUP(F1382,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1382" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="I1382" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1382" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1382" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1382" s="1"/>
+      <c r="M1382" s="1"/>
+      <c r="N1382" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1382" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1382" s="2">
+        <f>VLOOKUP(O1382,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:16">
+      <c r="A1383" s="7">
+        <v>130313</v>
+      </c>
+      <c r="B1383" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1383" s="2">
+        <f>VLOOKUP(B1383,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1383" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1383" s="2">
+        <f>VLOOKUP(D1383,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1383" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1383" s="2">
+        <f>VLOOKUP(F1383,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1383" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I1383" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1383" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1383" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1383" s="1"/>
+      <c r="M1383" s="1"/>
+      <c r="N1383" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1383" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="P1383" s="2">
+        <f>VLOOKUP(O1383,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:16">
+      <c r="A1384" s="7">
+        <v>130314</v>
+      </c>
+      <c r="B1384" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1384" s="2">
+        <f>VLOOKUP(B1384,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1384" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1384" s="2">
+        <f>VLOOKUP(D1384,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1384" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1384" s="2">
+        <f>VLOOKUP(F1384,Select!C:H,6,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H1384" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1384" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1384" s="1"/>
+      <c r="K1384" s="1"/>
+      <c r="L1384" s="1"/>
+      <c r="M1384" s="1"/>
+      <c r="N1384" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1384" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="P1384" s="2">
+        <f>VLOOKUP(O1384,Select!D:H,5,FALSE)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:16">
+      <c r="A1385" s="7">
+        <v>130315</v>
+      </c>
+      <c r="B1385" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1385" s="2">
+        <f>VLOOKUP(B1385,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1385" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1385" s="2">
+        <f>VLOOKUP(D1385,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1385" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1385" s="2">
+        <f>VLOOKUP(F1385,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1385" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="I1385" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1385" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1385" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1385" s="1"/>
+      <c r="M1385" s="1"/>
+      <c r="N1385" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1385" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1385" s="2">
+        <f>VLOOKUP(O1385,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:16">
+      <c r="A1386" s="7">
+        <v>130316</v>
+      </c>
+      <c r="B1386" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1386" s="2">
+        <f>VLOOKUP(B1386,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1386" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1386" s="2">
+        <f>VLOOKUP(D1386,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1386" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1386" s="2">
+        <f>VLOOKUP(F1386,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1386" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="I1386" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1386" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1386" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1386" s="1"/>
+      <c r="M1386" s="1"/>
+      <c r="N1386" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1386" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1386" s="2">
+        <f>VLOOKUP(O1386,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:16">
+      <c r="A1387" s="7">
+        <v>130317</v>
+      </c>
+      <c r="B1387" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1387" s="2">
+        <f>VLOOKUP(B1387,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1387" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1387" s="2">
+        <f>VLOOKUP(D1387,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1387" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1387" s="2">
+        <f>VLOOKUP(F1387,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1387" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1387" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1387" s="1"/>
+      <c r="K1387" s="1"/>
+      <c r="L1387" s="1"/>
+      <c r="M1387" s="1"/>
+      <c r="N1387" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1387" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1387" s="2">
+        <f>VLOOKUP(O1387,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:16">
+      <c r="A1388" s="7">
+        <v>130318</v>
+      </c>
+      <c r="B1388" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1388" s="2">
+        <f>VLOOKUP(B1388,Select!A:H,8,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D1388" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1388" s="2">
+        <f>VLOOKUP(D1388,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1388" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1388" s="2">
+        <f>VLOOKUP(F1388,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1388" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I1388" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1388" s="1">
+        <v>7</v>
+      </c>
+      <c r="K1388" s="1">
+        <v>7</v>
+      </c>
+      <c r="L1388" s="1"/>
+      <c r="M1388" s="1"/>
+      <c r="N1388" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1388" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1388" s="2">
+        <f>VLOOKUP(O1388,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:16">
+      <c r="A1389" s="7">
+        <v>130400</v>
+      </c>
+      <c r="B1389" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1389" s="2">
+        <f>VLOOKUP(B1389,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1389" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1389" s="2">
+        <f>VLOOKUP(D1389,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1389" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1389" s="2">
+        <f>VLOOKUP(F1389,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1389" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="I1389" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1389" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1389" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1389" s="1"/>
+      <c r="M1389" s="1"/>
+      <c r="N1389" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1389" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1389" s="2">
+        <f>VLOOKUP(O1389,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:16">
+      <c r="A1390" s="7">
+        <v>130401</v>
+      </c>
+      <c r="B1390" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1390" s="2">
+        <f>VLOOKUP(B1390,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1390" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1390" s="2">
+        <f>VLOOKUP(D1390,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1390" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1390" s="2">
+        <f>VLOOKUP(F1390,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1390" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="I1390" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1390" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1390" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1390" s="1"/>
+      <c r="M1390" s="1"/>
+      <c r="N1390" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1390" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1390" s="2">
+        <f>VLOOKUP(O1390,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:16">
+      <c r="A1391" s="7">
+        <v>130402</v>
+      </c>
+      <c r="B1391" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1391" s="2">
+        <f>VLOOKUP(B1391,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1391" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1391" s="2">
+        <f>VLOOKUP(D1391,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1391" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1391" s="2">
+        <f>VLOOKUP(F1391,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1391" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="I1391" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1391" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1391" s="1">
+        <v>7</v>
+      </c>
+      <c r="L1391" s="1"/>
+      <c r="M1391" s="1"/>
+      <c r="N1391" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1391" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1391" s="2">
+        <f>VLOOKUP(O1391,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:16">
+      <c r="A1392" s="7">
+        <v>130403</v>
+      </c>
+      <c r="B1392" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1392" s="2">
+        <f>VLOOKUP(B1392,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1392" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1392" s="2">
+        <f>VLOOKUP(D1392,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1392" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1392" s="2">
+        <f>VLOOKUP(F1392,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1392" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="I1392" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1392" s="1"/>
+      <c r="K1392" s="1"/>
+      <c r="L1392" s="1"/>
+      <c r="M1392" s="1"/>
+      <c r="N1392" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1392" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1392" s="2">
+        <f>VLOOKUP(O1392,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:16">
+      <c r="A1393" s="7">
+        <v>130404</v>
+      </c>
+      <c r="B1393" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1393" s="2">
+        <f>VLOOKUP(B1393,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1393" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1393" s="2">
+        <f>VLOOKUP(D1393,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1393" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1393" s="2">
+        <f>VLOOKUP(F1393,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1393" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="I1393" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1393" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1393" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1393" s="1"/>
+      <c r="M1393" s="1"/>
+      <c r="N1393" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1393" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1393" s="2">
+        <f>VLOOKUP(O1393,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:16">
+      <c r="A1394" s="7">
+        <v>130405</v>
+      </c>
+      <c r="B1394" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1394" s="2">
+        <f>VLOOKUP(B1394,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1394" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1394" s="2">
+        <f>VLOOKUP(D1394,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1394" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1394" s="2">
+        <f>VLOOKUP(F1394,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1394" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I1394" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1394" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1394" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1394" s="1"/>
+      <c r="M1394" s="1"/>
+      <c r="N1394" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1394" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1394" s="2">
+        <f>VLOOKUP(O1394,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:16">
+      <c r="A1395" s="7">
+        <v>130406</v>
+      </c>
+      <c r="B1395" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1395" s="2">
+        <f>VLOOKUP(B1395,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1395" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1395" s="2">
+        <f>VLOOKUP(D1395,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1395" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1395" s="2">
+        <f>VLOOKUP(F1395,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1395" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I1395" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1395" s="1"/>
+      <c r="K1395" s="1"/>
+      <c r="L1395" s="1"/>
+      <c r="M1395" s="1"/>
+      <c r="N1395" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1395" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1395" s="2">
+        <f>VLOOKUP(O1395,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:16">
+      <c r="A1396" s="7">
+        <v>130407</v>
+      </c>
+      <c r="B1396" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1396" s="2">
+        <f>VLOOKUP(B1396,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1396" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1396" s="2">
+        <f>VLOOKUP(D1396,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1396" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1396" s="2">
+        <f>VLOOKUP(F1396,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1396" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="I1396" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1396" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1396" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1396" s="1"/>
+      <c r="M1396" s="1"/>
+      <c r="N1396" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1396" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="P1396" s="2">
+        <f>VLOOKUP(O1396,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:16">
+      <c r="A1397" s="7">
+        <v>130408</v>
+      </c>
+      <c r="B1397" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1397" s="2">
+        <f>VLOOKUP(B1397,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1397" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1397" s="2">
+        <f>VLOOKUP(D1397,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1397" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1397" s="2">
+        <f>VLOOKUP(F1397,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1397" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I1397" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1397" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1397" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1397" s="1"/>
+      <c r="M1397" s="1"/>
+      <c r="N1397" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1397" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1397" s="2">
+        <f>VLOOKUP(O1397,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:16">
+      <c r="A1398" s="7">
+        <v>130409</v>
+      </c>
+      <c r="B1398" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1398" s="2">
+        <f>VLOOKUP(B1398,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1398" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1398" s="2">
+        <f>VLOOKUP(D1398,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1398" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1398" s="2">
+        <f>VLOOKUP(F1398,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1398" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="I1398" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1398" s="1"/>
+      <c r="K1398" s="1"/>
+      <c r="L1398" s="1"/>
+      <c r="M1398" s="1"/>
+      <c r="N1398" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1398" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1398" s="2">
+        <f>VLOOKUP(O1398,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:16">
+      <c r="A1399" s="7">
+        <v>130410</v>
+      </c>
+      <c r="B1399" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1399" s="2">
+        <f>VLOOKUP(B1399,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1399" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1399" s="2">
+        <f>VLOOKUP(D1399,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1399" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1399" s="2">
+        <f>VLOOKUP(F1399,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1399" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I1399" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1399" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1399" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1399" s="1"/>
+      <c r="M1399" s="1"/>
+      <c r="N1399" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1399" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1399" s="2">
+        <f>VLOOKUP(O1399,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:16">
+      <c r="A1400" s="7">
+        <v>130411</v>
+      </c>
+      <c r="B1400" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1400" s="2">
+        <f>VLOOKUP(B1400,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1400" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1400" s="2">
+        <f>VLOOKUP(D1400,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1400" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1400" s="2">
+        <f>VLOOKUP(F1400,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1400" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="I1400" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1400" s="1">
+        <v>10</v>
+      </c>
+      <c r="K1400" s="1">
+        <v>5</v>
+      </c>
+      <c r="L1400" s="1"/>
+      <c r="M1400" s="1"/>
+      <c r="N1400" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1400" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1400" s="2">
+        <f>VLOOKUP(O1400,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:16">
+      <c r="A1401" s="7">
+        <v>130412</v>
+      </c>
+      <c r="B1401" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1401" s="2">
+        <f>VLOOKUP(B1401,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1401" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1401" s="2">
+        <f>VLOOKUP(D1401,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1401" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1401" s="2">
+        <f>VLOOKUP(F1401,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1401" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="I1401" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1401" s="1">
+        <v>6</v>
+      </c>
+      <c r="K1401" s="1">
+        <v>8</v>
+      </c>
+      <c r="L1401" s="1"/>
+      <c r="M1401" s="1"/>
+      <c r="N1401" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1401" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1401" s="2">
+        <f>VLOOKUP(O1401,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:16">
+      <c r="A1402" s="7">
+        <v>130413</v>
+      </c>
+      <c r="B1402" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1402" s="2">
+        <f>VLOOKUP(B1402,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1402" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1402" s="2">
+        <f>VLOOKUP(D1402,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1402" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1402" s="2">
+        <f>VLOOKUP(F1402,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1402" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="I1402" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1402" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1402" s="1">
+        <v>7</v>
+      </c>
+      <c r="L1402" s="1"/>
+      <c r="M1402" s="1"/>
+      <c r="N1402" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1402" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1402" s="2">
+        <f>VLOOKUP(O1402,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:16">
+      <c r="A1403" s="7">
+        <v>130414</v>
+      </c>
+      <c r="B1403" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1403" s="2">
+        <f>VLOOKUP(B1403,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1403" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1403" s="2">
+        <f>VLOOKUP(D1403,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1403" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1403" s="2">
+        <f>VLOOKUP(F1403,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1403" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I1403" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1403" s="1"/>
+      <c r="K1403" s="1"/>
+      <c r="L1403" s="1"/>
+      <c r="M1403" s="1"/>
+      <c r="N1403" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1403" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1403" s="2">
+        <f>VLOOKUP(O1403,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:16">
+      <c r="A1404" s="7">
+        <v>130415</v>
+      </c>
+      <c r="B1404" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1404" s="2">
+        <f>VLOOKUP(B1404,Select!A:H,8,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D1404" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1404" s="2">
+        <f>VLOOKUP(D1404,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1404" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1404" s="2">
+        <f>VLOOKUP(F1404,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1404" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I1404" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1404" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1404" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1404" s="1"/>
+      <c r="M1404" s="1"/>
+      <c r="N1404" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O1404" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1404" s="2">
+        <f>VLOOKUP(O1404,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:16">
+      <c r="A1405" s="7">
+        <v>130500</v>
+      </c>
+      <c r="B1405" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1405" s="2">
+        <f>VLOOKUP(B1405,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1405" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1405" s="2">
+        <f>VLOOKUP(D1405,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1405" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1405" s="2">
+        <f>VLOOKUP(F1405,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1405" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="I1405" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1405" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1405" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1405" s="1"/>
+      <c r="M1405" s="1"/>
+      <c r="N1405" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1405" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1405" s="2">
+        <f>VLOOKUP(O1405,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:16">
+      <c r="A1406" s="7">
+        <v>130501</v>
+      </c>
+      <c r="B1406" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1406" s="2">
+        <f>VLOOKUP(B1406,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1406" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1406" s="2">
+        <f>VLOOKUP(D1406,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1406" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1406" s="2">
+        <f>VLOOKUP(F1406,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1406" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="I1406" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1406" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1406" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1406" s="1"/>
+      <c r="M1406" s="1"/>
+      <c r="N1406" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1406" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1406" s="2">
+        <f>VLOOKUP(O1406,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:16">
+      <c r="A1407" s="7">
+        <v>130502</v>
+      </c>
+      <c r="B1407" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1407" s="2">
+        <f>VLOOKUP(B1407,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1407" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1407" s="2">
+        <f>VLOOKUP(D1407,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1407" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1407" s="2">
+        <f>VLOOKUP(F1407,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1407" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="I1407" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1407" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1407" s="1">
+        <v>3</v>
+      </c>
+      <c r="L1407" s="1"/>
+      <c r="M1407" s="1"/>
+      <c r="N1407" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1407" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1407" s="2">
+        <f>VLOOKUP(O1407,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:16">
+      <c r="A1408" s="7">
+        <v>130503</v>
+      </c>
+      <c r="B1408" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1408" s="2">
+        <f>VLOOKUP(B1408,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1408" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1408" s="2">
+        <f>VLOOKUP(D1408,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1408" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1408" s="2">
+        <f>VLOOKUP(F1408,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1408" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="I1408" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1408" s="1"/>
+      <c r="K1408" s="1"/>
+      <c r="L1408" s="1"/>
+      <c r="M1408" s="1"/>
+      <c r="N1408" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1408" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1408" s="2">
+        <f>VLOOKUP(O1408,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:16">
+      <c r="A1409" s="7">
+        <v>130504</v>
+      </c>
+      <c r="B1409" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1409" s="2">
+        <f>VLOOKUP(B1409,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1409" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1409" s="2">
+        <f>VLOOKUP(D1409,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1409" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1409" s="2">
+        <f>VLOOKUP(F1409,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1409" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I1409" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1409" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1409" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1409" s="1"/>
+      <c r="M1409" s="1"/>
+      <c r="N1409" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1409" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1409" s="2">
+        <f>VLOOKUP(O1409,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:16">
+      <c r="A1410" s="7">
+        <v>130505</v>
+      </c>
+      <c r="B1410" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1410" s="2">
+        <f>VLOOKUP(B1410,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1410" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1410" s="2">
+        <f>VLOOKUP(D1410,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1410" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1410" s="2">
+        <f>VLOOKUP(F1410,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1410" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="I1410" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1410" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1410" s="1">
+        <v>7</v>
+      </c>
+      <c r="L1410" s="1"/>
+      <c r="M1410" s="1"/>
+      <c r="N1410" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1410" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1410" s="2">
+        <f>VLOOKUP(O1410,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:16">
+      <c r="A1411" s="7">
+        <v>130506</v>
+      </c>
+      <c r="B1411" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1411" s="2">
+        <f>VLOOKUP(B1411,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1411" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1411" s="2">
+        <f>VLOOKUP(D1411,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1411" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1411" s="2">
+        <f>VLOOKUP(F1411,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1411" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I1411" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1411" s="1"/>
+      <c r="K1411" s="1"/>
+      <c r="L1411" s="1"/>
+      <c r="M1411" s="1"/>
+      <c r="N1411" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1411" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1411" s="2">
+        <f>VLOOKUP(O1411,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:16">
+      <c r="A1412" s="7">
+        <v>130507</v>
+      </c>
+      <c r="B1412" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1412" s="2">
+        <f>VLOOKUP(B1412,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1412" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1412" s="2">
+        <f>VLOOKUP(D1412,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1412" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1412" s="2">
+        <f>VLOOKUP(F1412,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1412" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="I1412" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1412" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1412" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1412" s="1"/>
+      <c r="M1412" s="1"/>
+      <c r="N1412" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1412" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1412" s="2">
+        <f>VLOOKUP(O1412,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:16">
+      <c r="A1413" s="7">
+        <v>130508</v>
+      </c>
+      <c r="B1413" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1413" s="2">
+        <f>VLOOKUP(B1413,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1413" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1413" s="2">
+        <f>VLOOKUP(D1413,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1413" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1413" s="2">
+        <f>VLOOKUP(F1413,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1413" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="I1413" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1413" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1413" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1413" s="1"/>
+      <c r="M1413" s="1"/>
+      <c r="N1413" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1413" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1413" s="2">
+        <f>VLOOKUP(O1413,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:16">
+      <c r="A1414" s="7">
+        <v>130509</v>
+      </c>
+      <c r="B1414" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1414" s="2">
+        <f>VLOOKUP(B1414,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1414" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1414" s="2">
+        <f>VLOOKUP(D1414,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1414" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1414" s="2">
+        <f>VLOOKUP(F1414,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1414" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I1414" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1414" s="1"/>
+      <c r="K1414" s="1"/>
+      <c r="L1414" s="1"/>
+      <c r="M1414" s="1"/>
+      <c r="N1414" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1414" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1414" s="2">
+        <f>VLOOKUP(O1414,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:16">
+      <c r="A1415" s="7">
+        <v>130510</v>
+      </c>
+      <c r="B1415" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1415" s="2">
+        <f>VLOOKUP(B1415,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1415" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1415" s="2">
+        <f>VLOOKUP(D1415,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1415" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1415" s="2">
+        <f>VLOOKUP(F1415,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1415" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="I1415" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1415" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1415" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1415" s="1"/>
+      <c r="M1415" s="1"/>
+      <c r="N1415" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1415" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1415" s="2">
+        <f>VLOOKUP(O1415,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:16">
+      <c r="A1416" s="7">
+        <v>130511</v>
+      </c>
+      <c r="B1416" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1416" s="2">
+        <f>VLOOKUP(B1416,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1416" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1416" s="2">
+        <f>VLOOKUP(D1416,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1416" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1416" s="2">
+        <f>VLOOKUP(F1416,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1416" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="I1416" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1416" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1416" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1416" s="1"/>
+      <c r="M1416" s="1"/>
+      <c r="N1416" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1416" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1416" s="2">
+        <f>VLOOKUP(O1416,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:16">
+      <c r="A1417" s="7">
+        <v>130512</v>
+      </c>
+      <c r="B1417" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1417" s="2">
+        <f>VLOOKUP(B1417,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1417" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1417" s="2">
+        <f>VLOOKUP(D1417,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1417" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1417" s="2">
+        <f>VLOOKUP(F1417,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1417" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="I1417" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1417" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1417" s="1">
+        <v>4</v>
+      </c>
+      <c r="L1417" s="1"/>
+      <c r="M1417" s="1"/>
+      <c r="N1417" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1417" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1417" s="2">
+        <f>VLOOKUP(O1417,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:16">
+      <c r="A1418" s="7">
+        <v>130513</v>
+      </c>
+      <c r="B1418" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1418" s="2">
+        <f>VLOOKUP(B1418,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1418" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1418" s="2">
+        <f>VLOOKUP(D1418,Select!B:H,7,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F1418" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1418" s="2">
+        <f>VLOOKUP(F1418,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1418" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="I1418" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1418" s="1"/>
+      <c r="K1418" s="1"/>
+      <c r="L1418" s="1"/>
+      <c r="M1418" s="1"/>
+      <c r="N1418" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1418" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1418" s="2">
+        <f>VLOOKUP(O1418,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:16">
+      <c r="A1419" s="7">
+        <v>130514</v>
+      </c>
+      <c r="B1419" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C1419" s="2">
+        <f>VLOOKUP(B1419,Select!A:H,8,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D1419" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1419" s="2">
+        <f>VLOOKUP(D1419,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1419" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1419" s="2">
+        <f>VLOOKUP(F1419,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1419" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="I1419" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1419" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1419" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1419" s="1"/>
+      <c r="M1419" s="1"/>
+      <c r="N1419" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1419" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1419" s="2">
+        <f>VLOOKUP(O1419,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:16">
+      <c r="A1420" s="7">
+        <v>130600</v>
+      </c>
+      <c r="B1420" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1420" s="2">
+        <f>VLOOKUP(B1420,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1420" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1420" s="2">
+        <f>VLOOKUP(D1420,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1420" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1420" s="2">
+        <f>VLOOKUP(F1420,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1420" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="I1420" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1420" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1420" s="1">
+        <v>4</v>
+      </c>
+      <c r="L1420" s="1"/>
+      <c r="M1420" s="1"/>
+      <c r="N1420" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1420" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1420" s="2">
+        <f>VLOOKUP(O1420,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:16">
+      <c r="A1421" s="7">
+        <v>130601</v>
+      </c>
+      <c r="B1421" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1421" s="2">
+        <f>VLOOKUP(B1421,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1421" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1421" s="2">
+        <f>VLOOKUP(D1421,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1421" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1421" s="2">
+        <f>VLOOKUP(F1421,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1421" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="I1421" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1421" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1421" s="1">
+        <v>2</v>
+      </c>
+      <c r="L1421" s="1"/>
+      <c r="M1421" s="1"/>
+      <c r="N1421" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1421" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1421" s="2">
+        <f>VLOOKUP(O1421,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:16">
+      <c r="A1422" s="7">
+        <v>130602</v>
+      </c>
+      <c r="B1422" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1422" s="2">
+        <f>VLOOKUP(B1422,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1422" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1422" s="2">
+        <f>VLOOKUP(D1422,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1422" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1422" s="2">
+        <f>VLOOKUP(F1422,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1422" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="I1422" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1422" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1422" s="1">
+        <v>6</v>
+      </c>
+      <c r="L1422" s="1"/>
+      <c r="M1422" s="1"/>
+      <c r="N1422" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1422" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1422" s="2">
+        <f>VLOOKUP(O1422,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:16">
+      <c r="A1423" s="7">
+        <v>130603</v>
+      </c>
+      <c r="B1423" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1423" s="2">
+        <f>VLOOKUP(B1423,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1423" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1423" s="2">
+        <f>VLOOKUP(D1423,Select!B:H,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F1423" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1423" s="2">
+        <f>VLOOKUP(F1423,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1423" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="I1423" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1423" s="1"/>
+      <c r="K1423" s="1"/>
+      <c r="L1423" s="1"/>
+      <c r="M1423" s="1"/>
+      <c r="N1423" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1423" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1423" s="2">
+        <f>VLOOKUP(O1423,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:16">
+      <c r="A1424" s="7">
+        <v>130604</v>
+      </c>
+      <c r="B1424" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1424" s="2">
+        <f>VLOOKUP(B1424,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1424" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1424" s="2">
+        <f>VLOOKUP(D1424,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1424" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1424" s="2">
+        <f>VLOOKUP(F1424,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1424" s="1"/>
+      <c r="I1424" s="1"/>
+      <c r="J1424" s="1"/>
+      <c r="K1424" s="1"/>
+      <c r="L1424" s="1"/>
+      <c r="M1424" s="1"/>
+      <c r="N1424" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1424" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1424" s="2">
+        <f>VLOOKUP(O1424,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:16">
+      <c r="A1425" s="7">
+        <v>130605</v>
+      </c>
+      <c r="B1425" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1425" s="2">
+        <f>VLOOKUP(B1425,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1425" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1425" s="2">
+        <f>VLOOKUP(D1425,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1425" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1425" s="2">
+        <f>VLOOKUP(F1425,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1425" s="1"/>
+      <c r="I1425" s="1"/>
+      <c r="J1425" s="1"/>
+      <c r="K1425" s="1"/>
+      <c r="L1425" s="1"/>
+      <c r="M1425" s="1"/>
+      <c r="N1425" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1425" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1425" s="2">
+        <f>VLOOKUP(O1425,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:16">
+      <c r="A1426" s="7">
+        <v>130606</v>
+      </c>
+      <c r="B1426" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1426" s="2">
+        <f>VLOOKUP(B1426,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1426" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1426" s="2">
+        <f>VLOOKUP(D1426,Select!B:H,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F1426" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1426" s="2">
+        <f>VLOOKUP(F1426,Select!C:H,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H1426" s="1"/>
+      <c r="I1426" s="1"/>
+      <c r="J1426" s="1"/>
+      <c r="K1426" s="1"/>
+      <c r="L1426" s="1"/>
+      <c r="M1426" s="1"/>
+      <c r="N1426" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1426" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1426" s="2">
+        <f>VLOOKUP(O1426,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:16">
+      <c r="A1427" s="7">
+        <v>130607</v>
+      </c>
+      <c r="B1427" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1427" s="2">
+        <f>VLOOKUP(B1427,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1427" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1427" s="2">
+        <f>VLOOKUP(D1427,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1427" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1427" s="2">
+        <f>VLOOKUP(F1427,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1427" s="1"/>
+      <c r="I1427" s="1"/>
+      <c r="J1427" s="1"/>
+      <c r="K1427" s="1"/>
+      <c r="L1427" s="1"/>
+      <c r="M1427" s="1"/>
+      <c r="N1427" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1427" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1427" s="2">
+        <f>VLOOKUP(O1427,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:16">
+      <c r="A1428" s="7">
+        <v>130608</v>
+      </c>
+      <c r="B1428" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1428" s="2">
+        <f>VLOOKUP(B1428,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1428" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1428" s="2">
+        <f>VLOOKUP(D1428,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1428" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1428" s="2">
+        <f>VLOOKUP(F1428,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1428" s="1"/>
+      <c r="I1428" s="1"/>
+      <c r="J1428" s="1"/>
+      <c r="K1428" s="1"/>
+      <c r="L1428" s="1"/>
+      <c r="M1428" s="1"/>
+      <c r="N1428" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1428" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1428" s="2">
+        <f>VLOOKUP(O1428,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:16">
+      <c r="A1429" s="7">
+        <v>130609</v>
+      </c>
+      <c r="B1429" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1429" s="2">
+        <f>VLOOKUP(B1429,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1429" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1429" s="2">
+        <f>VLOOKUP(D1429,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1429" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1429" s="2">
+        <f>VLOOKUP(F1429,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1429" s="1"/>
+      <c r="I1429" s="1"/>
+      <c r="J1429" s="1"/>
+      <c r="K1429" s="1"/>
+      <c r="L1429" s="1"/>
+      <c r="M1429" s="1"/>
+      <c r="N1429" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1429" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1429" s="2">
+        <f>VLOOKUP(O1429,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:16">
+      <c r="A1430" s="7">
+        <v>130610</v>
+      </c>
+      <c r="B1430" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1430" s="2">
+        <f>VLOOKUP(B1430,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1430" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1430" s="2">
+        <f>VLOOKUP(D1430,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1430" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1430" s="2">
+        <f>VLOOKUP(F1430,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1430" s="1"/>
+      <c r="I1430" s="1"/>
+      <c r="J1430" s="1"/>
+      <c r="K1430" s="1"/>
+      <c r="L1430" s="1"/>
+      <c r="M1430" s="1"/>
+      <c r="N1430" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1430" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1430" s="2">
+        <f>VLOOKUP(O1430,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:16">
+      <c r="A1431" s="7">
+        <v>130611</v>
+      </c>
+      <c r="B1431" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1431" s="2">
+        <f>VLOOKUP(B1431,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1431" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1431" s="2">
+        <f>VLOOKUP(D1431,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1431" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1431" s="2">
+        <f>VLOOKUP(F1431,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1431" s="1"/>
+      <c r="I1431" s="1"/>
+      <c r="J1431" s="1"/>
+      <c r="K1431" s="1"/>
+      <c r="L1431" s="1"/>
+      <c r="M1431" s="1"/>
+      <c r="N1431" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1431" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1431" s="2">
+        <f>VLOOKUP(O1431,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:16">
+      <c r="A1432" s="7">
+        <v>130612</v>
+      </c>
+      <c r="B1432" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1432" s="2">
+        <f>VLOOKUP(B1432,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1432" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1432" s="2">
+        <f>VLOOKUP(D1432,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1432" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1432" s="2">
+        <f>VLOOKUP(F1432,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1432" s="1"/>
+      <c r="I1432" s="1"/>
+      <c r="J1432" s="1"/>
+      <c r="K1432" s="1"/>
+      <c r="L1432" s="1"/>
+      <c r="M1432" s="1"/>
+      <c r="N1432" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1432" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1432" s="2">
+        <f>VLOOKUP(O1432,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:16">
+      <c r="A1433" s="7">
+        <v>130613</v>
+      </c>
+      <c r="B1433" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1433" s="2">
+        <f>VLOOKUP(B1433,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1433" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1433" s="2">
+        <f>VLOOKUP(D1433,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1433" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1433" s="2">
+        <f>VLOOKUP(F1433,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1433" s="1"/>
+      <c r="I1433" s="1"/>
+      <c r="J1433" s="1"/>
+      <c r="K1433" s="1"/>
+      <c r="L1433" s="1"/>
+      <c r="M1433" s="1"/>
+      <c r="N1433" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1433" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1433" s="2">
+        <f>VLOOKUP(O1433,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:16">
+      <c r="A1434" s="7">
+        <v>130614</v>
+      </c>
+      <c r="B1434" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C1434" s="2">
+        <f>VLOOKUP(B1434,Select!A:H,8,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D1434" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1434" s="2">
+        <f>VLOOKUP(D1434,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1434" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1434" s="2">
+        <f>VLOOKUP(F1434,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1434" s="1"/>
+      <c r="I1434" s="1"/>
+      <c r="J1434" s="1"/>
+      <c r="K1434" s="1"/>
+      <c r="L1434" s="1"/>
+      <c r="M1434" s="1"/>
+      <c r="N1434" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1434" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1434" s="2">
+        <f>VLOOKUP(O1434,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:16">
+      <c r="A1435" s="7"/>
+      <c r="B1435" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1435" s="2">
+        <f>VLOOKUP(B1435,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1435" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1435" s="2">
+        <f>VLOOKUP(D1435,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1435" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1435" s="2">
+        <f>VLOOKUP(F1435,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1435" s="1"/>
+      <c r="I1435" s="1"/>
+      <c r="J1435" s="1"/>
+      <c r="K1435" s="1"/>
+      <c r="L1435" s="1"/>
+      <c r="M1435" s="1"/>
+      <c r="N1435" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1435" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1435" s="2">
+        <f>VLOOKUP(O1435,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:16">
+      <c r="A1436" s="7"/>
+      <c r="B1436" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1436" s="2">
+        <f>VLOOKUP(B1436,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1436" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1436" s="2">
+        <f>VLOOKUP(D1436,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1436" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1436" s="2">
+        <f>VLOOKUP(F1436,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1436" s="1"/>
+      <c r="I1436" s="1"/>
+      <c r="J1436" s="1"/>
+      <c r="K1436" s="1"/>
+      <c r="L1436" s="1"/>
+      <c r="M1436" s="1"/>
+      <c r="N1436" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1436" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1436" s="2">
+        <f>VLOOKUP(O1436,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:16">
+      <c r="A1437" s="7"/>
+      <c r="B1437" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1437" s="2">
+        <f>VLOOKUP(B1437,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1437" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1437" s="2">
+        <f>VLOOKUP(D1437,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1437" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1437" s="2">
+        <f>VLOOKUP(F1437,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1437" s="1"/>
+      <c r="I1437" s="1"/>
+      <c r="J1437" s="1"/>
+      <c r="K1437" s="1"/>
+      <c r="L1437" s="1"/>
+      <c r="M1437" s="1"/>
+      <c r="N1437" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1437" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1437" s="2">
+        <f>VLOOKUP(O1437,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:16">
+      <c r="A1438" s="7"/>
+      <c r="B1438" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1438" s="2">
+        <f>VLOOKUP(B1438,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1438" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1438" s="2">
+        <f>VLOOKUP(D1438,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1438" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1438" s="2">
+        <f>VLOOKUP(F1438,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1438" s="1"/>
+      <c r="I1438" s="1"/>
+      <c r="J1438" s="1"/>
+      <c r="K1438" s="1"/>
+      <c r="L1438" s="1"/>
+      <c r="M1438" s="1"/>
+      <c r="N1438" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1438" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1438" s="2">
+        <f>VLOOKUP(O1438,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:16">
+      <c r="A1439" s="7"/>
+      <c r="B1439" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1439" s="2">
+        <f>VLOOKUP(B1439,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1439" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1439" s="2">
+        <f>VLOOKUP(D1439,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1439" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1439" s="2">
+        <f>VLOOKUP(F1439,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1439" s="1"/>
+      <c r="I1439" s="1"/>
+      <c r="J1439" s="1"/>
+      <c r="K1439" s="1"/>
+      <c r="L1439" s="1"/>
+      <c r="M1439" s="1"/>
+      <c r="N1439" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1439" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1439" s="2">
+        <f>VLOOKUP(O1439,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:16">
+      <c r="A1440" s="7"/>
+      <c r="B1440" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1440" s="2">
+        <f>VLOOKUP(B1440,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1440" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1440" s="2">
+        <f>VLOOKUP(D1440,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1440" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1440" s="2">
+        <f>VLOOKUP(F1440,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1440" s="1"/>
+      <c r="I1440" s="1"/>
+      <c r="J1440" s="1"/>
+      <c r="K1440" s="1"/>
+      <c r="L1440" s="1"/>
+      <c r="M1440" s="1"/>
+      <c r="N1440" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1440" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1440" s="2">
+        <f>VLOOKUP(O1440,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:16">
+      <c r="A1441" s="7"/>
+      <c r="B1441" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1441" s="2">
+        <f>VLOOKUP(B1441,Select!A:H,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D1441" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1441" s="2">
+        <f>VLOOKUP(D1441,Select!B:H,7,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F1441" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1441" s="2">
+        <f>VLOOKUP(F1441,Select!C:H,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H1441" s="1"/>
+      <c r="I1441" s="1"/>
+      <c r="J1441" s="1"/>
+      <c r="K1441" s="1"/>
+      <c r="L1441" s="1"/>
+      <c r="M1441" s="1"/>
+      <c r="N1441" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O1441" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="P1441" s="2">
+        <f>VLOOKUP(O1441,Select!D:H,5,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -70926,7 +77499,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{99D89BCA-0BD9-4CE2-821E-34C39AE42621}">
+          <x14:cfRule type="containsText" priority="78" operator="containsText" id="{99D89BCA-0BD9-4CE2-821E-34C39AE42621}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$8,B1)))</xm:f>
             <xm:f>Select!$A$8</xm:f>
             <x14:dxf>
@@ -70937,7 +77510,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{C69D7B5B-D7A2-4E0A-BD00-0FDBC2AD95FB}">
+          <x14:cfRule type="containsText" priority="79" operator="containsText" id="{C69D7B5B-D7A2-4E0A-BD00-0FDBC2AD95FB}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$7,B1)))</xm:f>
             <xm:f>Select!$A$7</xm:f>
             <x14:dxf>
@@ -70948,7 +77521,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{7A1A35A6-DD9E-4143-8A19-366128D24E22}">
+          <x14:cfRule type="containsText" priority="81" operator="containsText" id="{7A1A35A6-DD9E-4143-8A19-366128D24E22}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$6,B1)))</xm:f>
             <xm:f>Select!$A$6</xm:f>
             <x14:dxf>
@@ -70959,7 +77532,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{6AF9B890-D4F2-4414-9165-6A629AB659CF}">
+          <x14:cfRule type="containsText" priority="82" operator="containsText" id="{6AF9B890-D4F2-4414-9165-6A629AB659CF}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$5,B1)))</xm:f>
             <xm:f>Select!$A$5</xm:f>
             <x14:dxf>
@@ -70970,7 +77543,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{3D6A8E9E-7973-406B-99C5-67C4FA2AFE40}">
+          <x14:cfRule type="containsText" priority="83" operator="containsText" id="{3D6A8E9E-7973-406B-99C5-67C4FA2AFE40}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$4,B1)))</xm:f>
             <xm:f>Select!$A$4</xm:f>
             <x14:dxf>
@@ -70981,7 +77554,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{15DE4380-B253-4995-B251-88E067C7F6A0}">
+          <x14:cfRule type="containsText" priority="84" operator="containsText" id="{15DE4380-B253-4995-B251-88E067C7F6A0}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$3,B1)))</xm:f>
             <xm:f>Select!$A$3</xm:f>
             <x14:dxf>
@@ -70992,7 +77565,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{C80F7600-6A4A-43CA-A47B-5362E6E2EA0B}">
+          <x14:cfRule type="containsText" priority="85" operator="containsText" id="{C80F7600-6A4A-43CA-A47B-5362E6E2EA0B}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$2,B1)))</xm:f>
             <xm:f>Select!$A$2</xm:f>
             <x14:dxf>
@@ -71003,7 +77576,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{CC52E7CD-C8E6-4221-93AF-A24FC1D2E858}">
+          <x14:cfRule type="containsText" priority="86" operator="containsText" id="{CC52E7CD-C8E6-4221-93AF-A24FC1D2E858}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$1,B1)))</xm:f>
             <xm:f>Select!$A$1</xm:f>
             <x14:dxf>
@@ -71014,10 +77587,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B1:B1048485</xm:sqref>
+          <xm:sqref>B1:B1322 B1442:B1048485</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{22FD9130-A289-4A10-9801-E2DC87546FB0}">
+          <x14:cfRule type="containsText" priority="69" operator="containsText" id="{22FD9130-A289-4A10-9801-E2DC87546FB0}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$10,B2)))</xm:f>
             <xm:f>Select!$A$10</xm:f>
             <x14:dxf>
@@ -71028,7 +77601,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{7B44D6AF-6B67-47C3-BB80-5B5BB17585B8}">
+          <x14:cfRule type="containsText" priority="70" operator="containsText" id="{7B44D6AF-6B67-47C3-BB80-5B5BB17585B8}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$A$9,B2)))</xm:f>
             <xm:f>Select!$A$9</xm:f>
             <x14:dxf>
@@ -71039,10 +77612,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:B1048485</xm:sqref>
+          <xm:sqref>B2:B1322 B1442:B1048485</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{4BE5AF07-632D-4617-A7D7-D144151048A8}">
+          <x14:cfRule type="containsText" priority="74" operator="containsText" id="{4BE5AF07-632D-4617-A7D7-D144151048A8}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$B$4,D1)))</xm:f>
             <xm:f>Select!$B$4</xm:f>
             <x14:dxf>
@@ -71053,7 +77626,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{98B5A476-FB7E-48CA-8B0C-607319B00387}">
+          <x14:cfRule type="containsText" priority="75" operator="containsText" id="{98B5A476-FB7E-48CA-8B0C-607319B00387}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$B$3,D1)))</xm:f>
             <xm:f>Select!$B$3</xm:f>
             <x14:dxf>
@@ -71064,7 +77637,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{7578001D-CA6A-4F4D-A326-B1BB6B2F3B4E}">
+          <x14:cfRule type="containsText" priority="76" operator="containsText" id="{7578001D-CA6A-4F4D-A326-B1BB6B2F3B4E}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$B$2,D1)))</xm:f>
             <xm:f>Select!$B$2</xm:f>
             <x14:dxf>
@@ -71075,7 +77648,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{1ED03CCB-CDEA-4FD3-87AB-E7BC9550BE88}">
+          <x14:cfRule type="containsText" priority="77" operator="containsText" id="{1ED03CCB-CDEA-4FD3-87AB-E7BC9550BE88}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$B$1,D1)))</xm:f>
             <xm:f>Select!$B$1</xm:f>
             <x14:dxf>
@@ -71086,10 +77659,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>D1:D1048485</xm:sqref>
+          <xm:sqref>D1:D1322 D1442:D1048485</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{BBAC420F-7571-4A77-83A0-FD132E7103B9}">
+          <x14:cfRule type="containsText" priority="71" operator="containsText" id="{BBAC420F-7571-4A77-83A0-FD132E7103B9}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$C$3,F1)))</xm:f>
             <xm:f>Select!$C$3</xm:f>
             <x14:dxf>
@@ -71100,7 +77673,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{0DBD0A4C-594D-43B5-A0FD-2E76CABBE938}">
+          <x14:cfRule type="containsText" priority="72" operator="containsText" id="{0DBD0A4C-594D-43B5-A0FD-2E76CABBE938}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$C$2,F1)))</xm:f>
             <xm:f>Select!$C$2</xm:f>
             <x14:dxf>
@@ -71111,7 +77684,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{A07E5F41-140C-479B-AD95-BB6BED570A27}">
+          <x14:cfRule type="containsText" priority="73" operator="containsText" id="{A07E5F41-140C-479B-AD95-BB6BED570A27}">
             <xm:f>NOT(ISERROR(SEARCH(Select!$C$1,F1)))</xm:f>
             <xm:f>Select!$C$1</xm:f>
             <x14:dxf>
@@ -71122,7 +77695,803 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F1:F1048485</xm:sqref>
+          <xm:sqref>F1:F1322 F1442:F1048485</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="61" operator="containsText" id="{92143C14-6504-4968-A01E-7690A9DE7024}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$8,B1323)))</xm:f>
+            <xm:f>Select!$A$8</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="4" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="62" operator="containsText" id="{DACC30B7-7B28-4D0B-9B7A-5FE3162D25E5}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$7,B1323)))</xm:f>
+            <xm:f>Select!$A$7</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCFCF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="63" operator="containsText" id="{2D5153C5-0D23-4FBE-A213-E6CA623D0EAA}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$6,B1323)))</xm:f>
+            <xm:f>Select!$A$6</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCD6D6"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="64" operator="containsText" id="{6716FAFB-9E5D-40A2-B1FA-D40256B33B7B}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$5,B1323)))</xm:f>
+            <xm:f>Select!$A$5</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="5" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="65" operator="containsText" id="{AB96FCE3-8714-4F09-8386-96CDCA95DAF4}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$4,B1323)))</xm:f>
+            <xm:f>Select!$A$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="66" operator="containsText" id="{B68C9254-BE89-421E-A459-10E2AEFEE3B6}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$3,B1323)))</xm:f>
+            <xm:f>Select!$A$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="67" operator="containsText" id="{3A3E4B67-E1C6-43F0-B354-9D4411C73787}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$2,B1323)))</xm:f>
+            <xm:f>Select!$A$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="68" operator="containsText" id="{8007A261-8AB6-41A1-8077-0CFC02ABD0EB}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$1,B1323)))</xm:f>
+            <xm:f>Select!$A$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1323:B1333 B1335:B1441</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="52" operator="containsText" id="{398F0B6C-D562-4DA8-B6CB-F2DC4C718DEE}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$10,B1323)))</xm:f>
+            <xm:f>Select!$A$10</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFD1D1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{FFEA31F8-2E25-4336-B4D4-C17E9C46A246}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$9,B1323)))</xm:f>
+            <xm:f>Select!$A$9</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE6D5F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1323:B1333 B1335:B1441</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="57" operator="containsText" id="{2BEA5303-F103-4565-BCD5-684FF6CCE194}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$4,D1323)))</xm:f>
+            <xm:f>Select!$B$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE8D9F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="58" operator="containsText" id="{B8EC7611-E87C-48D6-A144-452BA619023B}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$3,D1323)))</xm:f>
+            <xm:f>Select!$B$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="59" operator="containsText" id="{3EA833D9-54B1-4650-9E28-DFD4EC874B57}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$2,D1323)))</xm:f>
+            <xm:f>Select!$B$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="60" operator="containsText" id="{ABEB89CE-7CFD-434D-931A-4E2744F0BB8D}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$1,D1323)))</xm:f>
+            <xm:f>Select!$B$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFEBD8BB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>D1323:D1333 D1335:D1441</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{F95CF403-3625-4421-AB5E-04A8BEC31966}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$3,F1323)))</xm:f>
+            <xm:f>Select!$C$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="55" operator="containsText" id="{F9C67EBF-A17F-4E85-B588-0CF9372672F2}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$2,F1323)))</xm:f>
+            <xm:f>Select!$C$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE2DAF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="56" operator="containsText" id="{83EC786E-A6D4-4B12-857B-73EF8FC0F8BE}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$1,F1323)))</xm:f>
+            <xm:f>Select!$C$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFDE3E3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>F1323:F1333 F1335:F1441</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{546277DD-74C9-49D6-AE90-B826FF076F60}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$8,B1334)))</xm:f>
+            <xm:f>Select!$A$8</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="4" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="45" operator="containsText" id="{E00EF05E-B89A-4CE1-A445-4893909C2AD1}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$7,B1334)))</xm:f>
+            <xm:f>Select!$A$7</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCFCF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="46" operator="containsText" id="{177AAFC1-4D1A-4322-8BEE-74BCE99C0D40}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$6,B1334)))</xm:f>
+            <xm:f>Select!$A$6</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCD6D6"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{9E387369-24F4-4C53-AABD-67A51406B2FD}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$5,B1334)))</xm:f>
+            <xm:f>Select!$A$5</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="5" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="48" operator="containsText" id="{B8DC5A50-A9BF-4ED2-8FD6-2846A0302280}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$4,B1334)))</xm:f>
+            <xm:f>Select!$A$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{17F1CD04-01DF-4CA2-A1AF-32CC70249C2C}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$3,B1334)))</xm:f>
+            <xm:f>Select!$A$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="50" operator="containsText" id="{5014B8A3-C259-40C1-BFA7-9642378AC2F1}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$2,B1334)))</xm:f>
+            <xm:f>Select!$A$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="51" operator="containsText" id="{937B94AD-5D1A-4FA6-8DAC-52EEA80E975A}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$1,B1334)))</xm:f>
+            <xm:f>Select!$A$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{029D81E1-FDAD-421E-9511-EC17E595FEFB}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$10,B1334)))</xm:f>
+            <xm:f>Select!$A$10</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFD1D1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="36" operator="containsText" id="{74146C97-4C12-43E1-B8C3-2F7D40425394}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$9,B1334)))</xm:f>
+            <xm:f>Select!$A$9</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE6D5F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="40" operator="containsText" id="{A8172EB4-C00D-44BF-9C93-06A0C399257B}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$4,D1334)))</xm:f>
+            <xm:f>Select!$B$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE8D9F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{4AFB38BC-6F21-461B-B8C3-B8952319F897}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$3,D1334)))</xm:f>
+            <xm:f>Select!$B$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="42" operator="containsText" id="{BE2E58AA-EE69-40D4-84C9-24230E812FEA}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$2,D1334)))</xm:f>
+            <xm:f>Select!$B$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="43" operator="containsText" id="{22D7D771-FC4B-42E9-B50C-E308FFF796EC}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$1,D1334)))</xm:f>
+            <xm:f>Select!$B$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFEBD8BB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>D1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{A0737C6A-43F7-4DEF-A14C-8954485DDF0B}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$3,F1334)))</xm:f>
+            <xm:f>Select!$C$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{43E842BE-2A58-415E-98B4-3BCBEC9C53AC}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$2,F1334)))</xm:f>
+            <xm:f>Select!$C$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE2DAF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{4B7CD98F-889E-4626-855A-6E36817C877D}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$1,F1334)))</xm:f>
+            <xm:f>Select!$C$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFDE3E3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>F1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="27" operator="containsText" id="{D8274BFB-D339-4377-872E-52F3CAF43AD7}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$8,B1334)))</xm:f>
+            <xm:f>Select!$A$8</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="4" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{32B91E16-B5B7-4F91-B471-1BC7DBC7BAB6}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$7,B1334)))</xm:f>
+            <xm:f>Select!$A$7</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCFCF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{29B15899-9C08-41B0-BC6F-78CB1FF54FA3}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$6,B1334)))</xm:f>
+            <xm:f>Select!$A$6</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCD6D6"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="30" operator="containsText" id="{BF1F9CE3-0C8B-47D2-8F84-935A45E1E00C}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$5,B1334)))</xm:f>
+            <xm:f>Select!$A$5</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="5" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="31" operator="containsText" id="{1CC71886-45F8-433D-9F94-80F4085A5EE8}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$4,B1334)))</xm:f>
+            <xm:f>Select!$A$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{F6721A67-1C85-4ACC-9B06-043D31FDCC48}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$3,B1334)))</xm:f>
+            <xm:f>Select!$A$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{68638305-00A3-450F-8459-DE3C91CEDA69}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$2,B1334)))</xm:f>
+            <xm:f>Select!$A$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{F8C35419-0637-431A-AE48-6E13FAE52CC8}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$1,B1334)))</xm:f>
+            <xm:f>Select!$A$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{0B17CDD7-98C1-483A-93B1-1D3275CE8852}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$10,B1334)))</xm:f>
+            <xm:f>Select!$A$10</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFD1D1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="19" operator="containsText" id="{4A132E52-EE86-45C7-89F8-A9DEF2FA35D5}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$9,B1334)))</xm:f>
+            <xm:f>Select!$A$9</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE6D5F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="23" operator="containsText" id="{1A2B9AC5-22AC-431B-AB88-D9516BB3E34E}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$4,D1334)))</xm:f>
+            <xm:f>Select!$B$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE8D9F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{3F6667C6-AD6D-4B48-9AB6-3C6ECC845E21}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$3,D1334)))</xm:f>
+            <xm:f>Select!$B$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="25" operator="containsText" id="{5D50C1B7-602A-4897-AEB1-B41FA699943C}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$2,D1334)))</xm:f>
+            <xm:f>Select!$B$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{2865187E-CC56-4344-A0BD-3C36121BBCF8}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$1,D1334)))</xm:f>
+            <xm:f>Select!$B$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFEBD8BB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>D1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{666CC2F5-C1A4-48D9-AE12-28A1230EAA85}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$3,F1334)))</xm:f>
+            <xm:f>Select!$C$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="21" operator="containsText" id="{9F96C4F4-E563-4248-AD9A-BAED080C320C}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$2,F1334)))</xm:f>
+            <xm:f>Select!$C$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE2DAF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{4756FA72-022E-4A50-BF52-886EC6ED149A}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$1,F1334)))</xm:f>
+            <xm:f>Select!$C$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFDE3E3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>F1334</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{7D068086-419E-4ED3-83A5-A1F872653349}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$8,B1335)))</xm:f>
+            <xm:f>Select!$A$8</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="4" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{F0910699-5738-4369-B4D7-1E68C9FB38AF}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$7,B1335)))</xm:f>
+            <xm:f>Select!$A$7</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCFCF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{84FD8553-81E0-4299-AC8D-AC40059D8CC7}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$6,B1335)))</xm:f>
+            <xm:f>Select!$A$6</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFCD6D6"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{5D84F2DE-4298-4DD6-BEBF-A086945EE9B4}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$5,B1335)))</xm:f>
+            <xm:f>Select!$A$5</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="5" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{F9D0A32C-B3C4-43D6-9932-92A5AAC3F7DD}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$4,B1335)))</xm:f>
+            <xm:f>Select!$A$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{20A80A28-8D1E-4841-AF09-F798E744ADCD}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$3,B1335)))</xm:f>
+            <xm:f>Select!$A$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{14A301C1-2AF1-4838-9F94-EAB5C657C791}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$2,B1335)))</xm:f>
+            <xm:f>Select!$A$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{9E9332D0-8B3C-483D-A20E-093F6B5C34BD}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$1,B1335)))</xm:f>
+            <xm:f>Select!$A$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1335</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{085B923A-97CF-455F-875B-E6A509D4173D}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$10,B1335)))</xm:f>
+            <xm:f>Select!$A$10</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFD1D1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{E0599A6A-97DD-4061-AB64-58EB2125F7A7}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$A$9,B1335)))</xm:f>
+            <xm:f>Select!$A$9</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE6D5F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B1335</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{C61B483B-F86B-4C29-813C-92F564EB2B16}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$4,D1335)))</xm:f>
+            <xm:f>Select!$B$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE8D9F3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{24EEF98B-AE13-46BE-A88B-E9C540278211}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$3,D1335)))</xm:f>
+            <xm:f>Select!$B$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{58D4E435-F559-4CD5-9D19-A2CC09B2FC74}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$2,D1335)))</xm:f>
+            <xm:f>Select!$B$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{FEE8106A-9A0E-4E75-B6DB-F96B365AA214}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$B$1,D1335)))</xm:f>
+            <xm:f>Select!$B$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFEBD8BB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>D1335</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{A88992A4-3AB9-460B-B246-D0ED97C0BB31}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$3,F1335)))</xm:f>
+            <xm:f>Select!$C$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{2F339A82-9D41-4CE3-82C5-1FFAF003230F}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$2,F1335)))</xm:f>
+            <xm:f>Select!$C$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE2DAF2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{4F69B383-436E-431D-AA1A-F11C16E9410D}">
+            <xm:f>NOT(ISERROR(SEARCH(Select!$C$1,F1335)))</xm:f>
+            <xm:f>Select!$C$1</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFDE3E3"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>F1335</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -71165,6 +78534,52 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB72631C-A971-4DDF-8EB1-62FE8456FDB2}">
+  <dimension ref="B2:D5"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="10" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="10" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12953D30-CE33-4EF2-BD8B-9EB747A2658E}">
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
